--- a/DDD___Pamunkey___NSI.xlsx
+++ b/DDD___Pamunkey___NSI.xlsx
@@ -1,41 +1,119 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9a7f23234f188053/GitHub_projects/ADAPT/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_40EF431F4A29FC6F5C6002AB8855B237A12CC00A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A68E1D4D-DC90-48CB-9C3E-5969D78588BD}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="10690" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="29">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>occupancy_type</t>
+  </si>
+  <si>
+    <t>building_type</t>
+  </si>
+  <si>
+    <t>number_of_stories</t>
+  </si>
+  <si>
+    <t>area</t>
+  </si>
+  <si>
+    <t>foundation_type</t>
+  </si>
+  <si>
+    <t>foundation_height</t>
+  </si>
+  <si>
+    <t>year_built</t>
+  </si>
+  <si>
+    <t>ground_elevation</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>longitude</t>
+  </si>
+  <si>
+    <t>latitude</t>
+  </si>
+  <si>
+    <t>structure_value</t>
+  </si>
+  <si>
+    <t>content_value</t>
+  </si>
+  <si>
+    <t>RES2</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>RES1</t>
+  </si>
+  <si>
+    <t>REL1</t>
+  </si>
+  <si>
+    <t>RES4</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>RES3A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>COM8</t>
+  </si>
+  <si>
+    <t>RES3F</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +143,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,62 +482,66 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N115"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>occupancy_type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>building_type</v>
-      </c>
-      <c r="D1" t="str">
-        <v>number_of_stories</v>
-      </c>
-      <c r="E1" t="str">
-        <v>area</v>
-      </c>
-      <c r="F1" t="str">
-        <v>foundation_type</v>
-      </c>
-      <c r="G1" t="str">
-        <v>foundation_height</v>
-      </c>
-      <c r="H1" t="str">
-        <v>year_built</v>
-      </c>
-      <c r="I1" t="str">
-        <v>ground_elevation</v>
-      </c>
-      <c r="J1" t="str">
-        <v>address</v>
-      </c>
-      <c r="K1" t="str">
-        <v>longitude</v>
-      </c>
-      <c r="L1" t="str">
-        <v>latitude</v>
-      </c>
-      <c r="M1" t="str">
-        <v>structure_value</v>
-      </c>
-      <c r="N1" t="str">
-        <v>content_value</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>579512986</v>
       </c>
-      <c r="B2" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C2" t="str">
-        <v>H</v>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -459,8 +549,8 @@
       <c r="E2">
         <v>2368</v>
       </c>
-      <c r="F2" t="str">
-        <v>C</v>
+      <c r="F2" t="s">
+        <v>16</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -471,14 +561,14 @@
       <c r="I2">
         <v>14.83</v>
       </c>
-      <c r="J2" t="str">
-        <v/>
+      <c r="J2" t="s">
+        <v>17</v>
       </c>
       <c r="K2">
-        <v>-77.00008392333984</v>
+        <v>-77.000083923339844</v>
       </c>
       <c r="L2">
-        <v>37.57748237613323</v>
+        <v>37.577482376133233</v>
       </c>
       <c r="M2">
         <v>173575.88</v>
@@ -487,15 +577,15 @@
         <v>86787.94</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>579512987</v>
       </c>
-      <c r="B3" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C3" t="str">
-        <v>W</v>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -503,8 +593,8 @@
       <c r="E3">
         <v>1917.3</v>
       </c>
-      <c r="F3" t="str">
-        <v>C</v>
+      <c r="F3" t="s">
+        <v>16</v>
       </c>
       <c r="G3">
         <v>6</v>
@@ -515,31 +605,31 @@
       <c r="I3">
         <v>5.7363</v>
       </c>
-      <c r="J3" t="str">
-        <v/>
+      <c r="J3" t="s">
+        <v>17</v>
       </c>
       <c r="K3">
-        <v>-76.9972635</v>
+        <v>-76.997263500000003</v>
       </c>
       <c r="L3">
-        <v>37.5749975</v>
+        <v>37.574997500000002</v>
       </c>
       <c r="M3">
-        <v>158933.36</v>
+        <v>158933.35999999999</v>
       </c>
       <c r="N3">
-        <v>79466.68</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>79466.679999999993</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>579512988</v>
       </c>
-      <c r="B4" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C4" t="str">
-        <v>S</v>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -547,8 +637,8 @@
       <c r="E4">
         <v>1045</v>
       </c>
-      <c r="F4" t="str">
-        <v>P</v>
+      <c r="F4" t="s">
+        <v>20</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -559,14 +649,14 @@
       <c r="I4">
         <v>11.82</v>
       </c>
-      <c r="J4" t="str">
-        <v/>
+      <c r="J4" t="s">
+        <v>17</v>
       </c>
       <c r="K4">
-        <v>-77.0036566257477</v>
+        <v>-77.003656625747695</v>
       </c>
       <c r="L4">
-        <v>37.57843257112545</v>
+        <v>37.578432571125447</v>
       </c>
       <c r="M4">
         <v>197181.02</v>
@@ -575,15 +665,15 @@
         <v>98590.51</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>579512989</v>
       </c>
-      <c r="B5" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C5" t="str">
-        <v>H</v>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -591,8 +681,8 @@
       <c r="E5">
         <v>2289</v>
       </c>
-      <c r="F5" t="str">
-        <v>P</v>
+      <c r="F5" t="s">
+        <v>20</v>
       </c>
       <c r="G5">
         <v>1.5</v>
@@ -603,14 +693,14 @@
       <c r="I5">
         <v>12.33</v>
       </c>
-      <c r="J5" t="str">
-        <v/>
+      <c r="J5" t="s">
+        <v>17</v>
       </c>
       <c r="K5">
-        <v>-77.00291521</v>
+        <v>-77.002915209999998</v>
       </c>
       <c r="L5">
-        <v>37.57583802</v>
+        <v>37.575838019999999</v>
       </c>
       <c r="M5">
         <v>267814.75</v>
@@ -619,15 +709,15 @@
         <v>133907.38</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>579512990</v>
       </c>
-      <c r="B6" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C6" t="str">
-        <v>W</v>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -635,8 +725,8 @@
       <c r="E6">
         <v>3454.5</v>
       </c>
-      <c r="F6" t="str">
-        <v>C</v>
+      <c r="F6" t="s">
+        <v>16</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -645,16 +735,16 @@
         <v>1980</v>
       </c>
       <c r="I6">
-        <v>8.79</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="J6" t="s">
+        <v>17</v>
       </c>
       <c r="K6">
-        <v>-76.99906736612321</v>
+        <v>-76.999067366123214</v>
       </c>
       <c r="L6">
-        <v>37.57508664052678</v>
+        <v>37.575086640526777</v>
       </c>
       <c r="M6">
         <v>246568.46</v>
@@ -663,15 +753,15 @@
         <v>123284.23</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>579513006</v>
       </c>
-      <c r="B7" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C7" t="str">
-        <v>W</v>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -679,8 +769,8 @@
       <c r="E7">
         <v>1892.8</v>
       </c>
-      <c r="F7" t="str">
-        <v>P</v>
+      <c r="F7" t="s">
+        <v>20</v>
       </c>
       <c r="G7">
         <v>3.5</v>
@@ -689,13 +779,13 @@
         <v>1980</v>
       </c>
       <c r="I7">
-        <v>8.3592</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
+        <v>8.3591999999999995</v>
+      </c>
+      <c r="J7" t="s">
+        <v>17</v>
       </c>
       <c r="K7">
-        <v>-77.000773</v>
+        <v>-77.000772999999995</v>
       </c>
       <c r="L7">
         <v>37.572578</v>
@@ -707,15 +797,15 @@
         <v>91655.65</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>579513007</v>
       </c>
-      <c r="B8" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C8" t="str">
-        <v>H</v>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -723,8 +813,8 @@
       <c r="E8">
         <v>1340.1</v>
       </c>
-      <c r="F8" t="str">
-        <v>P</v>
+      <c r="F8" t="s">
+        <v>20</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -735,14 +825,14 @@
       <c r="I8">
         <v>11.63</v>
       </c>
-      <c r="J8" t="str">
-        <v/>
+      <c r="J8" t="s">
+        <v>17</v>
       </c>
       <c r="K8">
-        <v>-77.005322</v>
+        <v>-77.005322000000007</v>
       </c>
       <c r="L8">
-        <v>37.5785765</v>
+        <v>37.578576499999997</v>
       </c>
       <c r="M8">
         <v>212466.58</v>
@@ -751,15 +841,15 @@
         <v>106233.29</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>579513008</v>
       </c>
-      <c r="B9" t="str">
-        <v>REL1</v>
-      </c>
-      <c r="C9" t="str">
-        <v>W</v>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -767,8 +857,8 @@
       <c r="E9">
         <v>1721.5</v>
       </c>
-      <c r="F9" t="str">
-        <v>C</v>
+      <c r="F9" t="s">
+        <v>16</v>
       </c>
       <c r="G9">
         <v>1.5</v>
@@ -779,14 +869,14 @@
       <c r="I9">
         <v>12.64</v>
       </c>
-      <c r="J9" t="str">
-        <v/>
+      <c r="J9" t="s">
+        <v>17</v>
       </c>
       <c r="K9">
-        <v>-77.00648336</v>
+        <v>-77.006483360000004</v>
       </c>
       <c r="L9">
-        <v>37.5750528</v>
+        <v>37.575052800000002</v>
       </c>
       <c r="M9">
         <v>147011.75</v>
@@ -795,15 +885,15 @@
         <v>73505.88</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>579513009</v>
       </c>
-      <c r="B10" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C10" t="str">
-        <v>H</v>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -811,8 +901,8 @@
       <c r="E10">
         <v>1475</v>
       </c>
-      <c r="F10" t="str">
-        <v>S</v>
+      <c r="F10" t="s">
+        <v>19</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -823,14 +913,14 @@
       <c r="I10">
         <v>11.83</v>
       </c>
-      <c r="J10" t="str">
-        <v/>
+      <c r="J10" t="s">
+        <v>17</v>
       </c>
       <c r="K10">
-        <v>-77.01173812150957</v>
+        <v>-77.011738121509566</v>
       </c>
       <c r="L10">
-        <v>37.57670648084898</v>
+        <v>37.576706480848983</v>
       </c>
       <c r="M10">
         <v>231250.46</v>
@@ -839,15 +929,15 @@
         <v>115625.23</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>579513010</v>
       </c>
-      <c r="B11" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C11" t="str">
-        <v>W</v>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -855,8 +945,8 @@
       <c r="E11">
         <v>2738</v>
       </c>
-      <c r="F11" t="str">
-        <v>C</v>
+      <c r="F11" t="s">
+        <v>16</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -867,14 +957,14 @@
       <c r="I11">
         <v>12.07</v>
       </c>
-      <c r="J11" t="str">
-        <v/>
+      <c r="J11" t="s">
+        <v>17</v>
       </c>
       <c r="K11">
-        <v>-77.00576441</v>
+        <v>-77.005764409999998</v>
       </c>
       <c r="L11">
-        <v>37.57842078</v>
+        <v>37.578420780000002</v>
       </c>
       <c r="M11">
         <v>187039.01</v>
@@ -883,15 +973,15 @@
         <v>93519.5</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>579513011</v>
       </c>
-      <c r="B12" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C12" t="str">
-        <v>H</v>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -899,8 +989,8 @@
       <c r="E12">
         <v>1890</v>
       </c>
-      <c r="F12" t="str">
-        <v>P</v>
+      <c r="F12" t="s">
+        <v>20</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -911,14 +1001,14 @@
       <c r="I12">
         <v>10.88</v>
       </c>
-      <c r="J12" t="str">
-        <v/>
+      <c r="J12" t="s">
+        <v>17</v>
       </c>
       <c r="K12">
-        <v>-77.00185149908067</v>
+        <v>-77.001851499080672</v>
       </c>
       <c r="L12">
-        <v>37.57463384421405</v>
+        <v>37.574633844214048</v>
       </c>
       <c r="M12">
         <v>141073.85</v>
@@ -927,15 +1017,15 @@
         <v>70536.92</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>579513012</v>
       </c>
-      <c r="B13" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C13" t="str">
-        <v>W</v>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>18</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -943,8 +1033,8 @@
       <c r="E13">
         <v>1616.7</v>
       </c>
-      <c r="F13" t="str">
-        <v>S</v>
+      <c r="F13" t="s">
+        <v>19</v>
       </c>
       <c r="G13">
         <v>0.5</v>
@@ -953,33 +1043,33 @@
         <v>1980</v>
       </c>
       <c r="I13">
-        <v>7.5876</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
+        <v>7.5876000000000001</v>
+      </c>
+      <c r="J13" t="s">
+        <v>17</v>
       </c>
       <c r="K13">
-        <v>-77.00090556</v>
+        <v>-77.000905560000007</v>
       </c>
       <c r="L13">
-        <v>37.57230673</v>
+        <v>37.572306730000001</v>
       </c>
       <c r="M13">
-        <v>140230.95</v>
+        <v>140230.95000000001</v>
       </c>
       <c r="N13">
         <v>70115.47</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>579513013</v>
       </c>
-      <c r="B14" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C14" t="str">
-        <v>M</v>
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s">
+        <v>24</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -987,8 +1077,8 @@
       <c r="E14">
         <v>2672</v>
       </c>
-      <c r="F14" t="str">
-        <v>S</v>
+      <c r="F14" t="s">
+        <v>19</v>
       </c>
       <c r="G14">
         <v>0.5</v>
@@ -999,14 +1089,14 @@
       <c r="I14">
         <v>10.07</v>
       </c>
-      <c r="J14" t="str">
-        <v/>
+      <c r="J14" t="s">
+        <v>17</v>
       </c>
       <c r="K14">
-        <v>-77.00663655996324</v>
+        <v>-77.006636559963241</v>
       </c>
       <c r="L14">
-        <v>37.57347526834404</v>
+        <v>37.573475268344041</v>
       </c>
       <c r="M14">
         <v>173299.91</v>
@@ -1015,15 +1105,15 @@
         <v>86649.95</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>579513014</v>
       </c>
-      <c r="B15" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C15" t="str">
-        <v>M</v>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>24</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1031,8 +1121,8 @@
       <c r="E15">
         <v>3756.5</v>
       </c>
-      <c r="F15" t="str">
-        <v>S</v>
+      <c r="F15" t="s">
+        <v>19</v>
       </c>
       <c r="G15">
         <v>0.5</v>
@@ -1041,33 +1131,33 @@
         <v>1980</v>
       </c>
       <c r="I15">
-        <v>6.3471</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
+        <v>6.3471000000000002</v>
+      </c>
+      <c r="J15" t="s">
+        <v>17</v>
       </c>
       <c r="K15">
-        <v>-76.99735141</v>
+        <v>-76.997351409999993</v>
       </c>
       <c r="L15">
-        <v>37.57419176</v>
+        <v>37.574191759999998</v>
       </c>
       <c r="M15">
-        <v>263287.4</v>
+        <v>263287.40000000002</v>
       </c>
       <c r="N15">
-        <v>131643.7</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>131643.70000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>579513015</v>
       </c>
-      <c r="B16" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C16" t="str">
-        <v>H</v>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1075,8 +1165,8 @@
       <c r="E16">
         <v>3200</v>
       </c>
-      <c r="F16" t="str">
-        <v>P</v>
+      <c r="F16" t="s">
+        <v>20</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1087,31 +1177,31 @@
       <c r="I16">
         <v>11.06</v>
       </c>
-      <c r="J16" t="str">
-        <v/>
+      <c r="J16" t="s">
+        <v>17</v>
       </c>
       <c r="K16">
-        <v>-77.00848652</v>
+        <v>-77.008486520000005</v>
       </c>
       <c r="L16">
-        <v>37.57710274</v>
+        <v>37.577102740000001</v>
       </c>
       <c r="M16">
-        <v>322456.9</v>
+        <v>322456.90000000002</v>
       </c>
       <c r="N16">
-        <v>161228.45</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>161228.45000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>579513016</v>
       </c>
-      <c r="B17" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C17" t="str">
-        <v>W</v>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>18</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -1119,23 +1209,23 @@
       <c r="E17">
         <v>3086.7</v>
       </c>
-      <c r="F17" t="str">
-        <v>P</v>
+      <c r="F17" t="s">
+        <v>20</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17">
         <v>1980</v>
       </c>
       <c r="I17">
-        <v>4.9322</v>
-      </c>
-      <c r="J17" t="str">
-        <v/>
+        <v>4.9321999999999999</v>
+      </c>
+      <c r="J17" t="s">
+        <v>17</v>
       </c>
       <c r="K17">
-        <v>-77.00017780065536</v>
+        <v>-77.000177800655365</v>
       </c>
       <c r="L17">
         <v>37.569535975562985</v>
@@ -1147,15 +1237,15 @@
         <v>127796.59</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>579513017</v>
       </c>
-      <c r="B18" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C18" t="str">
-        <v>W</v>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" t="s">
+        <v>18</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1163,8 +1253,8 @@
       <c r="E18">
         <v>3814</v>
       </c>
-      <c r="F18" t="str">
-        <v>S</v>
+      <c r="F18" t="s">
+        <v>19</v>
       </c>
       <c r="G18">
         <v>0.5</v>
@@ -1175,14 +1265,14 @@
       <c r="I18">
         <v>10.44</v>
       </c>
-      <c r="J18" t="str">
-        <v/>
+      <c r="J18" t="s">
+        <v>17</v>
       </c>
       <c r="K18">
-        <v>-77.0073698</v>
+        <v>-77.007369800000006</v>
       </c>
       <c r="L18">
-        <v>37.57631952</v>
+        <v>37.576319519999998</v>
       </c>
       <c r="M18">
         <v>234919.03</v>
@@ -1191,15 +1281,15 @@
         <v>117459.51</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>579513018</v>
       </c>
-      <c r="B19" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C19" t="str">
-        <v>W</v>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s">
+        <v>18</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -1207,8 +1297,8 @@
       <c r="E19">
         <v>2422</v>
       </c>
-      <c r="F19" t="str">
-        <v>S</v>
+      <c r="F19" t="s">
+        <v>19</v>
       </c>
       <c r="G19">
         <v>0.5</v>
@@ -1219,14 +1309,14 @@
       <c r="I19">
         <v>8.25</v>
       </c>
-      <c r="J19" t="str">
-        <v/>
+      <c r="J19" t="s">
+        <v>17</v>
       </c>
       <c r="K19">
-        <v>-76.99326617</v>
+        <v>-76.993266169999998</v>
       </c>
       <c r="L19">
-        <v>37.57446955</v>
+        <v>37.574469550000003</v>
       </c>
       <c r="M19">
         <v>260503.11</v>
@@ -1235,15 +1325,15 @@
         <v>130251.55</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>579513019</v>
       </c>
-      <c r="B20" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C20" t="str">
-        <v>W</v>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
+        <v>18</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1251,8 +1341,8 @@
       <c r="E20">
         <v>1602</v>
       </c>
-      <c r="F20" t="str">
-        <v>P</v>
+      <c r="F20" t="s">
+        <v>20</v>
       </c>
       <c r="G20">
         <v>3.5</v>
@@ -1261,33 +1351,33 @@
         <v>1980</v>
       </c>
       <c r="I20">
-        <v>4.5299</v>
-      </c>
-      <c r="J20" t="str">
-        <v/>
+        <v>4.5298999999999996</v>
+      </c>
+      <c r="J20" t="s">
+        <v>17</v>
       </c>
       <c r="K20">
-        <v>-76.9995895</v>
+        <v>-76.999589499999999</v>
       </c>
       <c r="L20">
-        <v>37.571748</v>
+        <v>37.571747999999999</v>
       </c>
       <c r="M20">
         <v>139255.01</v>
       </c>
       <c r="N20">
-        <v>69627.51</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>69627.509999999995</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>579513020</v>
       </c>
-      <c r="B21" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C21" t="str">
-        <v>H</v>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" t="s">
+        <v>15</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1295,8 +1385,8 @@
       <c r="E21">
         <v>1524.9</v>
       </c>
-      <c r="F21" t="str">
-        <v>P</v>
+      <c r="F21" t="s">
+        <v>20</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1307,14 +1397,14 @@
       <c r="I21">
         <v>12.0861</v>
       </c>
-      <c r="J21" t="str">
-        <v/>
+      <c r="J21" t="s">
+        <v>17</v>
       </c>
       <c r="K21">
-        <v>-77.00627714395523</v>
+        <v>-77.006277143955231</v>
       </c>
       <c r="L21">
-        <v>37.57433835593385</v>
+        <v>37.574338355933847</v>
       </c>
       <c r="M21">
         <v>234068.41</v>
@@ -1323,15 +1413,15 @@
         <v>117034.21</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>579513021</v>
       </c>
-      <c r="B22" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C22" t="str">
-        <v>H</v>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
+        <v>15</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1339,8 +1429,8 @@
       <c r="E22">
         <v>1002</v>
       </c>
-      <c r="F22" t="str">
-        <v>P</v>
+      <c r="F22" t="s">
+        <v>20</v>
       </c>
       <c r="G22">
         <v>3</v>
@@ -1351,40 +1441,40 @@
       <c r="I22">
         <v>7.27</v>
       </c>
-      <c r="J22" t="str">
-        <v/>
+      <c r="J22" t="s">
+        <v>17</v>
       </c>
       <c r="K22">
-        <v>-77.00514793395998</v>
+        <v>-77.005147933959975</v>
       </c>
       <c r="L22">
-        <v>37.57250162550948</v>
+        <v>37.572501625509481</v>
       </c>
       <c r="M22">
         <v>151731.99</v>
       </c>
       <c r="N22">
-        <v>75865.99</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>75865.990000000005</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>579513022</v>
       </c>
-      <c r="B23" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C23" t="str">
-        <v>W</v>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" t="s">
+        <v>18</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23">
-        <v>2211.8</v>
-      </c>
-      <c r="F23" t="str">
-        <v>P</v>
+        <v>2211.8000000000002</v>
+      </c>
+      <c r="F23" t="s">
+        <v>20</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1395,14 +1485,14 @@
       <c r="I23">
         <v>10.7319</v>
       </c>
-      <c r="J23" t="str">
-        <v/>
+      <c r="J23" t="s">
+        <v>17</v>
       </c>
       <c r="K23">
-        <v>-77.01003760099412</v>
+        <v>-77.010037600994124</v>
       </c>
       <c r="L23">
-        <v>37.5787131633007</v>
+        <v>37.578713163300698</v>
       </c>
       <c r="M23">
         <v>175019.69</v>
@@ -1411,15 +1501,15 @@
         <v>87509.85</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>579513023</v>
       </c>
-      <c r="B24" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C24" t="str">
-        <v>H</v>
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" t="s">
+        <v>15</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1427,8 +1517,8 @@
       <c r="E24">
         <v>3854</v>
       </c>
-      <c r="F24" t="str">
-        <v>P</v>
+      <c r="F24" t="s">
+        <v>20</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -1437,16 +1527,16 @@
         <v>1980</v>
       </c>
       <c r="I24">
-        <v>9.79</v>
-      </c>
-      <c r="J24" t="str">
-        <v/>
+        <v>9.7899999999999991</v>
+      </c>
+      <c r="J24" t="s">
+        <v>17</v>
       </c>
       <c r="K24">
-        <v>-77.00658646</v>
+        <v>-77.006586459999994</v>
       </c>
       <c r="L24">
-        <v>37.57741962</v>
+        <v>37.577419620000001</v>
       </c>
       <c r="M24">
         <v>243600.88</v>
@@ -1455,15 +1545,15 @@
         <v>121800.44</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>579513024</v>
       </c>
-      <c r="B25" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C25" t="str">
-        <v>H</v>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1471,8 +1561,8 @@
       <c r="E25">
         <v>2194</v>
       </c>
-      <c r="F25" t="str">
-        <v>P</v>
+      <c r="F25" t="s">
+        <v>20</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -1483,11 +1573,11 @@
       <c r="I25">
         <v>10.38</v>
       </c>
-      <c r="J25" t="str">
-        <v/>
+      <c r="J25" t="s">
+        <v>17</v>
       </c>
       <c r="K25">
-        <v>-77.00383939</v>
+        <v>-77.003839389999996</v>
       </c>
       <c r="L25">
         <v>37.57942817</v>
@@ -1499,15 +1589,15 @@
         <v>96475.8</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>579513025</v>
       </c>
-      <c r="B26" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C26" t="str">
-        <v>W</v>
+      <c r="B26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" t="s">
+        <v>18</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1515,8 +1605,8 @@
       <c r="E26">
         <v>1920</v>
       </c>
-      <c r="F26" t="str">
-        <v>C</v>
+      <c r="F26" t="s">
+        <v>16</v>
       </c>
       <c r="G26">
         <v>1.5</v>
@@ -1527,11 +1617,11 @@
       <c r="I26">
         <v>8.67</v>
       </c>
-      <c r="J26" t="str">
-        <v/>
+      <c r="J26" t="s">
+        <v>17</v>
       </c>
       <c r="K26">
-        <v>-77.00597405433656</v>
+        <v>-77.005974054336562</v>
       </c>
       <c r="L26">
         <v>37.572814127981076</v>
@@ -1543,15 +1633,15 @@
         <v>83584.23</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>579513026</v>
       </c>
-      <c r="B27" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C27" t="str">
-        <v>W</v>
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" t="s">
+        <v>18</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1559,8 +1649,8 @@
       <c r="E27">
         <v>1788</v>
       </c>
-      <c r="F27" t="str">
-        <v>P</v>
+      <c r="F27" t="s">
+        <v>20</v>
       </c>
       <c r="G27">
         <v>0.5</v>
@@ -1571,14 +1661,14 @@
       <c r="I27">
         <v>2.82</v>
       </c>
-      <c r="J27" t="str">
-        <v/>
+      <c r="J27" t="s">
+        <v>17</v>
       </c>
       <c r="K27">
-        <v>-76.99260860681535</v>
+        <v>-76.992608606815352</v>
       </c>
       <c r="L27">
-        <v>37.57597521871485</v>
+        <v>37.575975218714852</v>
       </c>
       <c r="M27">
         <v>261843.66</v>
@@ -1587,15 +1677,15 @@
         <v>130921.83</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>579513027</v>
       </c>
-      <c r="B28" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C28" t="str">
-        <v>H</v>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -1603,8 +1693,8 @@
       <c r="E28">
         <v>1420.1</v>
       </c>
-      <c r="F28" t="str">
-        <v>C</v>
+      <c r="F28" t="s">
+        <v>16</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1615,14 +1705,14 @@
       <c r="I28">
         <v>10.9</v>
       </c>
-      <c r="J28" t="str">
-        <v/>
+      <c r="J28" t="s">
+        <v>17</v>
       </c>
       <c r="K28">
-        <v>-77.0076905</v>
+        <v>-77.007690499999995</v>
       </c>
       <c r="L28">
-        <v>37.5782755</v>
+        <v>37.578275499999997</v>
       </c>
       <c r="M28">
         <v>222042.43</v>
@@ -1631,15 +1721,15 @@
         <v>111021.22</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>579513028</v>
       </c>
-      <c r="B29" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C29" t="str">
-        <v>W</v>
+      <c r="B29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" t="s">
+        <v>18</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1647,8 +1737,8 @@
       <c r="E29">
         <v>1427</v>
       </c>
-      <c r="F29" t="str">
-        <v>S</v>
+      <c r="F29" t="s">
+        <v>19</v>
       </c>
       <c r="G29">
         <v>0.5</v>
@@ -1659,31 +1749,31 @@
       <c r="I29">
         <v>12.6</v>
       </c>
-      <c r="J29" t="str">
-        <v/>
+      <c r="J29" t="s">
+        <v>17</v>
       </c>
       <c r="K29">
-        <v>-77.01200198</v>
+        <v>-77.012001979999994</v>
       </c>
       <c r="L29">
         <v>37.57717306</v>
       </c>
       <c r="M29">
-        <v>166511.8</v>
+        <v>166511.79999999999</v>
       </c>
       <c r="N29">
-        <v>83255.9</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>83255.899999999994</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>579513029</v>
       </c>
-      <c r="B30" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C30" t="str">
-        <v>H</v>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>15</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1691,8 +1781,8 @@
       <c r="E30">
         <v>1859</v>
       </c>
-      <c r="F30" t="str">
-        <v>P</v>
+      <c r="F30" t="s">
+        <v>20</v>
       </c>
       <c r="G30">
         <v>2.5</v>
@@ -1703,14 +1793,14 @@
       <c r="I30">
         <v>7.56</v>
       </c>
-      <c r="J30" t="str">
-        <v/>
+      <c r="J30" t="s">
+        <v>17</v>
       </c>
       <c r="K30">
-        <v>-77.00543761253358</v>
+        <v>-77.005437612533584</v>
       </c>
       <c r="L30">
-        <v>37.57155560663291</v>
+        <v>37.571555606632913</v>
       </c>
       <c r="M30">
         <v>240843.43</v>
@@ -1719,15 +1809,15 @@
         <v>120421.71</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>579513030</v>
       </c>
-      <c r="B31" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C31" t="str">
-        <v>M</v>
+      <c r="B31" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" t="s">
+        <v>24</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -1735,8 +1825,8 @@
       <c r="E31">
         <v>1441.8</v>
       </c>
-      <c r="F31" t="str">
-        <v>C</v>
+      <c r="F31" t="s">
+        <v>16</v>
       </c>
       <c r="G31">
         <v>1.5</v>
@@ -1747,14 +1837,14 @@
       <c r="I31">
         <v>10.09</v>
       </c>
-      <c r="J31" t="str">
-        <v/>
+      <c r="J31" t="s">
+        <v>17</v>
       </c>
       <c r="K31">
         <v>-76.9935969</v>
       </c>
       <c r="L31">
-        <v>37.57455455</v>
+        <v>37.574554550000002</v>
       </c>
       <c r="M31">
         <v>224582.55</v>
@@ -1763,15 +1853,15 @@
         <v>112291.27</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>579513031</v>
       </c>
-      <c r="B32" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C32" t="str">
-        <v>M</v>
+      <c r="B32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" t="s">
+        <v>24</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -1779,8 +1869,8 @@
       <c r="E32">
         <v>3990.4</v>
       </c>
-      <c r="F32" t="str">
-        <v>S</v>
+      <c r="F32" t="s">
+        <v>19</v>
       </c>
       <c r="G32">
         <v>0.5</v>
@@ -1791,14 +1881,14 @@
       <c r="I32">
         <v>12.09</v>
       </c>
-      <c r="J32" t="str">
-        <v/>
+      <c r="J32" t="s">
+        <v>17</v>
       </c>
       <c r="K32">
-        <v>-77.0069873</v>
+        <v>-77.006987300000006</v>
       </c>
       <c r="L32">
-        <v>37.5758867</v>
+        <v>37.575886699999998</v>
       </c>
       <c r="M32">
         <v>255415.96</v>
@@ -1807,15 +1897,15 @@
         <v>127707.98</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>579513032</v>
       </c>
-      <c r="B33" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C33" t="str">
-        <v>H</v>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1823,8 +1913,8 @@
       <c r="E33">
         <v>2024</v>
       </c>
-      <c r="F33" t="str">
-        <v>P</v>
+      <c r="F33" t="s">
+        <v>20</v>
       </c>
       <c r="G33">
         <v>3</v>
@@ -1835,31 +1925,31 @@
       <c r="I33">
         <v>10.57</v>
       </c>
-      <c r="J33" t="str">
-        <v/>
+      <c r="J33" t="s">
+        <v>17</v>
       </c>
       <c r="K33">
-        <v>-77.00418167</v>
+        <v>-77.004181669999994</v>
       </c>
       <c r="L33">
-        <v>37.5748102</v>
+        <v>37.574810200000002</v>
       </c>
       <c r="M33">
         <v>168509.43</v>
       </c>
       <c r="N33">
-        <v>84254.72</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>84254.720000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>579513033</v>
       </c>
-      <c r="B34" t="str">
-        <v>RES3A</v>
-      </c>
-      <c r="C34" t="str">
-        <v>M</v>
+      <c r="B34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" t="s">
+        <v>24</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -1867,8 +1957,8 @@
       <c r="E34">
         <v>3170.7</v>
       </c>
-      <c r="F34" t="str">
-        <v>S</v>
+      <c r="F34" t="s">
+        <v>19</v>
       </c>
       <c r="G34">
         <v>4</v>
@@ -1877,16 +1967,16 @@
         <v>1980</v>
       </c>
       <c r="I34">
-        <v>6.3267</v>
-      </c>
-      <c r="J34" t="str">
-        <v/>
+        <v>6.3266999999999998</v>
+      </c>
+      <c r="J34" t="s">
+        <v>17</v>
       </c>
       <c r="K34">
-        <v>-76.99509499</v>
+        <v>-76.995094989999998</v>
       </c>
       <c r="L34">
-        <v>37.57444163</v>
+        <v>37.574441630000003</v>
       </c>
       <c r="M34">
         <v>290641</v>
@@ -1895,15 +1985,15 @@
         <v>145321</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>579534897</v>
       </c>
-      <c r="B35" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C35" t="str">
-        <v>H</v>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1911,8 +2001,8 @@
       <c r="E35">
         <v>1271</v>
       </c>
-      <c r="F35" t="str">
-        <v>P</v>
+      <c r="F35" t="s">
+        <v>20</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -1923,14 +2013,14 @@
       <c r="I35">
         <v>12.53</v>
       </c>
-      <c r="J35" t="str">
-        <v/>
+      <c r="J35" t="s">
+        <v>17</v>
       </c>
       <c r="K35">
-        <v>-76.99645896</v>
+        <v>-76.996458959999998</v>
       </c>
       <c r="L35">
-        <v>37.57720353</v>
+        <v>37.577203529999998</v>
       </c>
       <c r="M35">
         <v>169885.84</v>
@@ -1939,15 +2029,15 @@
         <v>84942.92</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>579534898</v>
       </c>
-      <c r="B36" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C36" t="str">
-        <v>W</v>
+      <c r="B36" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" t="s">
+        <v>18</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -1955,8 +2045,8 @@
       <c r="E36">
         <v>1595.2</v>
       </c>
-      <c r="F36" t="str">
-        <v>S</v>
+      <c r="F36" t="s">
+        <v>19</v>
       </c>
       <c r="G36">
         <v>0.5</v>
@@ -1967,31 +2057,31 @@
       <c r="I36">
         <v>6.96</v>
       </c>
-      <c r="J36" t="str">
-        <v/>
+      <c r="J36" t="s">
+        <v>17</v>
       </c>
       <c r="K36">
-        <v>-76.99778389</v>
+        <v>-76.997783889999994</v>
       </c>
       <c r="L36">
-        <v>37.57882271</v>
+        <v>37.578822709999997</v>
       </c>
       <c r="M36">
-        <v>138870.02</v>
+        <v>138870.01999999999</v>
       </c>
       <c r="N36">
-        <v>69435.01</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>69435.009999999995</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>579534899</v>
       </c>
-      <c r="B37" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C37" t="str">
-        <v>W</v>
+      <c r="B37" t="s">
+        <v>21</v>
+      </c>
+      <c r="C37" t="s">
+        <v>18</v>
       </c>
       <c r="D37">
         <v>2</v>
@@ -1999,8 +2089,8 @@
       <c r="E37">
         <v>2413</v>
       </c>
-      <c r="F37" t="str">
-        <v>S</v>
+      <c r="F37" t="s">
+        <v>19</v>
       </c>
       <c r="G37">
         <v>0.5</v>
@@ -2011,14 +2101,14 @@
       <c r="I37">
         <v>14.62</v>
       </c>
-      <c r="J37" t="str">
-        <v/>
+      <c r="J37" t="s">
+        <v>17</v>
       </c>
       <c r="K37">
-        <v>-76.99875561</v>
+        <v>-76.998755610000003</v>
       </c>
       <c r="L37">
-        <v>37.5774463</v>
+        <v>37.577446299999998</v>
       </c>
       <c r="M37">
         <v>311493.3</v>
@@ -2027,15 +2117,15 @@
         <v>155746.65</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>579534905</v>
       </c>
-      <c r="B38" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C38" t="str">
-        <v>W</v>
+      <c r="B38" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" t="s">
+        <v>18</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -2043,8 +2133,8 @@
       <c r="E38">
         <v>1375</v>
       </c>
-      <c r="F38" t="str">
-        <v>S</v>
+      <c r="F38" t="s">
+        <v>19</v>
       </c>
       <c r="G38">
         <v>0.5</v>
@@ -2053,13 +2143,13 @@
         <v>1980</v>
       </c>
       <c r="I38">
-        <v>9.72</v>
-      </c>
-      <c r="J38" t="str">
-        <v/>
+        <v>9.7200000000000006</v>
+      </c>
+      <c r="J38" t="s">
+        <v>17</v>
       </c>
       <c r="K38">
-        <v>-77.00260788202287</v>
+        <v>-77.002607882022872</v>
       </c>
       <c r="L38">
         <v>37.58002683078432</v>
@@ -2071,15 +2161,15 @@
         <v>70656.45</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>579534906</v>
       </c>
-      <c r="B39" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C39" t="str">
-        <v>M</v>
+      <c r="B39" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" t="s">
+        <v>24</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -2087,8 +2177,8 @@
       <c r="E39">
         <v>1956</v>
       </c>
-      <c r="F39" t="str">
-        <v>C</v>
+      <c r="F39" t="s">
+        <v>16</v>
       </c>
       <c r="G39">
         <v>2.5</v>
@@ -2099,40 +2189,40 @@
       <c r="I39">
         <v>10.15</v>
       </c>
-      <c r="J39" t="str">
-        <v/>
+      <c r="J39" t="s">
+        <v>17</v>
       </c>
       <c r="K39">
-        <v>-77.0025944709778</v>
+        <v>-77.002594470977797</v>
       </c>
       <c r="L39">
         <v>37.579399759391364</v>
       </c>
       <c r="M39">
-        <v>147409.95</v>
+        <v>147409.95000000001</v>
       </c>
       <c r="N39">
         <v>73704.98</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>579534907</v>
       </c>
-      <c r="B40" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C40" t="str">
-        <v>H</v>
+      <c r="B40" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" t="s">
+        <v>15</v>
       </c>
       <c r="D40">
         <v>1</v>
       </c>
       <c r="E40">
-        <v>1165.6</v>
-      </c>
-      <c r="F40" t="str">
-        <v>P</v>
+        <v>1165.5999999999999</v>
+      </c>
+      <c r="F40" t="s">
+        <v>20</v>
       </c>
       <c r="G40">
         <v>2</v>
@@ -2143,14 +2233,14 @@
       <c r="I40">
         <v>9.24</v>
       </c>
-      <c r="J40" t="str">
-        <v/>
+      <c r="J40" t="s">
+        <v>17</v>
       </c>
       <c r="K40">
-        <v>-77.00148096</v>
+        <v>-77.001480959999995</v>
       </c>
       <c r="L40">
-        <v>37.57914915</v>
+        <v>37.579149149999999</v>
       </c>
       <c r="M40">
         <v>190356.2</v>
@@ -2159,15 +2249,15 @@
         <v>95178.1</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>579536184</v>
       </c>
-      <c r="B41" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C41" t="str">
-        <v>M</v>
+      <c r="B41" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" t="s">
+        <v>24</v>
       </c>
       <c r="D41">
         <v>2</v>
@@ -2175,8 +2265,8 @@
       <c r="E41">
         <v>3858</v>
       </c>
-      <c r="F41" t="str">
-        <v>S</v>
+      <c r="F41" t="s">
+        <v>19</v>
       </c>
       <c r="G41">
         <v>0.5</v>
@@ -2187,11 +2277,11 @@
       <c r="I41">
         <v>6.3</v>
       </c>
-      <c r="J41" t="str">
-        <v/>
+      <c r="J41" t="s">
+        <v>17</v>
       </c>
       <c r="K41">
-        <v>-76.99329705</v>
+        <v>-76.993297049999995</v>
       </c>
       <c r="L41">
         <v>37.57617407</v>
@@ -2203,15 +2293,15 @@
         <v>200307.7</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>579536842</v>
       </c>
-      <c r="B42" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C42" t="str">
-        <v>W</v>
+      <c r="B42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C42" t="s">
+        <v>18</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -2219,8 +2309,8 @@
       <c r="E42">
         <v>1462</v>
       </c>
-      <c r="F42" t="str">
-        <v>C</v>
+      <c r="F42" t="s">
+        <v>16</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -2231,14 +2321,14 @@
       <c r="I42">
         <v>11.17</v>
       </c>
-      <c r="J42" t="str">
-        <v/>
+      <c r="J42" t="s">
+        <v>17</v>
       </c>
       <c r="K42">
-        <v>-77.00894862413408</v>
+        <v>-77.008948624134078</v>
       </c>
       <c r="L42">
-        <v>37.57993542748635</v>
+        <v>37.579935427486348</v>
       </c>
       <c r="M42">
         <v>87561.3</v>
@@ -2247,15 +2337,15 @@
         <v>43780.65</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>579536843</v>
       </c>
-      <c r="B43" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C43" t="str">
-        <v>M</v>
+      <c r="B43" t="s">
+        <v>21</v>
+      </c>
+      <c r="C43" t="s">
+        <v>24</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -2263,8 +2353,8 @@
       <c r="E43">
         <v>1202</v>
       </c>
-      <c r="F43" t="str">
-        <v>B</v>
+      <c r="F43" t="s">
+        <v>26</v>
       </c>
       <c r="G43">
         <v>2</v>
@@ -2273,16 +2363,16 @@
         <v>1980</v>
       </c>
       <c r="I43">
-        <v>10.0743</v>
-      </c>
-      <c r="J43" t="str">
-        <v/>
+        <v>10.074299999999999</v>
+      </c>
+      <c r="J43" t="s">
+        <v>17</v>
       </c>
       <c r="K43">
-        <v>-77.01079934835435</v>
+        <v>-77.010799348354354</v>
       </c>
       <c r="L43">
-        <v>37.58148926829097</v>
+        <v>37.581489268290973</v>
       </c>
       <c r="M43">
         <v>258203.36</v>
@@ -2291,15 +2381,15 @@
         <v>129101.68</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>579536844</v>
       </c>
-      <c r="B44" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C44" t="str">
-        <v>H</v>
+      <c r="B44" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" t="s">
+        <v>15</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -2307,8 +2397,8 @@
       <c r="E44">
         <v>2250</v>
       </c>
-      <c r="F44" t="str">
-        <v>P</v>
+      <c r="F44" t="s">
+        <v>20</v>
       </c>
       <c r="G44">
         <v>2</v>
@@ -2319,11 +2409,11 @@
       <c r="I44">
         <v>17.5</v>
       </c>
-      <c r="J44" t="str">
-        <v/>
+      <c r="J44" t="s">
+        <v>17</v>
       </c>
       <c r="K44">
-        <v>-77.00983911752702</v>
+        <v>-77.009839117527022</v>
       </c>
       <c r="L44">
         <v>37.582345886221525</v>
@@ -2335,15 +2425,15 @@
         <v>362092.02</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>579537054</v>
       </c>
-      <c r="B45" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C45" t="str">
-        <v>W</v>
+      <c r="B45" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" t="s">
+        <v>18</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -2351,8 +2441,8 @@
       <c r="E45">
         <v>1765</v>
       </c>
-      <c r="F45" t="str">
-        <v>S</v>
+      <c r="F45" t="s">
+        <v>19</v>
       </c>
       <c r="G45">
         <v>0.5</v>
@@ -2363,14 +2453,14 @@
       <c r="I45">
         <v>11.23</v>
       </c>
-      <c r="J45" t="str">
-        <v/>
+      <c r="J45" t="s">
+        <v>17</v>
       </c>
       <c r="K45">
-        <v>-77.007753</v>
+        <v>-77.007752999999994</v>
       </c>
       <c r="L45">
-        <v>37.580795</v>
+        <v>37.580795000000002</v>
       </c>
       <c r="M45">
         <v>149746.78</v>
@@ -2379,15 +2469,15 @@
         <v>74873.39</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>579537067</v>
       </c>
-      <c r="B46" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C46" t="str">
-        <v>W</v>
+      <c r="B46" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" t="s">
+        <v>18</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -2395,8 +2485,8 @@
       <c r="E46">
         <v>1576.6</v>
       </c>
-      <c r="F46" t="str">
-        <v>S</v>
+      <c r="F46" t="s">
+        <v>19</v>
       </c>
       <c r="G46">
         <v>0.5</v>
@@ -2407,14 +2497,14 @@
       <c r="I46">
         <v>10.06</v>
       </c>
-      <c r="J46" t="str">
-        <v/>
+      <c r="J46" t="s">
+        <v>17</v>
       </c>
       <c r="K46">
-        <v>-77.011919</v>
+        <v>-77.011919000000006</v>
       </c>
       <c r="L46">
-        <v>37.580516</v>
+        <v>37.580516000000003</v>
       </c>
       <c r="M46">
         <v>137875.75</v>
@@ -2423,15 +2513,15 @@
         <v>68937.87</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>10000001</v>
       </c>
-      <c r="B47" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C47" t="str">
-        <v>M</v>
+      <c r="B47" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" t="s">
+        <v>24</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -2439,8 +2529,8 @@
       <c r="E47">
         <v>1019</v>
       </c>
-      <c r="F47" t="str">
-        <v>C</v>
+      <c r="F47" t="s">
+        <v>16</v>
       </c>
       <c r="G47">
         <v>4</v>
@@ -2451,11 +2541,11 @@
       <c r="I47">
         <v>11</v>
       </c>
-      <c r="J47" t="str">
-        <v/>
+      <c r="J47" t="s">
+        <v>17</v>
       </c>
       <c r="K47">
-        <v>-76.9996950030327</v>
+        <v>-76.999695003032699</v>
       </c>
       <c r="L47">
         <v>37.573396612081154</v>
@@ -2467,15 +2557,15 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>10000002</v>
       </c>
-      <c r="B48" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C48" t="str">
-        <v>H</v>
+      <c r="B48" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" t="s">
+        <v>15</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -2483,8 +2573,8 @@
       <c r="E48">
         <v>1362</v>
       </c>
-      <c r="F48" t="str">
-        <v>P</v>
+      <c r="F48" t="s">
+        <v>20</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -2493,16 +2583,16 @@
         <v>1980</v>
       </c>
       <c r="I48">
-        <v>9.47</v>
-      </c>
-      <c r="J48" t="str">
-        <v/>
+        <v>9.4700000000000006</v>
+      </c>
+      <c r="J48" t="s">
+        <v>17</v>
       </c>
       <c r="K48">
-        <v>-77.00350373983385</v>
+        <v>-77.003503739833846</v>
       </c>
       <c r="L48">
-        <v>37.57872804315927</v>
+        <v>37.578728043159273</v>
       </c>
       <c r="M48">
         <v>207278</v>
@@ -2511,15 +2601,15 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>10000003</v>
       </c>
-      <c r="B49" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C49" t="str">
-        <v>H</v>
+      <c r="B49" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" t="s">
+        <v>15</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -2527,8 +2617,8 @@
       <c r="E49">
         <v>1366</v>
       </c>
-      <c r="F49" t="str">
-        <v>P</v>
+      <c r="F49" t="s">
+        <v>20</v>
       </c>
       <c r="G49">
         <v>3</v>
@@ -2539,14 +2629,14 @@
       <c r="I49">
         <v>16</v>
       </c>
-      <c r="J49" t="str">
-        <v/>
+      <c r="J49" t="s">
+        <v>17</v>
       </c>
       <c r="K49">
-        <v>-77.00533568859102</v>
+        <v>-77.005335688591018</v>
       </c>
       <c r="L49">
-        <v>37.58050935331149</v>
+        <v>37.580509353311491</v>
       </c>
       <c r="M49">
         <v>207278</v>
@@ -2555,15 +2645,15 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>10000004</v>
       </c>
-      <c r="B50" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C50" t="str">
-        <v>W</v>
+      <c r="B50" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50" t="s">
+        <v>18</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -2571,8 +2661,8 @@
       <c r="E50">
         <v>3051</v>
       </c>
-      <c r="F50" t="str">
-        <v>S</v>
+      <c r="F50" t="s">
+        <v>19</v>
       </c>
       <c r="G50">
         <v>0.5</v>
@@ -2583,11 +2673,11 @@
       <c r="I50">
         <v>11.67</v>
       </c>
-      <c r="J50" t="str">
-        <v/>
+      <c r="J50" t="s">
+        <v>17</v>
       </c>
       <c r="K50">
-        <v>-77.0084991</v>
+        <v>-77.008499099999995</v>
       </c>
       <c r="L50">
         <v>37.5807492</v>
@@ -2599,15 +2689,15 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>10000005</v>
       </c>
-      <c r="B51" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C51" t="str">
-        <v>W</v>
+      <c r="B51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51" t="s">
+        <v>18</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -2615,8 +2705,8 @@
       <c r="E51">
         <v>859</v>
       </c>
-      <c r="F51" t="str">
-        <v>S</v>
+      <c r="F51" t="s">
+        <v>19</v>
       </c>
       <c r="G51">
         <v>0.5</v>
@@ -2627,14 +2717,14 @@
       <c r="I51">
         <v>17.28</v>
       </c>
-      <c r="J51" t="str">
-        <v/>
+      <c r="J51" t="s">
+        <v>17</v>
       </c>
       <c r="K51">
-        <v>-77.00918197631837</v>
+        <v>-77.009181976318374</v>
       </c>
       <c r="L51">
-        <v>37.58238202125258</v>
+        <v>37.582382021252577</v>
       </c>
       <c r="M51">
         <v>178578</v>
@@ -2643,15 +2733,15 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>10000006</v>
       </c>
-      <c r="B52" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C52" t="str">
-        <v>H</v>
+      <c r="B52" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52" t="s">
+        <v>15</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2659,8 +2749,8 @@
       <c r="E52">
         <v>952</v>
       </c>
-      <c r="F52" t="str">
-        <v>P</v>
+      <c r="F52" t="s">
+        <v>20</v>
       </c>
       <c r="G52">
         <v>3</v>
@@ -2671,14 +2761,14 @@
       <c r="I52">
         <v>12.05</v>
       </c>
-      <c r="J52" t="str">
-        <v/>
+      <c r="J52" t="s">
+        <v>17</v>
       </c>
       <c r="K52">
-        <v>-77.01248914003374</v>
+        <v>-77.012489140033736</v>
       </c>
       <c r="L52">
-        <v>37.57893210949088</v>
+        <v>37.578932109490879</v>
       </c>
       <c r="M52">
         <v>207278</v>
@@ -2687,15 +2777,15 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>10000007</v>
       </c>
-      <c r="B53" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C53" t="str">
-        <v>W</v>
+      <c r="B53" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53" t="s">
+        <v>18</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2703,8 +2793,8 @@
       <c r="E53">
         <v>1369</v>
       </c>
-      <c r="F53" t="str">
-        <v>P</v>
+      <c r="F53" t="s">
+        <v>20</v>
       </c>
       <c r="G53">
         <v>2</v>
@@ -2715,14 +2805,14 @@
       <c r="I53">
         <v>12.13</v>
       </c>
-      <c r="J53" t="str">
-        <v/>
+      <c r="J53" t="s">
+        <v>17</v>
       </c>
       <c r="K53">
-        <v>-77.01335281133653</v>
+        <v>-77.013352811336532</v>
       </c>
       <c r="L53">
-        <v>37.57800955516556</v>
+        <v>37.578009555165558</v>
       </c>
       <c r="M53">
         <v>178578</v>
@@ -2731,15 +2821,15 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>10000008</v>
       </c>
-      <c r="B54" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C54" t="str">
-        <v>H</v>
+      <c r="B54" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" t="s">
+        <v>15</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2747,8 +2837,8 @@
       <c r="E54">
         <v>2752</v>
       </c>
-      <c r="F54" t="str">
-        <v>P</v>
+      <c r="F54" t="s">
+        <v>20</v>
       </c>
       <c r="G54">
         <v>2.5</v>
@@ -2759,14 +2849,14 @@
       <c r="I54">
         <v>13</v>
       </c>
-      <c r="J54" t="str">
-        <v/>
+      <c r="J54" t="s">
+        <v>17</v>
       </c>
       <c r="K54">
-        <v>-77.0009091</v>
+        <v>-77.000909100000001</v>
       </c>
       <c r="L54">
-        <v>35.5741653</v>
+        <v>35.574165299999997</v>
       </c>
       <c r="M54">
         <v>207278</v>
@@ -2775,15 +2865,15 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>10000009</v>
       </c>
-      <c r="B55" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C55" t="str">
-        <v>H</v>
+      <c r="B55" t="s">
+        <v>14</v>
+      </c>
+      <c r="C55" t="s">
+        <v>15</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2791,8 +2881,8 @@
       <c r="E55">
         <v>1058</v>
       </c>
-      <c r="F55" t="str">
-        <v>P</v>
+      <c r="F55" t="s">
+        <v>20</v>
       </c>
       <c r="G55">
         <v>0.5</v>
@@ -2803,14 +2893,14 @@
       <c r="I55">
         <v>9</v>
       </c>
-      <c r="J55" t="str">
-        <v/>
+      <c r="J55" t="s">
+        <v>17</v>
       </c>
       <c r="K55">
-        <v>-76.9992743</v>
+        <v>-76.999274299999996</v>
       </c>
       <c r="L55">
-        <v>37.5698896</v>
+        <v>37.569889600000003</v>
       </c>
       <c r="M55">
         <v>207278</v>
@@ -2819,15 +2909,15 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>10000010</v>
       </c>
-      <c r="B56" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C56" t="str">
-        <v>H</v>
+      <c r="B56" t="s">
+        <v>14</v>
+      </c>
+      <c r="C56" t="s">
+        <v>15</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2835,8 +2925,8 @@
       <c r="E56">
         <v>1339</v>
       </c>
-      <c r="F56" t="str">
-        <v>P</v>
+      <c r="F56" t="s">
+        <v>20</v>
       </c>
       <c r="G56">
         <v>0.5</v>
@@ -2847,14 +2937,14 @@
       <c r="I56">
         <v>9</v>
       </c>
-      <c r="J56" t="str">
-        <v/>
+      <c r="J56" t="s">
+        <v>17</v>
       </c>
       <c r="K56">
-        <v>-76.9990958</v>
+        <v>-76.999095800000006</v>
       </c>
       <c r="L56">
-        <v>37.5695597</v>
+        <v>37.569559699999999</v>
       </c>
       <c r="M56">
         <v>207278</v>
@@ -2863,15 +2953,15 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>10000011</v>
       </c>
-      <c r="B57" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C57" t="str">
-        <v>W</v>
+      <c r="B57" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57" t="s">
+        <v>18</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -2879,8 +2969,8 @@
       <c r="E57">
         <v>1594</v>
       </c>
-      <c r="F57" t="str">
-        <v>S</v>
+      <c r="F57" t="s">
+        <v>19</v>
       </c>
       <c r="G57">
         <v>0.5</v>
@@ -2891,14 +2981,14 @@
       <c r="I57">
         <v>7.98</v>
       </c>
-      <c r="J57" t="str">
-        <v/>
+      <c r="J57" t="s">
+        <v>17</v>
       </c>
       <c r="K57">
-        <v>-76.9913079</v>
+        <v>-76.991307899999995</v>
       </c>
       <c r="L57">
-        <v>37.5748534</v>
+        <v>37.574853400000002</v>
       </c>
       <c r="M57">
         <v>270574</v>
@@ -2907,15 +2997,15 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>10000012</v>
       </c>
-      <c r="B58" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C58" t="str">
-        <v>W</v>
+      <c r="B58" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58" t="s">
+        <v>18</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -2923,8 +3013,8 @@
       <c r="E58">
         <v>1567</v>
       </c>
-      <c r="F58" t="str">
-        <v>C</v>
+      <c r="F58" t="s">
+        <v>16</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -2935,14 +3025,14 @@
       <c r="I58">
         <v>12.22</v>
       </c>
-      <c r="J58" t="str">
-        <v/>
+      <c r="J58" t="s">
+        <v>17</v>
       </c>
       <c r="K58">
-        <v>-77.0041718</v>
+        <v>-77.004171799999995</v>
       </c>
       <c r="L58">
-        <v>37.5751793</v>
+        <v>37.575179300000002</v>
       </c>
       <c r="M58">
         <v>270574</v>
@@ -2951,15 +3041,15 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>10000013</v>
       </c>
-      <c r="B59" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C59" t="str">
-        <v>W</v>
+      <c r="B59" t="s">
+        <v>23</v>
+      </c>
+      <c r="C59" t="s">
+        <v>18</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2967,8 +3057,8 @@
       <c r="E59">
         <v>903</v>
       </c>
-      <c r="F59" t="str">
-        <v>P</v>
+      <c r="F59" t="s">
+        <v>20</v>
       </c>
       <c r="G59">
         <v>2</v>
@@ -2979,11 +3069,11 @@
       <c r="I59">
         <v>12</v>
       </c>
-      <c r="J59" t="str">
-        <v/>
+      <c r="J59" t="s">
+        <v>17</v>
       </c>
       <c r="K59">
-        <v>-77.00178712606431</v>
+        <v>-77.001787126064315</v>
       </c>
       <c r="L59">
         <v>37.575673358414306</v>
@@ -2995,15 +3085,15 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>10000014</v>
       </c>
-      <c r="B60" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C60" t="str">
-        <v>W</v>
+      <c r="B60" t="s">
+        <v>21</v>
+      </c>
+      <c r="C60" t="s">
+        <v>18</v>
       </c>
       <c r="D60">
         <v>2</v>
@@ -3011,8 +3101,8 @@
       <c r="E60">
         <v>1129</v>
       </c>
-      <c r="F60" t="str">
-        <v>S</v>
+      <c r="F60" t="s">
+        <v>19</v>
       </c>
       <c r="G60">
         <v>0.5</v>
@@ -3023,14 +3113,14 @@
       <c r="I60">
         <v>12.38</v>
       </c>
-      <c r="J60" t="str">
-        <v/>
+      <c r="J60" t="s">
+        <v>17</v>
       </c>
       <c r="K60">
-        <v>-77.0046609</v>
+        <v>-77.004660900000005</v>
       </c>
       <c r="L60">
-        <v>37.5781729</v>
+        <v>37.578172899999998</v>
       </c>
       <c r="M60">
         <v>270574</v>
@@ -3039,15 +3129,15 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>10000015</v>
       </c>
-      <c r="B61" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C61" t="str">
-        <v>H</v>
+      <c r="B61" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61" t="s">
+        <v>15</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -3055,8 +3145,8 @@
       <c r="E61">
         <v>1015</v>
       </c>
-      <c r="F61" t="str">
-        <v>P</v>
+      <c r="F61" t="s">
+        <v>20</v>
       </c>
       <c r="G61">
         <v>3</v>
@@ -3067,14 +3157,14 @@
       <c r="I61">
         <v>9.26</v>
       </c>
-      <c r="J61" t="str">
-        <v/>
+      <c r="J61" t="s">
+        <v>17</v>
       </c>
       <c r="K61">
-        <v>-77.0041428</v>
+        <v>-77.004142799999997</v>
       </c>
       <c r="L61">
-        <v>37.5789171</v>
+        <v>37.578917099999998</v>
       </c>
       <c r="M61">
         <v>207278</v>
@@ -3083,15 +3173,15 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>10001</v>
       </c>
-      <c r="B62" t="str">
-        <v>COM8</v>
-      </c>
-      <c r="C62" t="str">
-        <v>W</v>
+      <c r="B62" t="s">
+        <v>27</v>
+      </c>
+      <c r="C62" t="s">
+        <v>18</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -3099,23 +3189,23 @@
       <c r="E62">
         <v>8541</v>
       </c>
-      <c r="F62" t="str">
-        <v>S</v>
+      <c r="F62" t="s">
+        <v>19</v>
       </c>
       <c r="G62">
         <v>0.5</v>
       </c>
-      <c r="H62" t="str">
-        <v/>
+      <c r="H62" t="s">
+        <v>17</v>
       </c>
       <c r="I62">
         <v>10.01</v>
       </c>
-      <c r="J62" t="str">
-        <v/>
+      <c r="J62" t="s">
+        <v>17</v>
       </c>
       <c r="K62">
-        <v>-77.00088858604433</v>
+        <v>-77.000888586044326</v>
       </c>
       <c r="L62">
         <v>37.57556919506888</v>
@@ -3127,15 +3217,15 @@
         <v>171172</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>10002</v>
       </c>
-      <c r="B63" t="str">
-        <v>COM8</v>
-      </c>
-      <c r="C63" t="str">
-        <v>W</v>
+      <c r="B63" t="s">
+        <v>27</v>
+      </c>
+      <c r="C63" t="s">
+        <v>18</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -3143,26 +3233,26 @@
       <c r="E63">
         <v>4665</v>
       </c>
-      <c r="F63" t="str">
-        <v>S</v>
+      <c r="F63" t="s">
+        <v>19</v>
       </c>
       <c r="G63">
         <v>0.5</v>
       </c>
-      <c r="H63" t="str">
-        <v/>
+      <c r="H63" t="s">
+        <v>17</v>
       </c>
       <c r="I63">
         <v>12.48</v>
       </c>
-      <c r="J63" t="str">
-        <v/>
+      <c r="J63" t="s">
+        <v>17</v>
       </c>
       <c r="K63">
-        <v>-77.00206607580186</v>
+        <v>-77.002066075801864</v>
       </c>
       <c r="L63">
-        <v>37.57560958495481</v>
+        <v>37.575609584954812</v>
       </c>
       <c r="M63">
         <v>262820</v>
@@ -3171,15 +3261,15 @@
         <v>131410</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>10003</v>
       </c>
-      <c r="B64" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C64" t="str">
-        <v>W</v>
+      <c r="B64" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64" t="s">
+        <v>18</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -3187,23 +3277,23 @@
       <c r="E64">
         <v>559</v>
       </c>
-      <c r="F64" t="str">
-        <v>P</v>
+      <c r="F64" t="s">
+        <v>20</v>
       </c>
       <c r="G64">
         <v>0.5</v>
       </c>
-      <c r="H64" t="str">
-        <v/>
+      <c r="H64" t="s">
+        <v>17</v>
       </c>
       <c r="I64">
         <v>4.17</v>
       </c>
-      <c r="J64" t="str">
-        <v/>
+      <c r="J64" t="s">
+        <v>17</v>
       </c>
       <c r="K64">
-        <v>-76.99227333068849</v>
+        <v>-76.992273330688491</v>
       </c>
       <c r="L64">
         <v>37.575728628701675</v>
@@ -3215,15 +3305,15 @@
         <v>89583</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>10004</v>
       </c>
-      <c r="B65" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C65" t="str">
-        <v>W</v>
+      <c r="B65" t="s">
+        <v>23</v>
+      </c>
+      <c r="C65" t="s">
+        <v>18</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -3231,23 +3321,23 @@
       <c r="E65">
         <v>1473</v>
       </c>
-      <c r="F65" t="str">
-        <v>S</v>
+      <c r="F65" t="s">
+        <v>19</v>
       </c>
       <c r="G65">
         <v>0.5</v>
       </c>
-      <c r="H65" t="str">
-        <v/>
+      <c r="H65" t="s">
+        <v>17</v>
       </c>
       <c r="I65">
         <v>4.49</v>
       </c>
-      <c r="J65" t="str">
-        <v/>
+      <c r="J65" t="s">
+        <v>17</v>
       </c>
       <c r="K65">
-        <v>-76.99968695640565</v>
+        <v>-76.999686956405654</v>
       </c>
       <c r="L65">
         <v>37.57147269654066</v>
@@ -3259,15 +3349,15 @@
         <v>98945</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>10005</v>
       </c>
-      <c r="B66" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C66" t="str">
-        <v>W</v>
+      <c r="B66" t="s">
+        <v>23</v>
+      </c>
+      <c r="C66" t="s">
+        <v>18</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -3275,26 +3365,26 @@
       <c r="E66">
         <v>2105</v>
       </c>
-      <c r="F66" t="str">
-        <v>S</v>
+      <c r="F66" t="s">
+        <v>19</v>
       </c>
       <c r="G66">
         <v>0.5</v>
       </c>
-      <c r="H66" t="str">
-        <v/>
+      <c r="H66" t="s">
+        <v>17</v>
       </c>
       <c r="I66">
         <v>7.54</v>
       </c>
-      <c r="J66" t="str">
-        <v/>
+      <c r="J66" t="s">
+        <v>17</v>
       </c>
       <c r="K66">
-        <v>-76.99926853179933</v>
+        <v>-76.999268531799331</v>
       </c>
       <c r="L66">
-        <v>37.57352841442061</v>
+        <v>37.573528414420608</v>
       </c>
       <c r="M66">
         <v>210837</v>
@@ -3303,15 +3393,15 @@
         <v>105419</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>10007</v>
       </c>
-      <c r="B67" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C67" t="str">
-        <v>W</v>
+      <c r="B67" t="s">
+        <v>23</v>
+      </c>
+      <c r="C67" t="s">
+        <v>18</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -3319,26 +3409,26 @@
       <c r="E67">
         <v>930</v>
       </c>
-      <c r="F67" t="str">
-        <v>S</v>
+      <c r="F67" t="s">
+        <v>19</v>
       </c>
       <c r="G67">
         <v>0.5</v>
       </c>
-      <c r="H67" t="str">
-        <v/>
+      <c r="H67" t="s">
+        <v>17</v>
       </c>
       <c r="I67">
         <v>7.18</v>
       </c>
-      <c r="J67" t="str">
-        <v/>
+      <c r="J67" t="s">
+        <v>17</v>
       </c>
       <c r="K67">
         <v>-76.99765115976335</v>
       </c>
       <c r="L67">
-        <v>37.5741874226189</v>
+        <v>37.574187422618898</v>
       </c>
       <c r="M67">
         <v>186766</v>
@@ -3347,15 +3437,15 @@
         <v>93383</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>10008</v>
       </c>
-      <c r="B68" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C68" t="str">
-        <v>W</v>
+      <c r="B68" t="s">
+        <v>21</v>
+      </c>
+      <c r="C68" t="s">
+        <v>18</v>
       </c>
       <c r="D68">
         <v>2</v>
@@ -3363,26 +3453,26 @@
       <c r="E68">
         <v>763</v>
       </c>
-      <c r="F68" t="str">
-        <v>C</v>
+      <c r="F68" t="s">
+        <v>16</v>
       </c>
       <c r="G68">
         <v>1</v>
       </c>
-      <c r="H68" t="str">
-        <v/>
+      <c r="H68" t="s">
+        <v>17</v>
       </c>
       <c r="I68">
         <v>7</v>
       </c>
-      <c r="J68" t="str">
-        <v/>
+      <c r="J68" t="s">
+        <v>17</v>
       </c>
       <c r="K68">
-        <v>-76.99751973152162</v>
+        <v>-76.997519731521621</v>
       </c>
       <c r="L68">
-        <v>37.57437236903301</v>
+        <v>37.574372369033007</v>
       </c>
       <c r="M68">
         <v>198976</v>
@@ -3391,15 +3481,15 @@
         <v>99488</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>10009</v>
       </c>
-      <c r="B69" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C69" t="str">
-        <v>W</v>
+      <c r="B69" t="s">
+        <v>23</v>
+      </c>
+      <c r="C69" t="s">
+        <v>18</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -3407,26 +3497,26 @@
       <c r="E69">
         <v>2153</v>
       </c>
-      <c r="F69" t="str">
-        <v>S</v>
+      <c r="F69" t="s">
+        <v>19</v>
       </c>
       <c r="G69">
         <v>0.5</v>
       </c>
-      <c r="H69" t="str">
-        <v/>
+      <c r="H69" t="s">
+        <v>17</v>
       </c>
       <c r="I69">
         <v>6.02</v>
       </c>
-      <c r="J69" t="str">
-        <v/>
+      <c r="J69" t="s">
+        <v>17</v>
       </c>
       <c r="K69">
-        <v>-76.99764847755432</v>
+        <v>-76.997648477554321</v>
       </c>
       <c r="L69">
-        <v>37.57395358166769</v>
+        <v>37.573953581667688</v>
       </c>
       <c r="M69">
         <v>211820</v>
@@ -3435,15 +3525,15 @@
         <v>105910</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>10010</v>
       </c>
-      <c r="B70" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C70" t="str">
-        <v>W</v>
+      <c r="B70" t="s">
+        <v>23</v>
+      </c>
+      <c r="C70" t="s">
+        <v>18</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -3451,26 +3541,26 @@
       <c r="E70">
         <v>939</v>
       </c>
-      <c r="F70" t="str">
-        <v>S</v>
+      <c r="F70" t="s">
+        <v>19</v>
       </c>
       <c r="G70">
         <v>0.5</v>
       </c>
-      <c r="H70" t="str">
-        <v/>
+      <c r="H70" t="s">
+        <v>17</v>
       </c>
       <c r="I70">
         <v>6.03</v>
       </c>
-      <c r="J70" t="str">
-        <v/>
+      <c r="J70" t="s">
+        <v>17</v>
       </c>
       <c r="K70">
-        <v>-76.99496358633043</v>
+        <v>-76.994963586330428</v>
       </c>
       <c r="L70">
-        <v>37.57427458133105</v>
+        <v>37.574274581331053</v>
       </c>
       <c r="M70">
         <v>186951</v>
@@ -3479,15 +3569,15 @@
         <v>93476</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>10011</v>
       </c>
-      <c r="B71" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C71" t="str">
-        <v>W</v>
+      <c r="B71" t="s">
+        <v>23</v>
+      </c>
+      <c r="C71" t="s">
+        <v>18</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -3495,26 +3585,26 @@
       <c r="E71">
         <v>992</v>
       </c>
-      <c r="F71" t="str">
-        <v>S</v>
+      <c r="F71" t="s">
+        <v>19</v>
       </c>
       <c r="G71">
         <v>0.5</v>
       </c>
-      <c r="H71" t="str">
-        <v/>
+      <c r="H71" t="s">
+        <v>17</v>
       </c>
       <c r="I71">
         <v>4.33</v>
       </c>
-      <c r="J71" t="str">
-        <v/>
+      <c r="J71" t="s">
+        <v>17</v>
       </c>
       <c r="K71">
-        <v>-76.99283927679062</v>
+        <v>-76.992839276790619</v>
       </c>
       <c r="L71">
-        <v>37.57418317097179</v>
+        <v>37.574183170971793</v>
       </c>
       <c r="M71">
         <v>188036</v>
@@ -3523,15 +3613,15 @@
         <v>94018</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>10012</v>
       </c>
-      <c r="B72" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C72" t="str">
-        <v>W</v>
+      <c r="B72" t="s">
+        <v>23</v>
+      </c>
+      <c r="C72" t="s">
+        <v>18</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -3539,23 +3629,23 @@
       <c r="E72">
         <v>789</v>
       </c>
-      <c r="F72" t="str">
-        <v>S</v>
+      <c r="F72" t="s">
+        <v>19</v>
       </c>
       <c r="G72">
         <v>0.5</v>
       </c>
-      <c r="H72" t="str">
-        <v/>
+      <c r="H72" t="s">
+        <v>17</v>
       </c>
       <c r="I72">
         <v>5.9</v>
       </c>
-      <c r="J72" t="str">
-        <v/>
+      <c r="J72" t="s">
+        <v>17</v>
       </c>
       <c r="K72">
-        <v>-76.9930323958397</v>
+        <v>-76.993032395839705</v>
       </c>
       <c r="L72">
         <v>37.574317097739005</v>
@@ -3567,15 +3657,15 @@
         <v>91939</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>10013</v>
       </c>
-      <c r="B73" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C73" t="str">
-        <v>W</v>
+      <c r="B73" t="s">
+        <v>23</v>
+      </c>
+      <c r="C73" t="s">
+        <v>18</v>
       </c>
       <c r="D73">
         <v>2</v>
@@ -3583,23 +3673,23 @@
       <c r="E73">
         <v>1692</v>
       </c>
-      <c r="F73" t="str">
-        <v>S</v>
+      <c r="F73" t="s">
+        <v>19</v>
       </c>
       <c r="G73">
         <v>0.5</v>
       </c>
-      <c r="H73" t="str">
-        <v/>
+      <c r="H73" t="s">
+        <v>17</v>
       </c>
       <c r="I73">
         <v>7.8</v>
       </c>
-      <c r="J73" t="str">
-        <v/>
+      <c r="J73" t="s">
+        <v>17</v>
       </c>
       <c r="K73">
-        <v>-76.9941508769989</v>
+        <v>-76.994150876998901</v>
       </c>
       <c r="L73">
         <v>37.575654226382184</v>
@@ -3611,15 +3701,15 @@
         <v>118519</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>10014</v>
       </c>
-      <c r="B74" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C74" t="str">
-        <v>W</v>
+      <c r="B74" t="s">
+        <v>23</v>
+      </c>
+      <c r="C74" t="s">
+        <v>18</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -3627,26 +3717,26 @@
       <c r="E74">
         <v>675</v>
       </c>
-      <c r="F74" t="str">
-        <v>P</v>
+      <c r="F74" t="s">
+        <v>20</v>
       </c>
       <c r="G74">
         <v>0.5</v>
       </c>
-      <c r="H74" t="str">
-        <v/>
+      <c r="H74" t="s">
+        <v>17</v>
       </c>
       <c r="I74">
         <v>3</v>
       </c>
-      <c r="J74" t="str">
-        <v/>
+      <c r="J74" t="s">
+        <v>17</v>
       </c>
       <c r="K74">
-        <v>-76.99285805225374</v>
+        <v>-76.992858052253737</v>
       </c>
       <c r="L74">
-        <v>37.57646201901601</v>
+        <v>37.576462019016013</v>
       </c>
       <c r="M74">
         <v>181542</v>
@@ -3655,15 +3745,15 @@
         <v>90771</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>10015</v>
       </c>
-      <c r="B75" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C75" t="str">
-        <v>W</v>
+      <c r="B75" t="s">
+        <v>23</v>
+      </c>
+      <c r="C75" t="s">
+        <v>18</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3671,23 +3761,23 @@
       <c r="E75">
         <v>1141</v>
       </c>
-      <c r="F75" t="str">
-        <v>S</v>
+      <c r="F75" t="s">
+        <v>19</v>
       </c>
       <c r="G75">
         <v>0.5</v>
       </c>
-      <c r="H75" t="str">
-        <v/>
+      <c r="H75" t="s">
+        <v>17</v>
       </c>
       <c r="I75">
         <v>5.37</v>
       </c>
-      <c r="J75" t="str">
-        <v/>
+      <c r="J75" t="s">
+        <v>17</v>
       </c>
       <c r="K75">
-        <v>-76.99271857738496</v>
+        <v>-76.992718577384963</v>
       </c>
       <c r="L75">
         <v>37.57565635216379</v>
@@ -3699,15 +3789,15 @@
         <v>95545</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>10016</v>
       </c>
-      <c r="B76" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C76" t="str">
-        <v>W</v>
+      <c r="B76" t="s">
+        <v>23</v>
+      </c>
+      <c r="C76" t="s">
+        <v>18</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -3715,23 +3805,23 @@
       <c r="E76">
         <v>724</v>
       </c>
-      <c r="F76" t="str">
-        <v>P</v>
+      <c r="F76" t="s">
+        <v>20</v>
       </c>
       <c r="G76">
         <v>0.5</v>
       </c>
-      <c r="H76" t="str">
-        <v/>
+      <c r="H76" t="s">
+        <v>17</v>
       </c>
       <c r="I76">
-        <v>2.03</v>
-      </c>
-      <c r="J76" t="str">
-        <v/>
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="J76" t="s">
+        <v>17</v>
       </c>
       <c r="K76">
-        <v>-76.99269443750383</v>
+        <v>-76.992694437503829</v>
       </c>
       <c r="L76">
         <v>37.57607300418362</v>
@@ -3743,15 +3833,15 @@
         <v>91273</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>10017</v>
       </c>
-      <c r="B77" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C77" t="str">
-        <v>W</v>
+      <c r="B77" t="s">
+        <v>23</v>
+      </c>
+      <c r="C77" t="s">
+        <v>18</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3759,26 +3849,26 @@
       <c r="E77">
         <v>795</v>
       </c>
-      <c r="F77" t="str">
-        <v>P</v>
+      <c r="F77" t="s">
+        <v>20</v>
       </c>
       <c r="G77">
         <v>0.5</v>
       </c>
-      <c r="H77" t="str">
-        <v/>
+      <c r="H77" t="s">
+        <v>17</v>
       </c>
       <c r="I77">
         <v>4.46</v>
       </c>
-      <c r="J77" t="str">
-        <v/>
+      <c r="J77" t="s">
+        <v>17</v>
       </c>
       <c r="K77">
-        <v>-76.9921499490738</v>
+        <v>-76.992149949073806</v>
       </c>
       <c r="L77">
-        <v>37.57566272950818</v>
+        <v>37.575662729508181</v>
       </c>
       <c r="M77">
         <v>184001</v>
@@ -3787,15 +3877,15 @@
         <v>92001</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>10018</v>
       </c>
-      <c r="B78" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C78" t="str">
-        <v>W</v>
+      <c r="B78" t="s">
+        <v>23</v>
+      </c>
+      <c r="C78" t="s">
+        <v>18</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -3803,26 +3893,26 @@
       <c r="E78">
         <v>604</v>
       </c>
-      <c r="F78" t="str">
-        <v>P</v>
+      <c r="F78" t="s">
+        <v>20</v>
       </c>
       <c r="G78">
         <v>0.5</v>
       </c>
-      <c r="H78" t="str">
-        <v/>
+      <c r="H78" t="s">
+        <v>17</v>
       </c>
       <c r="I78">
         <v>4.46</v>
       </c>
-      <c r="J78" t="str">
-        <v/>
+      <c r="J78" t="s">
+        <v>17</v>
       </c>
       <c r="K78">
         <v>-76.99204266071321</v>
       </c>
       <c r="L78">
-        <v>37.57561171073767</v>
+        <v>37.575611710737668</v>
       </c>
       <c r="M78">
         <v>192461</v>
@@ -3831,15 +3921,15 @@
         <v>96231</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>10019</v>
       </c>
-      <c r="B79" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C79" t="str">
-        <v>W</v>
+      <c r="B79" t="s">
+        <v>23</v>
+      </c>
+      <c r="C79" t="s">
+        <v>18</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3847,23 +3937,23 @@
       <c r="E79">
         <v>444</v>
       </c>
-      <c r="F79" t="str">
-        <v>P</v>
+      <c r="F79" t="s">
+        <v>20</v>
       </c>
       <c r="G79">
         <v>0.5</v>
       </c>
-      <c r="H79" t="str">
-        <v/>
+      <c r="H79" t="s">
+        <v>17</v>
       </c>
       <c r="I79">
         <v>4</v>
       </c>
-      <c r="J79" t="str">
-        <v/>
+      <c r="J79" t="s">
+        <v>17</v>
       </c>
       <c r="K79">
-        <v>-76.99192464351655</v>
+        <v>-76.991924643516555</v>
       </c>
       <c r="L79">
         <v>37.57556919506888</v>
@@ -3875,15 +3965,15 @@
         <v>88405</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>10020</v>
       </c>
-      <c r="B80" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C80" t="str">
-        <v>W</v>
+      <c r="B80" t="s">
+        <v>23</v>
+      </c>
+      <c r="C80" t="s">
+        <v>18</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -3891,23 +3981,23 @@
       <c r="E80">
         <v>183</v>
       </c>
-      <c r="F80" t="str">
-        <v>P</v>
+      <c r="F80" t="s">
+        <v>20</v>
       </c>
       <c r="G80">
         <v>1.5</v>
       </c>
-      <c r="H80" t="str">
-        <v/>
+      <c r="H80" t="s">
+        <v>17</v>
       </c>
       <c r="I80">
         <v>2.59</v>
       </c>
-      <c r="J80" t="str">
-        <v/>
+      <c r="J80" t="s">
+        <v>17</v>
       </c>
       <c r="K80">
-        <v>-76.9917342066765</v>
+        <v>-76.991734206676497</v>
       </c>
       <c r="L80">
         <v>37.575473534725326</v>
@@ -3919,15 +4009,15 @@
         <v>85732</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>10021</v>
       </c>
-      <c r="B81" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C81" t="str">
-        <v>H</v>
+      <c r="B81" t="s">
+        <v>23</v>
+      </c>
+      <c r="C81" t="s">
+        <v>15</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -3935,26 +4025,26 @@
       <c r="E81">
         <v>298</v>
       </c>
-      <c r="F81" t="str">
-        <v>S</v>
+      <c r="F81" t="s">
+        <v>19</v>
       </c>
       <c r="G81">
         <v>0.5</v>
       </c>
-      <c r="H81" t="str">
-        <v/>
+      <c r="H81" t="s">
+        <v>17</v>
       </c>
       <c r="I81">
         <v>7.53</v>
       </c>
-      <c r="J81" t="str">
-        <v/>
+      <c r="J81" t="s">
+        <v>17</v>
       </c>
       <c r="K81">
-        <v>-76.99123263359071</v>
+        <v>-76.991232633590712</v>
       </c>
       <c r="L81">
-        <v>37.57469549270023</v>
+        <v>37.574695492700229</v>
       </c>
       <c r="M81">
         <v>173819</v>
@@ -3963,15 +4053,15 @@
         <v>86910</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>10022</v>
       </c>
-      <c r="B82" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C82" t="str">
-        <v>H</v>
+      <c r="B82" t="s">
+        <v>23</v>
+      </c>
+      <c r="C82" t="s">
+        <v>15</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -3979,26 +4069,26 @@
       <c r="E82">
         <v>717</v>
       </c>
-      <c r="F82" t="str">
-        <v>S</v>
+      <c r="F82" t="s">
+        <v>19</v>
       </c>
       <c r="G82">
         <v>0.5</v>
       </c>
-      <c r="H82" t="str">
-        <v/>
+      <c r="H82" t="s">
+        <v>17</v>
       </c>
       <c r="I82">
         <v>5.71</v>
       </c>
-      <c r="J82" t="str">
-        <v/>
+      <c r="J82" t="s">
+        <v>17</v>
       </c>
       <c r="K82">
-        <v>-76.99130505323411</v>
+        <v>-76.991305053234115</v>
       </c>
       <c r="L82">
-        <v>37.57449141475774</v>
+        <v>37.574491414757738</v>
       </c>
       <c r="M82">
         <v>182403</v>
@@ -4007,15 +4097,15 @@
         <v>91202</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>10023</v>
       </c>
-      <c r="B83" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C83" t="str">
-        <v>W</v>
+      <c r="B83" t="s">
+        <v>23</v>
+      </c>
+      <c r="C83" t="s">
+        <v>18</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -4023,26 +4113,26 @@
       <c r="E83">
         <v>389</v>
       </c>
-      <c r="F83" t="str">
-        <v>S</v>
+      <c r="F83" t="s">
+        <v>19</v>
       </c>
       <c r="G83">
         <v>0.5</v>
       </c>
-      <c r="H83" t="str">
-        <v/>
+      <c r="H83" t="s">
+        <v>17</v>
       </c>
       <c r="I83">
         <v>6.85</v>
       </c>
-      <c r="J83" t="str">
-        <v/>
+      <c r="J83" t="s">
+        <v>17</v>
       </c>
       <c r="K83">
-        <v>-76.99088126420976</v>
+        <v>-76.990881264209762</v>
       </c>
       <c r="L83">
-        <v>37.57469124108213</v>
+        <v>37.574691241082128</v>
       </c>
       <c r="M83">
         <v>175684</v>
@@ -4051,15 +4141,15 @@
         <v>87842</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>10024</v>
       </c>
-      <c r="B84" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C84" t="str">
-        <v>W</v>
+      <c r="B84" t="s">
+        <v>21</v>
+      </c>
+      <c r="C84" t="s">
+        <v>18</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -4067,23 +4157,23 @@
       <c r="E84">
         <v>1681</v>
       </c>
-      <c r="F84" t="str">
-        <v>C</v>
+      <c r="F84" t="s">
+        <v>16</v>
       </c>
       <c r="G84">
         <v>0.5</v>
       </c>
-      <c r="H84" t="str">
-        <v/>
+      <c r="H84" t="s">
+        <v>17</v>
       </c>
       <c r="I84">
         <v>6.7</v>
       </c>
-      <c r="J84" t="str">
-        <v/>
+      <c r="J84" t="s">
+        <v>17</v>
       </c>
       <c r="K84">
-        <v>-76.9907632470131</v>
+        <v>-76.990763247013106</v>
       </c>
       <c r="L84">
         <v>37.57479115404324</v>
@@ -4095,15 +4185,15 @@
         <v>101076</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>10025</v>
       </c>
-      <c r="B85" t="str">
-        <v>RES1</v>
-      </c>
-      <c r="C85" t="str">
-        <v>W</v>
+      <c r="B85" t="s">
+        <v>21</v>
+      </c>
+      <c r="C85" t="s">
+        <v>18</v>
       </c>
       <c r="D85">
         <v>2</v>
@@ -4111,26 +4201,26 @@
       <c r="E85">
         <v>1590</v>
       </c>
-      <c r="F85" t="str">
-        <v>C</v>
+      <c r="F85" t="s">
+        <v>16</v>
       </c>
       <c r="G85">
         <v>1</v>
       </c>
-      <c r="H85" t="str">
-        <v/>
+      <c r="H85" t="s">
+        <v>17</v>
       </c>
       <c r="I85">
         <v>13.94</v>
       </c>
-      <c r="J85" t="str">
-        <v/>
+      <c r="J85" t="s">
+        <v>17</v>
       </c>
       <c r="K85">
-        <v>-76.99618130922319</v>
+        <v>-76.996181309223189</v>
       </c>
       <c r="L85">
-        <v>37.5768999239915</v>
+        <v>37.576899923991498</v>
       </c>
       <c r="M85">
         <v>232859</v>
@@ -4139,15 +4229,15 @@
         <v>116430</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>10026</v>
       </c>
-      <c r="B86" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C86" t="str">
-        <v>W</v>
+      <c r="B86" t="s">
+        <v>23</v>
+      </c>
+      <c r="C86" t="s">
+        <v>18</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -4155,26 +4245,26 @@
       <c r="E86">
         <v>880</v>
       </c>
-      <c r="F86" t="str">
-        <v>S</v>
+      <c r="F86" t="s">
+        <v>19</v>
       </c>
       <c r="G86">
         <v>0.5</v>
       </c>
-      <c r="H86" t="str">
-        <v/>
+      <c r="H86" t="s">
+        <v>17</v>
       </c>
       <c r="I86">
         <v>12.44</v>
       </c>
-      <c r="J86" t="str">
-        <v/>
+      <c r="J86" t="s">
+        <v>17</v>
       </c>
       <c r="K86">
-        <v>-76.99625372886658</v>
+        <v>-76.996253728866577</v>
       </c>
       <c r="L86">
-        <v>37.57718902489411</v>
+        <v>37.577189024894111</v>
       </c>
       <c r="M86">
         <v>185742</v>
@@ -4183,15 +4273,15 @@
         <v>92871</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>10027</v>
       </c>
-      <c r="B87" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C87" t="str">
-        <v>W</v>
+      <c r="B87" t="s">
+        <v>23</v>
+      </c>
+      <c r="C87" t="s">
+        <v>18</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -4199,26 +4289,26 @@
       <c r="E87">
         <v>679</v>
       </c>
-      <c r="F87" t="str">
-        <v>S</v>
+      <c r="F87" t="s">
+        <v>19</v>
       </c>
       <c r="G87">
         <v>0.5</v>
       </c>
-      <c r="H87" t="str">
-        <v/>
+      <c r="H87" t="s">
+        <v>17</v>
       </c>
       <c r="I87">
         <v>12.54</v>
       </c>
-      <c r="J87" t="str">
-        <v/>
+      <c r="J87" t="s">
+        <v>17</v>
       </c>
       <c r="K87">
-        <v>-76.99616253376009</v>
+        <v>-76.996162533760085</v>
       </c>
       <c r="L87">
-        <v>37.57725492273686</v>
+        <v>37.577254922736863</v>
       </c>
       <c r="M87">
         <v>181624</v>
@@ -4227,15 +4317,15 @@
         <v>90812</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>10028</v>
       </c>
-      <c r="B88" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C88" t="str">
-        <v>W</v>
+      <c r="B88" t="s">
+        <v>23</v>
+      </c>
+      <c r="C88" t="s">
+        <v>18</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -4243,23 +4333,23 @@
       <c r="E88">
         <v>457</v>
       </c>
-      <c r="F88" t="str">
-        <v>S</v>
+      <c r="F88" t="s">
+        <v>19</v>
       </c>
       <c r="G88">
         <v>0.5</v>
       </c>
-      <c r="H88" t="str">
-        <v/>
+      <c r="H88" t="s">
+        <v>17</v>
       </c>
       <c r="I88">
         <v>12.24</v>
       </c>
-      <c r="J88" t="str">
-        <v/>
+      <c r="J88" t="s">
+        <v>17</v>
       </c>
       <c r="K88">
-        <v>-76.99661850929262</v>
+        <v>-76.996618509292617</v>
       </c>
       <c r="L88">
         <v>37.577346329325465</v>
@@ -4271,15 +4361,15 @@
         <v>88539</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>10029</v>
       </c>
-      <c r="B89" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C89" t="str">
-        <v>W</v>
+      <c r="B89" t="s">
+        <v>23</v>
+      </c>
+      <c r="C89" t="s">
+        <v>18</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -4287,23 +4377,23 @@
       <c r="E89">
         <v>354</v>
       </c>
-      <c r="F89" t="str">
-        <v>S</v>
+      <c r="F89" t="s">
+        <v>19</v>
       </c>
       <c r="G89">
         <v>0.5</v>
       </c>
-      <c r="H89" t="str">
-        <v/>
+      <c r="H89" t="s">
+        <v>17</v>
       </c>
       <c r="I89">
         <v>12.5</v>
       </c>
-      <c r="J89" t="str">
-        <v/>
+      <c r="J89" t="s">
+        <v>17</v>
       </c>
       <c r="K89">
-        <v>-76.99673384428026</v>
+        <v>-76.996733844280257</v>
       </c>
       <c r="L89">
         <v>37.577371838120854</v>
@@ -4315,15 +4405,15 @@
         <v>87484</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>10030</v>
       </c>
-      <c r="B90" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C90" t="str">
-        <v>W</v>
+      <c r="B90" t="s">
+        <v>23</v>
+      </c>
+      <c r="C90" t="s">
+        <v>18</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -4331,20 +4421,20 @@
       <c r="E90">
         <v>814</v>
       </c>
-      <c r="F90" t="str">
-        <v>S</v>
+      <c r="F90" t="s">
+        <v>19</v>
       </c>
       <c r="G90">
         <v>0.5</v>
       </c>
-      <c r="H90" t="str">
-        <v/>
+      <c r="H90" t="s">
+        <v>17</v>
       </c>
       <c r="I90">
         <v>15.02</v>
       </c>
-      <c r="J90" t="str">
-        <v/>
+      <c r="J90" t="s">
+        <v>17</v>
       </c>
       <c r="K90">
         <v>-76.99879646301271</v>
@@ -4359,15 +4449,15 @@
         <v>92195</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>10031</v>
       </c>
-      <c r="B91" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C91" t="str">
-        <v>W</v>
+      <c r="B91" t="s">
+        <v>23</v>
+      </c>
+      <c r="C91" t="s">
+        <v>18</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -4375,26 +4465,26 @@
       <c r="E91">
         <v>1233</v>
       </c>
-      <c r="F91" t="str">
-        <v>S</v>
+      <c r="F91" t="s">
+        <v>19</v>
       </c>
       <c r="G91">
         <v>0.5</v>
       </c>
-      <c r="H91" t="str">
-        <v/>
+      <c r="H91" t="s">
+        <v>17</v>
       </c>
       <c r="I91">
         <v>15.13</v>
       </c>
-      <c r="J91" t="str">
-        <v/>
+      <c r="J91" t="s">
+        <v>17</v>
       </c>
       <c r="K91">
         <v>-77.00027704238893</v>
       </c>
       <c r="L91">
-        <v>37.57763542849488</v>
+        <v>37.577635428494879</v>
       </c>
       <c r="M91">
         <v>192973</v>
@@ -4403,15 +4493,15 @@
         <v>96487</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>10032</v>
       </c>
-      <c r="B92" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C92" t="str">
-        <v>W</v>
+      <c r="B92" t="s">
+        <v>23</v>
+      </c>
+      <c r="C92" t="s">
+        <v>18</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -4419,26 +4509,26 @@
       <c r="E92">
         <v>1069</v>
       </c>
-      <c r="F92" t="str">
-        <v>S</v>
+      <c r="F92" t="s">
+        <v>19</v>
       </c>
       <c r="G92">
         <v>0.5</v>
       </c>
-      <c r="H92" t="str">
-        <v/>
+      <c r="H92" t="s">
+        <v>17</v>
       </c>
       <c r="I92">
         <v>14.25</v>
       </c>
-      <c r="J92" t="str">
-        <v/>
+      <c r="J92" t="s">
+        <v>17</v>
       </c>
       <c r="K92">
-        <v>-77.00038969516756</v>
+        <v>-77.000389695167556</v>
       </c>
       <c r="L92">
-        <v>37.57740584983446</v>
+        <v>37.577405849834463</v>
       </c>
       <c r="M92">
         <v>189614</v>
@@ -4447,15 +4537,15 @@
         <v>94807</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>10033</v>
       </c>
-      <c r="B93" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C93" t="str">
-        <v>H</v>
+      <c r="B93" t="s">
+        <v>23</v>
+      </c>
+      <c r="C93" t="s">
+        <v>15</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -4463,26 +4553,26 @@
       <c r="E93">
         <v>2043</v>
       </c>
-      <c r="F93" t="str">
-        <v>S</v>
+      <c r="F93" t="s">
+        <v>19</v>
       </c>
       <c r="G93">
         <v>0.5</v>
       </c>
-      <c r="H93" t="str">
-        <v/>
+      <c r="H93" t="s">
+        <v>17</v>
       </c>
       <c r="I93">
         <v>9.81</v>
       </c>
-      <c r="J93" t="str">
-        <v/>
+      <c r="J93" t="s">
+        <v>17</v>
       </c>
       <c r="K93">
-        <v>-77.00099855661394</v>
+        <v>-77.000998556613936</v>
       </c>
       <c r="L93">
-        <v>37.57961232655693</v>
+        <v>37.579612326556934</v>
       </c>
       <c r="M93">
         <v>209567</v>
@@ -4491,15 +4581,15 @@
         <v>104784</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>10034</v>
       </c>
-      <c r="B94" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C94" t="str">
-        <v>H</v>
+      <c r="B94" t="s">
+        <v>23</v>
+      </c>
+      <c r="C94" t="s">
+        <v>15</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -4507,23 +4597,23 @@
       <c r="E94">
         <v>490</v>
       </c>
-      <c r="F94" t="str">
-        <v>S</v>
+      <c r="F94" t="s">
+        <v>19</v>
       </c>
       <c r="G94">
         <v>0.5</v>
       </c>
-      <c r="H94" t="str">
-        <v/>
+      <c r="H94" t="s">
+        <v>17</v>
       </c>
       <c r="I94">
         <v>8.65</v>
       </c>
-      <c r="J94" t="str">
-        <v/>
+      <c r="J94" t="s">
+        <v>17</v>
       </c>
       <c r="K94">
-        <v>-77.00134456157686</v>
+        <v>-77.001344561576857</v>
       </c>
       <c r="L94">
         <v>37.57922120250327</v>
@@ -4535,15 +4625,15 @@
         <v>88877</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>10035</v>
       </c>
-      <c r="B95" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C95" t="str">
-        <v>H</v>
+      <c r="B95" t="s">
+        <v>23</v>
+      </c>
+      <c r="C95" t="s">
+        <v>15</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -4551,26 +4641,26 @@
       <c r="E95">
         <v>215</v>
       </c>
-      <c r="F95" t="str">
-        <v>S</v>
+      <c r="F95" t="s">
+        <v>19</v>
       </c>
       <c r="G95">
         <v>0.5</v>
       </c>
-      <c r="H95" t="str">
-        <v/>
+      <c r="H95" t="s">
+        <v>17</v>
       </c>
       <c r="I95">
         <v>9.68</v>
       </c>
-      <c r="J95" t="str">
-        <v/>
+      <c r="J95" t="s">
+        <v>17</v>
       </c>
       <c r="K95">
-        <v>-77.00267225503923</v>
+        <v>-77.002672255039229</v>
       </c>
       <c r="L95">
-        <v>37.57952942543456</v>
+        <v>37.579529425434558</v>
       </c>
       <c r="M95">
         <v>172119</v>
@@ -4579,15 +4669,15 @@
         <v>86060</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>10036</v>
       </c>
-      <c r="B96" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C96" t="str">
-        <v>H</v>
+      <c r="B96" t="s">
+        <v>23</v>
+      </c>
+      <c r="C96" t="s">
+        <v>15</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -4595,23 +4685,23 @@
       <c r="E96">
         <v>208</v>
       </c>
-      <c r="F96" t="str">
-        <v>S</v>
+      <c r="F96" t="s">
+        <v>19</v>
       </c>
       <c r="G96">
         <v>0.5</v>
       </c>
-      <c r="H96" t="str">
-        <v/>
+      <c r="H96" t="s">
+        <v>17</v>
       </c>
       <c r="I96">
         <v>10.1</v>
       </c>
-      <c r="J96" t="str">
-        <v/>
+      <c r="J96" t="s">
+        <v>17</v>
       </c>
       <c r="K96">
-        <v>-77.00286805629732</v>
+        <v>-77.002868056297316</v>
       </c>
       <c r="L96">
         <v>37.57945715258586</v>
@@ -4623,15 +4713,15 @@
         <v>85988</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>10037</v>
       </c>
-      <c r="B97" t="str">
-        <v>RES3F</v>
-      </c>
-      <c r="C97" t="str">
-        <v>H</v>
+      <c r="B97" t="s">
+        <v>28</v>
+      </c>
+      <c r="C97" t="s">
+        <v>15</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -4639,26 +4729,26 @@
       <c r="E97">
         <v>1365</v>
       </c>
-      <c r="F97" t="str">
-        <v>S</v>
+      <c r="F97" t="s">
+        <v>19</v>
       </c>
       <c r="G97">
         <v>0.5</v>
       </c>
-      <c r="H97" t="str">
-        <v/>
+      <c r="H97" t="s">
+        <v>17</v>
       </c>
       <c r="I97">
         <v>10.91</v>
       </c>
-      <c r="J97" t="str">
-        <v/>
+      <c r="J97" t="s">
+        <v>17</v>
       </c>
       <c r="K97">
-        <v>-77.00855165719987</v>
+        <v>-77.008551657199874</v>
       </c>
       <c r="L97">
-        <v>37.57699983398919</v>
+        <v>37.576999833989191</v>
       </c>
       <c r="M97">
         <v>195677</v>
@@ -4667,15 +4757,15 @@
         <v>97839</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>10038</v>
       </c>
-      <c r="B98" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C98" t="str">
-        <v>H</v>
+      <c r="B98" t="s">
+        <v>23</v>
+      </c>
+      <c r="C98" t="s">
+        <v>15</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -4683,23 +4773,23 @@
       <c r="E98">
         <v>995</v>
       </c>
-      <c r="F98" t="str">
-        <v>S</v>
+      <c r="F98" t="s">
+        <v>19</v>
       </c>
       <c r="G98">
         <v>0.5</v>
       </c>
-      <c r="H98" t="str">
-        <v/>
+      <c r="H98" t="s">
+        <v>17</v>
       </c>
       <c r="I98">
         <v>12.39</v>
       </c>
-      <c r="J98" t="str">
-        <v/>
+      <c r="J98" t="s">
+        <v>17</v>
       </c>
       <c r="K98">
-        <v>-77.00656414031984</v>
+        <v>-77.006564140319838</v>
       </c>
       <c r="L98">
         <v>37.574346859210095</v>
@@ -4711,15 +4801,15 @@
         <v>94049</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>10039</v>
       </c>
-      <c r="B99" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C99" t="str">
-        <v>H</v>
+      <c r="B99" t="s">
+        <v>23</v>
+      </c>
+      <c r="C99" t="s">
+        <v>15</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -4727,26 +4817,26 @@
       <c r="E99">
         <v>739</v>
       </c>
-      <c r="F99" t="str">
-        <v>S</v>
+      <c r="F99" t="s">
+        <v>19</v>
       </c>
       <c r="G99">
         <v>0.5</v>
       </c>
-      <c r="H99" t="str">
-        <v/>
+      <c r="H99" t="s">
+        <v>17</v>
       </c>
       <c r="I99">
-        <v>9.96</v>
-      </c>
-      <c r="J99" t="str">
-        <v/>
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="J99" t="s">
+        <v>17</v>
       </c>
       <c r="K99">
-        <v>-77.00683236122133</v>
+        <v>-77.006832361221328</v>
       </c>
       <c r="L99">
-        <v>37.57360919638434</v>
+        <v>37.573609196384339</v>
       </c>
       <c r="M99">
         <v>182853</v>
@@ -4755,15 +4845,15 @@
         <v>91427</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>10040</v>
       </c>
-      <c r="B100" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C100" t="str">
-        <v>W</v>
+      <c r="B100" t="s">
+        <v>23</v>
+      </c>
+      <c r="C100" t="s">
+        <v>18</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -4771,23 +4861,23 @@
       <c r="E100">
         <v>1280</v>
       </c>
-      <c r="F100" t="str">
-        <v>S</v>
+      <c r="F100" t="s">
+        <v>19</v>
       </c>
       <c r="G100">
         <v>0.5</v>
       </c>
-      <c r="H100" t="str">
-        <v/>
+      <c r="H100" t="s">
+        <v>17</v>
       </c>
       <c r="I100">
-        <v>8.96</v>
-      </c>
-      <c r="J100" t="str">
-        <v/>
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="J100" t="s">
+        <v>17</v>
       </c>
       <c r="K100">
-        <v>-77.00621008872987</v>
+        <v>-77.006210088729873</v>
       </c>
       <c r="L100">
         <v>37.57288853313819</v>
@@ -4799,15 +4889,15 @@
         <v>96968</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>10041</v>
       </c>
-      <c r="B101" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C101" t="str">
-        <v>W</v>
+      <c r="B101" t="s">
+        <v>23</v>
+      </c>
+      <c r="C101" t="s">
+        <v>18</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -4815,26 +4905,26 @@
       <c r="E101">
         <v>388</v>
       </c>
-      <c r="F101" t="str">
-        <v>S</v>
+      <c r="F101" t="s">
+        <v>19</v>
       </c>
       <c r="G101">
         <v>0.5</v>
       </c>
-      <c r="H101" t="str">
-        <v/>
+      <c r="H101" t="s">
+        <v>17</v>
       </c>
       <c r="I101">
         <v>8.09</v>
       </c>
-      <c r="J101" t="str">
-        <v/>
+      <c r="J101" t="s">
+        <v>17</v>
       </c>
       <c r="K101">
-        <v>-77.00492262840272</v>
+        <v>-77.004922628402724</v>
       </c>
       <c r="L101">
-        <v>37.57235068847196</v>
+        <v>37.572350688471957</v>
       </c>
       <c r="M101">
         <v>175663</v>
@@ -4843,15 +4933,15 @@
         <v>87832</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>10042</v>
       </c>
-      <c r="B102" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C102" t="str">
-        <v>W</v>
+      <c r="B102" t="s">
+        <v>23</v>
+      </c>
+      <c r="C102" t="s">
+        <v>18</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -4859,26 +4949,26 @@
       <c r="E102">
         <v>1529</v>
       </c>
-      <c r="F102" t="str">
-        <v>S</v>
+      <c r="F102" t="s">
+        <v>19</v>
       </c>
       <c r="G102">
         <v>0.5</v>
       </c>
-      <c r="H102" t="str">
-        <v/>
+      <c r="H102" t="s">
+        <v>17</v>
       </c>
       <c r="I102">
         <v>5.92</v>
       </c>
-      <c r="J102" t="str">
-        <v/>
+      <c r="J102" t="s">
+        <v>17</v>
       </c>
       <c r="K102">
-        <v>-77.00534105300905</v>
+        <v>-77.005341053009047</v>
       </c>
       <c r="L102">
-        <v>37.57133663875339</v>
+        <v>37.571336638753387</v>
       </c>
       <c r="M102">
         <v>199037</v>
@@ -4887,15 +4977,15 @@
         <v>99519</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>10043</v>
       </c>
-      <c r="B103" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C103" t="str">
-        <v>W</v>
+      <c r="B103" t="s">
+        <v>23</v>
+      </c>
+      <c r="C103" t="s">
+        <v>18</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -4903,26 +4993,26 @@
       <c r="E103">
         <v>582</v>
       </c>
-      <c r="F103" t="str">
-        <v>S</v>
+      <c r="F103" t="s">
+        <v>19</v>
       </c>
       <c r="G103">
         <v>0.5</v>
       </c>
-      <c r="H103" t="str">
-        <v/>
+      <c r="H103" t="s">
+        <v>17</v>
       </c>
       <c r="I103">
-        <v>10.03</v>
-      </c>
-      <c r="J103" t="str">
-        <v/>
+        <v>10.029999999999999</v>
+      </c>
+      <c r="J103" t="s">
+        <v>17</v>
       </c>
       <c r="K103">
-        <v>-77.00394093990327</v>
+        <v>-77.003940939903273</v>
       </c>
       <c r="L103">
-        <v>37.57467636041689</v>
+        <v>37.574676360416888</v>
       </c>
       <c r="M103">
         <v>179637</v>
@@ -4931,15 +5021,15 @@
         <v>89819</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>10044</v>
       </c>
-      <c r="B104" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C104" t="str">
-        <v>W</v>
+      <c r="B104" t="s">
+        <v>23</v>
+      </c>
+      <c r="C104" t="s">
+        <v>18</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -4947,23 +5037,23 @@
       <c r="E104">
         <v>573</v>
       </c>
-      <c r="F104" t="str">
-        <v>S</v>
+      <c r="F104" t="s">
+        <v>19</v>
       </c>
       <c r="G104">
         <v>0.5</v>
       </c>
-      <c r="H104" t="str">
-        <v/>
+      <c r="H104" t="s">
+        <v>17</v>
       </c>
       <c r="I104">
         <v>11.28</v>
       </c>
-      <c r="J104" t="str">
-        <v/>
+      <c r="J104" t="s">
+        <v>17</v>
       </c>
       <c r="K104">
-        <v>-77.00396239757539</v>
+        <v>-77.003962397575393</v>
       </c>
       <c r="L104">
         <v>37.574997356964715</v>
@@ -4975,15 +5065,15 @@
         <v>89727</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>10045</v>
       </c>
-      <c r="B105" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C105" t="str">
-        <v>W</v>
+      <c r="B105" t="s">
+        <v>23</v>
+      </c>
+      <c r="C105" t="s">
+        <v>18</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -4991,26 +5081,26 @@
       <c r="E105">
         <v>358</v>
       </c>
-      <c r="F105" t="str">
-        <v>S</v>
+      <c r="F105" t="s">
+        <v>19</v>
       </c>
       <c r="G105">
         <v>0.5</v>
       </c>
-      <c r="H105" t="str">
-        <v/>
+      <c r="H105" t="s">
+        <v>17</v>
       </c>
       <c r="I105">
         <v>12.36</v>
       </c>
-      <c r="J105" t="str">
-        <v/>
+      <c r="J105" t="s">
+        <v>17</v>
       </c>
       <c r="K105">
-        <v>-77.00273394584657</v>
+        <v>-77.002733945846572</v>
       </c>
       <c r="L105">
-        <v>37.57582003716388</v>
+        <v>37.575820037163879</v>
       </c>
       <c r="M105">
         <v>175048</v>
@@ -5019,15 +5109,15 @@
         <v>87524</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>10046</v>
       </c>
-      <c r="B106" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C106" t="str">
-        <v>W</v>
+      <c r="B106" t="s">
+        <v>23</v>
+      </c>
+      <c r="C106" t="s">
+        <v>18</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -5035,26 +5125,26 @@
       <c r="E106">
         <v>984</v>
       </c>
-      <c r="F106" t="str">
-        <v>S</v>
+      <c r="F106" t="s">
+        <v>19</v>
       </c>
       <c r="G106">
         <v>0.5</v>
       </c>
-      <c r="H106" t="str">
-        <v/>
+      <c r="H106" t="s">
+        <v>17</v>
       </c>
       <c r="I106">
         <v>10.35</v>
       </c>
-      <c r="J106" t="str">
-        <v/>
+      <c r="J106" t="s">
+        <v>17</v>
       </c>
       <c r="K106">
-        <v>-77.00207680463792</v>
+        <v>-77.002076804637923</v>
       </c>
       <c r="L106">
-        <v>37.57453180522823</v>
+        <v>37.574531805228233</v>
       </c>
       <c r="M106">
         <v>187872</v>
@@ -5063,15 +5153,15 @@
         <v>93936</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>10047</v>
       </c>
-      <c r="B107" t="str">
-        <v>RES2</v>
-      </c>
-      <c r="C107" t="str">
-        <v>H</v>
+      <c r="B107" t="s">
+        <v>14</v>
+      </c>
+      <c r="C107" t="s">
+        <v>15</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -5079,26 +5169,26 @@
       <c r="E107">
         <v>2185</v>
       </c>
-      <c r="F107" t="str">
-        <v>P</v>
+      <c r="F107" t="s">
+        <v>20</v>
       </c>
       <c r="G107">
         <v>3</v>
       </c>
-      <c r="H107" t="str">
-        <v/>
+      <c r="H107" t="s">
+        <v>17</v>
       </c>
       <c r="I107">
         <v>7.29</v>
       </c>
-      <c r="J107" t="str">
-        <v/>
+      <c r="J107" t="s">
+        <v>17</v>
       </c>
       <c r="K107">
         <v>-77.0009019970894</v>
       </c>
       <c r="L107">
-        <v>37.57415340943526</v>
+        <v>37.574153409435262</v>
       </c>
       <c r="M107">
         <v>212475</v>
@@ -5107,15 +5197,15 @@
         <v>106238</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>10048</v>
       </c>
-      <c r="B108" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C108" t="str">
-        <v>W</v>
+      <c r="B108" t="s">
+        <v>23</v>
+      </c>
+      <c r="C108" t="s">
+        <v>18</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -5123,26 +5213,26 @@
       <c r="E108">
         <v>532</v>
       </c>
-      <c r="F108" t="str">
-        <v>P</v>
+      <c r="F108" t="s">
+        <v>20</v>
       </c>
       <c r="G108">
         <v>1</v>
       </c>
-      <c r="H108" t="str">
-        <v/>
+      <c r="H108" t="s">
+        <v>17</v>
       </c>
       <c r="I108">
         <v>6.49</v>
       </c>
-      <c r="J108" t="str">
-        <v/>
+      <c r="J108" t="s">
+        <v>17</v>
       </c>
       <c r="K108">
-        <v>-77.00082153081895</v>
+        <v>-77.000821530818953</v>
       </c>
       <c r="L108">
-        <v>37.57381540257863</v>
+        <v>37.573815402578632</v>
       </c>
       <c r="M108">
         <v>178613</v>
@@ -5151,15 +5241,15 @@
         <v>89307</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>10049</v>
       </c>
-      <c r="B109" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C109" t="str">
-        <v>W</v>
+      <c r="B109" t="s">
+        <v>23</v>
+      </c>
+      <c r="C109" t="s">
+        <v>18</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -5167,26 +5257,26 @@
       <c r="E109">
         <v>1687</v>
       </c>
-      <c r="F109" t="str">
-        <v>C</v>
+      <c r="F109" t="s">
+        <v>16</v>
       </c>
       <c r="G109">
         <v>0.5</v>
       </c>
-      <c r="H109" t="str">
-        <v/>
+      <c r="H109" t="s">
+        <v>17</v>
       </c>
       <c r="I109">
         <v>10.39</v>
       </c>
-      <c r="J109" t="str">
-        <v/>
+      <c r="J109" t="s">
+        <v>17</v>
       </c>
       <c r="K109">
-        <v>-77.00863480567934</v>
+        <v>-77.008634805679335</v>
       </c>
       <c r="L109">
-        <v>37.58086433484812</v>
+        <v>37.580864334848123</v>
       </c>
       <c r="M109">
         <v>202274</v>
@@ -5195,15 +5285,15 @@
         <v>101137</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>10050</v>
       </c>
-      <c r="B110" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C110" t="str">
-        <v>H</v>
+      <c r="B110" t="s">
+        <v>23</v>
+      </c>
+      <c r="C110" t="s">
+        <v>15</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -5211,26 +5301,26 @@
       <c r="E110">
         <v>1272</v>
       </c>
-      <c r="F110" t="str">
-        <v>S</v>
+      <c r="F110" t="s">
+        <v>19</v>
       </c>
       <c r="G110">
         <v>0.5</v>
       </c>
-      <c r="H110" t="str">
-        <v/>
+      <c r="H110" t="s">
+        <v>17</v>
       </c>
       <c r="I110">
         <v>10.52</v>
       </c>
-      <c r="J110" t="str">
-        <v/>
+      <c r="J110" t="s">
+        <v>17</v>
       </c>
       <c r="K110">
-        <v>-77.0091336965561</v>
+        <v>-77.009133696556106</v>
       </c>
       <c r="L110">
-        <v>37.57975474621838</v>
+        <v>37.579754746218377</v>
       </c>
       <c r="M110">
         <v>193772</v>
@@ -5239,15 +5329,15 @@
         <v>96886</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>10051</v>
       </c>
-      <c r="B111" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C111" t="str">
-        <v>W</v>
+      <c r="B111" t="s">
+        <v>23</v>
+      </c>
+      <c r="C111" t="s">
+        <v>18</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -5255,26 +5345,26 @@
       <c r="E111">
         <v>689</v>
       </c>
-      <c r="F111" t="str">
-        <v>S</v>
+      <c r="F111" t="s">
+        <v>19</v>
       </c>
       <c r="G111">
         <v>0.5</v>
       </c>
-      <c r="H111" t="str">
-        <v/>
+      <c r="H111" t="s">
+        <v>17</v>
       </c>
       <c r="I111">
         <v>13</v>
       </c>
-      <c r="J111" t="str">
-        <v/>
+      <c r="J111" t="s">
+        <v>17</v>
       </c>
       <c r="K111">
-        <v>-77.01216727495195</v>
+        <v>-77.012167274951949</v>
       </c>
       <c r="L111">
-        <v>37.57724216832023</v>
+        <v>37.577242168320232</v>
       </c>
       <c r="M111">
         <v>181829</v>
@@ -5283,15 +5373,15 @@
         <v>90915</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>10052</v>
       </c>
-      <c r="B112" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C112" t="str">
-        <v>W</v>
+      <c r="B112" t="s">
+        <v>23</v>
+      </c>
+      <c r="C112" t="s">
+        <v>18</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -5299,26 +5389,26 @@
       <c r="E112">
         <v>642</v>
       </c>
-      <c r="F112" t="str">
-        <v>S</v>
+      <c r="F112" t="s">
+        <v>19</v>
       </c>
       <c r="G112">
         <v>0.5</v>
       </c>
-      <c r="H112" t="str">
-        <v/>
+      <c r="H112" t="s">
+        <v>17</v>
       </c>
       <c r="I112">
         <v>11.37</v>
       </c>
-      <c r="J112" t="str">
-        <v/>
+      <c r="J112" t="s">
+        <v>17</v>
       </c>
       <c r="K112">
-        <v>-77.0113304257393</v>
+        <v>-77.011330425739303</v>
       </c>
       <c r="L112">
-        <v>37.57692543293983</v>
+        <v>37.576925432939831</v>
       </c>
       <c r="M112">
         <v>180866</v>
@@ -5327,15 +5417,15 @@
         <v>90433</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>579537068</v>
       </c>
-      <c r="B113" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C113" t="str">
-        <v>W</v>
+      <c r="B113" t="s">
+        <v>23</v>
+      </c>
+      <c r="C113" t="s">
+        <v>18</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -5343,23 +5433,23 @@
       <c r="E113">
         <v>642</v>
       </c>
-      <c r="F113" t="str">
-        <v>S</v>
+      <c r="F113" t="s">
+        <v>19</v>
       </c>
       <c r="G113">
         <v>0.5</v>
       </c>
-      <c r="H113" t="str">
-        <v/>
+      <c r="H113" t="s">
+        <v>17</v>
       </c>
       <c r="I113">
         <v>10.87</v>
       </c>
-      <c r="J113" t="str">
-        <v/>
+      <c r="J113" t="s">
+        <v>17</v>
       </c>
       <c r="K113">
-        <v>-77.01116412878038</v>
+        <v>-77.011164128780379</v>
       </c>
       <c r="L113">
         <v>37.57661507347494</v>
@@ -5371,15 +5461,15 @@
         <v>90433</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>579537069</v>
       </c>
-      <c r="B114" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C114" t="str">
-        <v>W</v>
+      <c r="B114" t="s">
+        <v>23</v>
+      </c>
+      <c r="C114" t="s">
+        <v>18</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -5387,20 +5477,20 @@
       <c r="E114">
         <v>642</v>
       </c>
-      <c r="F114" t="str">
-        <v>S</v>
+      <c r="F114" t="s">
+        <v>19</v>
       </c>
       <c r="G114">
         <v>0.5</v>
       </c>
-      <c r="H114" t="str">
-        <v/>
+      <c r="H114" t="s">
+        <v>17</v>
       </c>
       <c r="I114">
         <v>12.48</v>
       </c>
-      <c r="J114" t="str">
-        <v/>
+      <c r="J114" t="s">
+        <v>17</v>
       </c>
       <c r="K114">
         <v>-77.01164156198503</v>
@@ -5415,15 +5505,15 @@
         <v>90433</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>10006</v>
       </c>
-      <c r="B115" t="str">
-        <v>RES4</v>
-      </c>
-      <c r="C115" t="str">
-        <v>W</v>
+      <c r="B115" t="s">
+        <v>23</v>
+      </c>
+      <c r="C115" t="s">
+        <v>18</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -5431,26 +5521,26 @@
       <c r="E115">
         <v>1157</v>
       </c>
-      <c r="F115" t="str">
-        <v>S</v>
+      <c r="F115" t="s">
+        <v>19</v>
       </c>
       <c r="G115">
         <v>0.5</v>
       </c>
-      <c r="H115" t="str">
-        <v/>
+      <c r="H115" t="s">
+        <v>17</v>
       </c>
       <c r="I115">
         <v>5.21</v>
       </c>
-      <c r="J115" t="str">
-        <v/>
+      <c r="J115" t="s">
+        <v>17</v>
       </c>
       <c r="K115">
-        <v>-76.99731051921846</v>
+        <v>-76.997310519218459</v>
       </c>
       <c r="L115">
-        <v>37.57401735654538</v>
+        <v>37.574017356545383</v>
       </c>
       <c r="M115">
         <v>191416</v>
@@ -5460,8 +5550,9 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N115"/>
+    <ignoredError sqref="A1:N16 A18:N115 A17:F17 H17:N17" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/DDD___Pamunkey___NSI.xlsx
+++ b/DDD___Pamunkey___NSI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9a7f23234f188053/GitHub_projects/ADAPT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_40EF431F4A29FC6F5C6002AB8855B237A12CC00A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A68E1D4D-DC90-48CB-9C3E-5969D78588BD}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_40EF431F4A29FC6F5C6002AB8855B237A12CC00A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C94CE4A-BA46-4CEB-AC73-D792CDB23A28}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="10690" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1630" yWindow="10690" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -484,12 +484,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N115"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -533,7 +533,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>579512986</v>
       </c>
@@ -577,7 +577,7 @@
         <v>86787.94</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>579512987</v>
       </c>
@@ -621,7 +621,7 @@
         <v>79466.679999999993</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>579512988</v>
       </c>
@@ -665,7 +665,7 @@
         <v>98590.51</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>579512989</v>
       </c>
@@ -709,7 +709,7 @@
         <v>133907.38</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>579512990</v>
       </c>
@@ -753,7 +753,7 @@
         <v>123284.23</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>579513006</v>
       </c>
@@ -797,7 +797,7 @@
         <v>91655.65</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>579513007</v>
       </c>
@@ -841,7 +841,7 @@
         <v>106233.29</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>579513008</v>
       </c>
@@ -885,7 +885,7 @@
         <v>73505.88</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>579513009</v>
       </c>
@@ -929,7 +929,7 @@
         <v>115625.23</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>579513010</v>
       </c>
@@ -973,7 +973,7 @@
         <v>93519.5</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>579513011</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>70536.92</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>579513012</v>
       </c>
@@ -1061,7 +1061,7 @@
         <v>70115.47</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>579513013</v>
       </c>
@@ -1105,7 +1105,7 @@
         <v>86649.95</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>579513014</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>131643.70000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>579513015</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>161228.45000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>579513016</v>
       </c>
@@ -1237,7 +1237,7 @@
         <v>127796.59</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>579513017</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>117459.51</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>579513018</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>130251.55</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>579513019</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>69627.509999999995</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>579513020</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>117034.21</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>579513021</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>75865.990000000005</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>579513022</v>
       </c>
@@ -1501,7 +1501,7 @@
         <v>87509.85</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>579513023</v>
       </c>
@@ -1545,7 +1545,7 @@
         <v>121800.44</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>579513024</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>96475.8</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>579513025</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>83584.23</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>579513026</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>130921.83</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>579513027</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>111021.22</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>579513028</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>83255.899999999994</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>579513029</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>120421.71</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>579513030</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>112291.27</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>579513031</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>127707.98</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>579513032</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>84254.720000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>579513033</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>145321</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>579534897</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>84942.92</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>579534898</v>
       </c>
@@ -2073,7 +2073,7 @@
         <v>69435.009999999995</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>579534899</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>155746.65</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>579534905</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>70656.45</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>579534906</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>73704.98</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>579534907</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>95178.1</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>579536184</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>1980</v>
       </c>
       <c r="I41">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="J41" t="s">
         <v>17</v>
@@ -2293,7 +2293,7 @@
         <v>200307.7</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>579536842</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>43780.65</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>579536843</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>129101.68</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>579536844</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>362092.02</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>579537054</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>74873.39</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>579537067</v>
       </c>
@@ -2513,7 +2513,7 @@
         <v>68937.87</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>10000001</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>10000002</v>
       </c>
@@ -2601,7 +2601,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>10000003</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>10000004</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>10000005</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>10000006</v>
       </c>
@@ -2777,7 +2777,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>10000007</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>10000008</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>10000009</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>10000010</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>10000011</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>10000012</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>10000013</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>10000014</v>
       </c>
@@ -3129,7 +3129,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>10000015</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>10001</v>
       </c>
@@ -3217,7 +3217,7 @@
         <v>171172</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>10002</v>
       </c>
@@ -3261,7 +3261,7 @@
         <v>131410</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>10003</v>
       </c>
@@ -3305,7 +3305,7 @@
         <v>89583</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>10004</v>
       </c>
@@ -3349,7 +3349,7 @@
         <v>98945</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>10005</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>105419</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>10007</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>93383</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>10008</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>99488</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>10009</v>
       </c>
@@ -3525,7 +3525,7 @@
         <v>105910</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>10010</v>
       </c>
@@ -3569,7 +3569,7 @@
         <v>93476</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>10011</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>94018</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>10012</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>91939</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>10013</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>118519</v>
       </c>
     </row>
-    <row r="74" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>10014</v>
       </c>
@@ -3745,7 +3745,7 @@
         <v>90771</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>10015</v>
       </c>
@@ -3789,7 +3789,7 @@
         <v>95545</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>10016</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>91273</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>10017</v>
       </c>
@@ -3877,7 +3877,7 @@
         <v>92001</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>10018</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>96231</v>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>10019</v>
       </c>
@@ -3965,7 +3965,7 @@
         <v>88405</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>10020</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>85732</v>
       </c>
     </row>
-    <row r="81" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>10021</v>
       </c>
@@ -4053,7 +4053,7 @@
         <v>86910</v>
       </c>
     </row>
-    <row r="82" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>10022</v>
       </c>
@@ -4097,7 +4097,7 @@
         <v>91202</v>
       </c>
     </row>
-    <row r="83" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>10023</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>87842</v>
       </c>
     </row>
-    <row r="84" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>10024</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>101076</v>
       </c>
     </row>
-    <row r="85" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>10025</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>116430</v>
       </c>
     </row>
-    <row r="86" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>10026</v>
       </c>
@@ -4273,7 +4273,7 @@
         <v>92871</v>
       </c>
     </row>
-    <row r="87" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>10027</v>
       </c>
@@ -4317,7 +4317,7 @@
         <v>90812</v>
       </c>
     </row>
-    <row r="88" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>10028</v>
       </c>
@@ -4361,7 +4361,7 @@
         <v>88539</v>
       </c>
     </row>
-    <row r="89" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>10029</v>
       </c>
@@ -4405,7 +4405,7 @@
         <v>87484</v>
       </c>
     </row>
-    <row r="90" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>10030</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>92195</v>
       </c>
     </row>
-    <row r="91" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>10031</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>96487</v>
       </c>
     </row>
-    <row r="92" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>10032</v>
       </c>
@@ -4537,7 +4537,7 @@
         <v>94807</v>
       </c>
     </row>
-    <row r="93" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>10033</v>
       </c>
@@ -4581,7 +4581,7 @@
         <v>104784</v>
       </c>
     </row>
-    <row r="94" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>10034</v>
       </c>
@@ -4625,7 +4625,7 @@
         <v>88877</v>
       </c>
     </row>
-    <row r="95" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>10035</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>86060</v>
       </c>
     </row>
-    <row r="96" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>10036</v>
       </c>
@@ -4713,7 +4713,7 @@
         <v>85988</v>
       </c>
     </row>
-    <row r="97" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>10037</v>
       </c>
@@ -4757,7 +4757,7 @@
         <v>97839</v>
       </c>
     </row>
-    <row r="98" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>10038</v>
       </c>
@@ -4801,7 +4801,7 @@
         <v>94049</v>
       </c>
     </row>
-    <row r="99" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>10039</v>
       </c>
@@ -4845,7 +4845,7 @@
         <v>91427</v>
       </c>
     </row>
-    <row r="100" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>10040</v>
       </c>
@@ -4889,7 +4889,7 @@
         <v>96968</v>
       </c>
     </row>
-    <row r="101" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>10041</v>
       </c>
@@ -4933,7 +4933,7 @@
         <v>87832</v>
       </c>
     </row>
-    <row r="102" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>10042</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>99519</v>
       </c>
     </row>
-    <row r="103" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>10043</v>
       </c>
@@ -5021,7 +5021,7 @@
         <v>89819</v>
       </c>
     </row>
-    <row r="104" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>10044</v>
       </c>
@@ -5065,7 +5065,7 @@
         <v>89727</v>
       </c>
     </row>
-    <row r="105" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>10045</v>
       </c>
@@ -5109,7 +5109,7 @@
         <v>87524</v>
       </c>
     </row>
-    <row r="106" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>10046</v>
       </c>
@@ -5153,7 +5153,7 @@
         <v>93936</v>
       </c>
     </row>
-    <row r="107" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>10047</v>
       </c>
@@ -5197,7 +5197,7 @@
         <v>106238</v>
       </c>
     </row>
-    <row r="108" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>10048</v>
       </c>
@@ -5241,7 +5241,7 @@
         <v>89307</v>
       </c>
     </row>
-    <row r="109" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>10049</v>
       </c>
@@ -5285,7 +5285,7 @@
         <v>101137</v>
       </c>
     </row>
-    <row r="110" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>10050</v>
       </c>
@@ -5329,7 +5329,7 @@
         <v>96886</v>
       </c>
     </row>
-    <row r="111" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>10051</v>
       </c>
@@ -5373,7 +5373,7 @@
         <v>90915</v>
       </c>
     </row>
-    <row r="112" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>10052</v>
       </c>
@@ -5417,7 +5417,7 @@
         <v>90433</v>
       </c>
     </row>
-    <row r="113" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>579537068</v>
       </c>
@@ -5461,7 +5461,7 @@
         <v>90433</v>
       </c>
     </row>
-    <row r="114" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>579537069</v>
       </c>
@@ -5505,7 +5505,7 @@
         <v>90433</v>
       </c>
     </row>
-    <row r="115" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>10006</v>
       </c>
@@ -5552,7 +5552,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:N16 A18:N115 A17:F17 H17:N17" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:N16 A18:N40 A17:F17 H17:N17 A42:N115 A41:H41 J41:N41" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/DDD___Pamunkey___NSI.xlsx
+++ b/DDD___Pamunkey___NSI.xlsx
@@ -1,119 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9a7f23234f188053/GitHub_projects/ADAPT/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_40EF431F4A29FC6F5C6002AB8855B237A12CC00A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C94CE4A-BA46-4CEB-AC73-D792CDB23A28}"/>
-  <bookViews>
-    <workbookView xWindow="-1630" yWindow="10690" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="29">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>occupancy_type</t>
-  </si>
-  <si>
-    <t>building_type</t>
-  </si>
-  <si>
-    <t>number_of_stories</t>
-  </si>
-  <si>
-    <t>area</t>
-  </si>
-  <si>
-    <t>foundation_type</t>
-  </si>
-  <si>
-    <t>foundation_height</t>
-  </si>
-  <si>
-    <t>year_built</t>
-  </si>
-  <si>
-    <t>ground_elevation</t>
-  </si>
-  <si>
-    <t>address</t>
-  </si>
-  <si>
-    <t>longitude</t>
-  </si>
-  <si>
-    <t>latitude</t>
-  </si>
-  <si>
-    <t>structure_value</t>
-  </si>
-  <si>
-    <t>content_value</t>
-  </si>
-  <si>
-    <t>RES2</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>RES1</t>
-  </si>
-  <si>
-    <t>REL1</t>
-  </si>
-  <si>
-    <t>RES4</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>RES3A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>COM8</t>
-  </si>
-  <si>
-    <t>RES3F</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -143,21 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -482,66 +396,62 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N115"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>occupancy_type</v>
+      </c>
+      <c r="C1" t="str">
+        <v>building_type</v>
+      </c>
+      <c r="D1" t="str">
+        <v>number_of_stories</v>
+      </c>
+      <c r="E1" t="str">
+        <v>area</v>
+      </c>
+      <c r="F1" t="str">
+        <v>foundation_type</v>
+      </c>
+      <c r="G1" t="str">
+        <v>foundation_height</v>
+      </c>
+      <c r="H1" t="str">
+        <v>year_built</v>
+      </c>
+      <c r="I1" t="str">
+        <v>ground_elevation</v>
+      </c>
+      <c r="J1" t="str">
+        <v>address</v>
+      </c>
+      <c r="K1" t="str">
+        <v>longitude</v>
+      </c>
+      <c r="L1" t="str">
+        <v>latitude</v>
+      </c>
+      <c r="M1" t="str">
+        <v>structure_value</v>
+      </c>
+      <c r="N1" t="str">
+        <v>content_value</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>579512986</v>
       </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
+      <c r="B2" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C2" t="str">
+        <v>H</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -549,8 +459,8 @@
       <c r="E2">
         <v>2368</v>
       </c>
-      <c r="F2" t="s">
-        <v>16</v>
+      <c r="F2" t="str">
+        <v>C</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -561,14 +471,14 @@
       <c r="I2">
         <v>14.83</v>
       </c>
-      <c r="J2" t="s">
-        <v>17</v>
+      <c r="J2" t="str">
+        <v/>
       </c>
       <c r="K2">
-        <v>-77.000083923339844</v>
+        <v>-77.00008392333984</v>
       </c>
       <c r="L2">
-        <v>37.577482376133233</v>
+        <v>37.57748237613323</v>
       </c>
       <c r="M2">
         <v>173575.88</v>
@@ -577,15 +487,15 @@
         <v>86787.94</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3">
         <v>579512987</v>
       </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
+      <c r="B3" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C3" t="str">
+        <v>W</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -593,8 +503,8 @@
       <c r="E3">
         <v>1917.3</v>
       </c>
-      <c r="F3" t="s">
-        <v>16</v>
+      <c r="F3" t="str">
+        <v>C</v>
       </c>
       <c r="G3">
         <v>6</v>
@@ -605,31 +515,31 @@
       <c r="I3">
         <v>5.7363</v>
       </c>
-      <c r="J3" t="s">
-        <v>17</v>
+      <c r="J3" t="str">
+        <v/>
       </c>
       <c r="K3">
-        <v>-76.997263500000003</v>
+        <v>-76.9972635</v>
       </c>
       <c r="L3">
-        <v>37.574997500000002</v>
+        <v>37.5749975</v>
       </c>
       <c r="M3">
-        <v>158933.35999999999</v>
+        <v>158933.36</v>
       </c>
       <c r="N3">
-        <v>79466.679999999993</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>79466.68</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>579512988</v>
       </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
+      <c r="B4" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C4" t="str">
+        <v>S</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -637,8 +547,8 @@
       <c r="E4">
         <v>1045</v>
       </c>
-      <c r="F4" t="s">
-        <v>20</v>
+      <c r="F4" t="str">
+        <v>P</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -649,14 +559,14 @@
       <c r="I4">
         <v>11.82</v>
       </c>
-      <c r="J4" t="s">
-        <v>17</v>
+      <c r="J4" t="str">
+        <v/>
       </c>
       <c r="K4">
-        <v>-77.003656625747695</v>
+        <v>-77.0036566257477</v>
       </c>
       <c r="L4">
-        <v>37.578432571125447</v>
+        <v>37.57843257112545</v>
       </c>
       <c r="M4">
         <v>197181.02</v>
@@ -665,15 +575,15 @@
         <v>98590.51</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5">
         <v>579512989</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
+      <c r="B5" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C5" t="str">
+        <v>H</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -681,8 +591,8 @@
       <c r="E5">
         <v>2289</v>
       </c>
-      <c r="F5" t="s">
-        <v>20</v>
+      <c r="F5" t="str">
+        <v>P</v>
       </c>
       <c r="G5">
         <v>1.5</v>
@@ -693,14 +603,14 @@
       <c r="I5">
         <v>12.33</v>
       </c>
-      <c r="J5" t="s">
-        <v>17</v>
+      <c r="J5" t="str">
+        <v/>
       </c>
       <c r="K5">
-        <v>-77.002915209999998</v>
+        <v>-77.00291521</v>
       </c>
       <c r="L5">
-        <v>37.575838019999999</v>
+        <v>37.57583802</v>
       </c>
       <c r="M5">
         <v>267814.75</v>
@@ -709,15 +619,15 @@
         <v>133907.38</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6">
         <v>579512990</v>
       </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
+      <c r="B6" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C6" t="str">
+        <v>W</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -725,8 +635,8 @@
       <c r="E6">
         <v>3454.5</v>
       </c>
-      <c r="F6" t="s">
-        <v>16</v>
+      <c r="F6" t="str">
+        <v>C</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -735,16 +645,16 @@
         <v>1980</v>
       </c>
       <c r="I6">
-        <v>8.7899999999999991</v>
-      </c>
-      <c r="J6" t="s">
-        <v>17</v>
+        <v>8.79</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
       </c>
       <c r="K6">
-        <v>-76.999067366123214</v>
+        <v>-76.99906736612321</v>
       </c>
       <c r="L6">
-        <v>37.575086640526777</v>
+        <v>37.57508664052678</v>
       </c>
       <c r="M6">
         <v>246568.46</v>
@@ -753,15 +663,15 @@
         <v>123284.23</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7">
         <v>579513006</v>
       </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
+      <c r="B7" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C7" t="str">
+        <v>W</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -769,8 +679,8 @@
       <c r="E7">
         <v>1892.8</v>
       </c>
-      <c r="F7" t="s">
-        <v>20</v>
+      <c r="F7" t="str">
+        <v>P</v>
       </c>
       <c r="G7">
         <v>3.5</v>
@@ -779,13 +689,13 @@
         <v>1980</v>
       </c>
       <c r="I7">
-        <v>8.3591999999999995</v>
-      </c>
-      <c r="J7" t="s">
-        <v>17</v>
+        <v>8.3592</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
       </c>
       <c r="K7">
-        <v>-77.000772999999995</v>
+        <v>-77.000773</v>
       </c>
       <c r="L7">
         <v>37.572578</v>
@@ -797,15 +707,15 @@
         <v>91655.65</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8">
         <v>579513007</v>
       </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
+      <c r="B8" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C8" t="str">
+        <v>H</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -813,8 +723,8 @@
       <c r="E8">
         <v>1340.1</v>
       </c>
-      <c r="F8" t="s">
-        <v>20</v>
+      <c r="F8" t="str">
+        <v>P</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -825,14 +735,14 @@
       <c r="I8">
         <v>11.63</v>
       </c>
-      <c r="J8" t="s">
-        <v>17</v>
+      <c r="J8" t="str">
+        <v/>
       </c>
       <c r="K8">
-        <v>-77.005322000000007</v>
+        <v>-77.005322</v>
       </c>
       <c r="L8">
-        <v>37.578576499999997</v>
+        <v>37.5785765</v>
       </c>
       <c r="M8">
         <v>212466.58</v>
@@ -841,15 +751,15 @@
         <v>106233.29</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9">
         <v>579513008</v>
       </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
+      <c r="B9" t="str">
+        <v>REL1</v>
+      </c>
+      <c r="C9" t="str">
+        <v>W</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -857,8 +767,8 @@
       <c r="E9">
         <v>1721.5</v>
       </c>
-      <c r="F9" t="s">
-        <v>16</v>
+      <c r="F9" t="str">
+        <v>C</v>
       </c>
       <c r="G9">
         <v>1.5</v>
@@ -869,14 +779,14 @@
       <c r="I9">
         <v>12.64</v>
       </c>
-      <c r="J9" t="s">
-        <v>17</v>
+      <c r="J9" t="str">
+        <v/>
       </c>
       <c r="K9">
-        <v>-77.006483360000004</v>
+        <v>-77.00648336</v>
       </c>
       <c r="L9">
-        <v>37.575052800000002</v>
+        <v>37.5750528</v>
       </c>
       <c r="M9">
         <v>147011.75</v>
@@ -885,15 +795,15 @@
         <v>73505.88</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10">
         <v>579513009</v>
       </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
+      <c r="B10" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C10" t="str">
+        <v>H</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -901,8 +811,8 @@
       <c r="E10">
         <v>1475</v>
       </c>
-      <c r="F10" t="s">
-        <v>19</v>
+      <c r="F10" t="str">
+        <v>S</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -913,14 +823,14 @@
       <c r="I10">
         <v>11.83</v>
       </c>
-      <c r="J10" t="s">
-        <v>17</v>
+      <c r="J10" t="str">
+        <v/>
       </c>
       <c r="K10">
-        <v>-77.011738121509566</v>
+        <v>-77.01173812150957</v>
       </c>
       <c r="L10">
-        <v>37.576706480848983</v>
+        <v>37.57670648084898</v>
       </c>
       <c r="M10">
         <v>231250.46</v>
@@ -929,15 +839,15 @@
         <v>115625.23</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11">
         <v>579513010</v>
       </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" t="s">
-        <v>18</v>
+      <c r="B11" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C11" t="str">
+        <v>W</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -945,8 +855,8 @@
       <c r="E11">
         <v>2738</v>
       </c>
-      <c r="F11" t="s">
-        <v>16</v>
+      <c r="F11" t="str">
+        <v>C</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -957,14 +867,14 @@
       <c r="I11">
         <v>12.07</v>
       </c>
-      <c r="J11" t="s">
-        <v>17</v>
+      <c r="J11" t="str">
+        <v/>
       </c>
       <c r="K11">
-        <v>-77.005764409999998</v>
+        <v>-77.00576441</v>
       </c>
       <c r="L11">
-        <v>37.578420780000002</v>
+        <v>37.57842078</v>
       </c>
       <c r="M11">
         <v>187039.01</v>
@@ -973,15 +883,15 @@
         <v>93519.5</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12">
         <v>579513011</v>
       </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" t="s">
-        <v>15</v>
+      <c r="B12" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C12" t="str">
+        <v>H</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -989,8 +899,8 @@
       <c r="E12">
         <v>1890</v>
       </c>
-      <c r="F12" t="s">
-        <v>20</v>
+      <c r="F12" t="str">
+        <v>P</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1001,14 +911,14 @@
       <c r="I12">
         <v>10.88</v>
       </c>
-      <c r="J12" t="s">
-        <v>17</v>
+      <c r="J12" t="str">
+        <v/>
       </c>
       <c r="K12">
-        <v>-77.001851499080672</v>
+        <v>-77.00185149908067</v>
       </c>
       <c r="L12">
-        <v>37.574633844214048</v>
+        <v>37.57463384421405</v>
       </c>
       <c r="M12">
         <v>141073.85</v>
@@ -1017,15 +927,15 @@
         <v>70536.92</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13">
         <v>579513012</v>
       </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" t="s">
-        <v>18</v>
+      <c r="B13" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C13" t="str">
+        <v>W</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1033,8 +943,8 @@
       <c r="E13">
         <v>1616.7</v>
       </c>
-      <c r="F13" t="s">
-        <v>19</v>
+      <c r="F13" t="str">
+        <v>S</v>
       </c>
       <c r="G13">
         <v>0.5</v>
@@ -1043,33 +953,33 @@
         <v>1980</v>
       </c>
       <c r="I13">
-        <v>7.5876000000000001</v>
-      </c>
-      <c r="J13" t="s">
-        <v>17</v>
+        <v>7.5876</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
       </c>
       <c r="K13">
-        <v>-77.000905560000007</v>
+        <v>-77.00090556</v>
       </c>
       <c r="L13">
-        <v>37.572306730000001</v>
+        <v>37.57230673</v>
       </c>
       <c r="M13">
-        <v>140230.95000000001</v>
+        <v>140230.95</v>
       </c>
       <c r="N13">
         <v>70115.47</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14">
         <v>579513013</v>
       </c>
-      <c r="B14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" t="s">
-        <v>24</v>
+      <c r="B14" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C14" t="str">
+        <v>M</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1077,8 +987,8 @@
       <c r="E14">
         <v>2672</v>
       </c>
-      <c r="F14" t="s">
-        <v>19</v>
+      <c r="F14" t="str">
+        <v>S</v>
       </c>
       <c r="G14">
         <v>0.5</v>
@@ -1089,14 +999,14 @@
       <c r="I14">
         <v>10.07</v>
       </c>
-      <c r="J14" t="s">
-        <v>17</v>
+      <c r="J14" t="str">
+        <v/>
       </c>
       <c r="K14">
-        <v>-77.006636559963241</v>
+        <v>-77.00663655996324</v>
       </c>
       <c r="L14">
-        <v>37.573475268344041</v>
+        <v>37.57347526834404</v>
       </c>
       <c r="M14">
         <v>173299.91</v>
@@ -1105,15 +1015,15 @@
         <v>86649.95</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15">
         <v>579513014</v>
       </c>
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" t="s">
-        <v>24</v>
+      <c r="B15" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C15" t="str">
+        <v>M</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1121,8 +1031,8 @@
       <c r="E15">
         <v>3756.5</v>
       </c>
-      <c r="F15" t="s">
-        <v>19</v>
+      <c r="F15" t="str">
+        <v>S</v>
       </c>
       <c r="G15">
         <v>0.5</v>
@@ -1131,33 +1041,33 @@
         <v>1980</v>
       </c>
       <c r="I15">
-        <v>6.3471000000000002</v>
-      </c>
-      <c r="J15" t="s">
-        <v>17</v>
+        <v>6.3471</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
       </c>
       <c r="K15">
-        <v>-76.997351409999993</v>
+        <v>-76.99735141</v>
       </c>
       <c r="L15">
-        <v>37.574191759999998</v>
+        <v>37.57419176</v>
       </c>
       <c r="M15">
-        <v>263287.40000000002</v>
+        <v>263287.4</v>
       </c>
       <c r="N15">
-        <v>131643.70000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+        <v>131643.7</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16">
         <v>579513015</v>
       </c>
-      <c r="B16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" t="s">
-        <v>15</v>
+      <c r="B16" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C16" t="str">
+        <v>H</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1165,8 +1075,8 @@
       <c r="E16">
         <v>3200</v>
       </c>
-      <c r="F16" t="s">
-        <v>20</v>
+      <c r="F16" t="str">
+        <v>P</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1177,31 +1087,31 @@
       <c r="I16">
         <v>11.06</v>
       </c>
-      <c r="J16" t="s">
-        <v>17</v>
+      <c r="J16" t="str">
+        <v/>
       </c>
       <c r="K16">
-        <v>-77.008486520000005</v>
+        <v>-77.00848652</v>
       </c>
       <c r="L16">
-        <v>37.577102740000001</v>
+        <v>37.57710274</v>
       </c>
       <c r="M16">
-        <v>322456.90000000002</v>
+        <v>322456.9</v>
       </c>
       <c r="N16">
-        <v>161228.45000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+        <v>161228.45</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17">
         <v>579513016</v>
       </c>
-      <c r="B17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" t="s">
-        <v>18</v>
+      <c r="B17" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C17" t="str">
+        <v>W</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -1209,8 +1119,8 @@
       <c r="E17">
         <v>3086.7</v>
       </c>
-      <c r="F17" t="s">
-        <v>20</v>
+      <c r="F17" t="str">
+        <v>P</v>
       </c>
       <c r="G17">
         <v>4</v>
@@ -1219,13 +1129,13 @@
         <v>1980</v>
       </c>
       <c r="I17">
-        <v>4.9321999999999999</v>
-      </c>
-      <c r="J17" t="s">
-        <v>17</v>
+        <v>4.9322</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
       </c>
       <c r="K17">
-        <v>-77.000177800655365</v>
+        <v>-77.00017780065536</v>
       </c>
       <c r="L17">
         <v>37.569535975562985</v>
@@ -1237,15 +1147,15 @@
         <v>127796.59</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18">
         <v>579513017</v>
       </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" t="s">
-        <v>18</v>
+      <c r="B18" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C18" t="str">
+        <v>W</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1253,8 +1163,8 @@
       <c r="E18">
         <v>3814</v>
       </c>
-      <c r="F18" t="s">
-        <v>19</v>
+      <c r="F18" t="str">
+        <v>S</v>
       </c>
       <c r="G18">
         <v>0.5</v>
@@ -1265,14 +1175,14 @@
       <c r="I18">
         <v>10.44</v>
       </c>
-      <c r="J18" t="s">
-        <v>17</v>
+      <c r="J18" t="str">
+        <v/>
       </c>
       <c r="K18">
-        <v>-77.007369800000006</v>
+        <v>-77.0073698</v>
       </c>
       <c r="L18">
-        <v>37.576319519999998</v>
+        <v>37.57631952</v>
       </c>
       <c r="M18">
         <v>234919.03</v>
@@ -1281,15 +1191,15 @@
         <v>117459.51</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19">
         <v>579513018</v>
       </c>
-      <c r="B19" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" t="s">
-        <v>18</v>
+      <c r="B19" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C19" t="str">
+        <v>W</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -1297,8 +1207,8 @@
       <c r="E19">
         <v>2422</v>
       </c>
-      <c r="F19" t="s">
-        <v>19</v>
+      <c r="F19" t="str">
+        <v>S</v>
       </c>
       <c r="G19">
         <v>0.5</v>
@@ -1307,16 +1217,16 @@
         <v>1980</v>
       </c>
       <c r="I19">
-        <v>8.25</v>
-      </c>
-      <c r="J19" t="s">
-        <v>17</v>
+        <v>8.68</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
       </c>
       <c r="K19">
-        <v>-76.993266169999998</v>
+        <v>-76.99329525232316</v>
       </c>
       <c r="L19">
-        <v>37.574469550000003</v>
+        <v>37.574485037313025</v>
       </c>
       <c r="M19">
         <v>260503.11</v>
@@ -1325,15 +1235,15 @@
         <v>130251.55</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20">
         <v>579513019</v>
       </c>
-      <c r="B20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" t="s">
-        <v>18</v>
+      <c r="B20" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C20" t="str">
+        <v>W</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1341,8 +1251,8 @@
       <c r="E20">
         <v>1602</v>
       </c>
-      <c r="F20" t="s">
-        <v>20</v>
+      <c r="F20" t="str">
+        <v>P</v>
       </c>
       <c r="G20">
         <v>3.5</v>
@@ -1351,33 +1261,33 @@
         <v>1980</v>
       </c>
       <c r="I20">
-        <v>4.5298999999999996</v>
-      </c>
-      <c r="J20" t="s">
-        <v>17</v>
+        <v>4.5299</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
       </c>
       <c r="K20">
-        <v>-76.999589499999999</v>
+        <v>-76.9995895</v>
       </c>
       <c r="L20">
-        <v>37.571747999999999</v>
+        <v>37.571748</v>
       </c>
       <c r="M20">
         <v>139255.01</v>
       </c>
       <c r="N20">
-        <v>69627.509999999995</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+        <v>69627.51</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21">
         <v>579513020</v>
       </c>
-      <c r="B21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" t="s">
-        <v>15</v>
+      <c r="B21" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C21" t="str">
+        <v>H</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1385,8 +1295,8 @@
       <c r="E21">
         <v>1524.9</v>
       </c>
-      <c r="F21" t="s">
-        <v>20</v>
+      <c r="F21" t="str">
+        <v>P</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1397,14 +1307,14 @@
       <c r="I21">
         <v>12.0861</v>
       </c>
-      <c r="J21" t="s">
-        <v>17</v>
+      <c r="J21" t="str">
+        <v/>
       </c>
       <c r="K21">
-        <v>-77.006277143955231</v>
+        <v>-77.00627714395523</v>
       </c>
       <c r="L21">
-        <v>37.574338355933847</v>
+        <v>37.57433835593385</v>
       </c>
       <c r="M21">
         <v>234068.41</v>
@@ -1413,15 +1323,15 @@
         <v>117034.21</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22">
         <v>579513021</v>
       </c>
-      <c r="B22" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" t="s">
-        <v>15</v>
+      <c r="B22" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C22" t="str">
+        <v>H</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1429,8 +1339,8 @@
       <c r="E22">
         <v>1002</v>
       </c>
-      <c r="F22" t="s">
-        <v>20</v>
+      <c r="F22" t="str">
+        <v>P</v>
       </c>
       <c r="G22">
         <v>3</v>
@@ -1441,40 +1351,40 @@
       <c r="I22">
         <v>7.27</v>
       </c>
-      <c r="J22" t="s">
-        <v>17</v>
+      <c r="J22" t="str">
+        <v/>
       </c>
       <c r="K22">
-        <v>-77.005147933959975</v>
+        <v>-77.00514793395998</v>
       </c>
       <c r="L22">
-        <v>37.572501625509481</v>
+        <v>37.57250162550948</v>
       </c>
       <c r="M22">
         <v>151731.99</v>
       </c>
       <c r="N22">
-        <v>75865.990000000005</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+        <v>75865.99</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23">
         <v>579513022</v>
       </c>
-      <c r="B23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" t="s">
-        <v>18</v>
+      <c r="B23" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C23" t="str">
+        <v>W</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23">
-        <v>2211.8000000000002</v>
-      </c>
-      <c r="F23" t="s">
-        <v>20</v>
+        <v>2211.8</v>
+      </c>
+      <c r="F23" t="str">
+        <v>P</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1485,14 +1395,14 @@
       <c r="I23">
         <v>10.7319</v>
       </c>
-      <c r="J23" t="s">
-        <v>17</v>
+      <c r="J23" t="str">
+        <v/>
       </c>
       <c r="K23">
-        <v>-77.010037600994124</v>
+        <v>-77.01003760099412</v>
       </c>
       <c r="L23">
-        <v>37.578713163300698</v>
+        <v>37.5787131633007</v>
       </c>
       <c r="M23">
         <v>175019.69</v>
@@ -1501,15 +1411,15 @@
         <v>87509.85</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24">
         <v>579513023</v>
       </c>
-      <c r="B24" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" t="s">
-        <v>15</v>
+      <c r="B24" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C24" t="str">
+        <v>H</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1517,8 +1427,8 @@
       <c r="E24">
         <v>3854</v>
       </c>
-      <c r="F24" t="s">
-        <v>20</v>
+      <c r="F24" t="str">
+        <v>P</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -1527,16 +1437,16 @@
         <v>1980</v>
       </c>
       <c r="I24">
-        <v>9.7899999999999991</v>
-      </c>
-      <c r="J24" t="s">
-        <v>17</v>
+        <v>9.79</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
       </c>
       <c r="K24">
-        <v>-77.006586459999994</v>
+        <v>-77.00658646</v>
       </c>
       <c r="L24">
-        <v>37.577419620000001</v>
+        <v>37.57741962</v>
       </c>
       <c r="M24">
         <v>243600.88</v>
@@ -1545,15 +1455,15 @@
         <v>121800.44</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25">
         <v>579513024</v>
       </c>
-      <c r="B25" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" t="s">
-        <v>15</v>
+      <c r="B25" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C25" t="str">
+        <v>H</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1561,8 +1471,8 @@
       <c r="E25">
         <v>2194</v>
       </c>
-      <c r="F25" t="s">
-        <v>20</v>
+      <c r="F25" t="str">
+        <v>P</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -1573,11 +1483,11 @@
       <c r="I25">
         <v>10.38</v>
       </c>
-      <c r="J25" t="s">
-        <v>17</v>
+      <c r="J25" t="str">
+        <v/>
       </c>
       <c r="K25">
-        <v>-77.003839389999996</v>
+        <v>-77.00383939</v>
       </c>
       <c r="L25">
         <v>37.57942817</v>
@@ -1589,15 +1499,15 @@
         <v>96475.8</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26">
         <v>579513025</v>
       </c>
-      <c r="B26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" t="s">
-        <v>18</v>
+      <c r="B26" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C26" t="str">
+        <v>W</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1605,8 +1515,8 @@
       <c r="E26">
         <v>1920</v>
       </c>
-      <c r="F26" t="s">
-        <v>16</v>
+      <c r="F26" t="str">
+        <v>C</v>
       </c>
       <c r="G26">
         <v>1.5</v>
@@ -1617,11 +1527,11 @@
       <c r="I26">
         <v>8.67</v>
       </c>
-      <c r="J26" t="s">
-        <v>17</v>
+      <c r="J26" t="str">
+        <v/>
       </c>
       <c r="K26">
-        <v>-77.005974054336562</v>
+        <v>-77.00597405433656</v>
       </c>
       <c r="L26">
         <v>37.572814127981076</v>
@@ -1633,15 +1543,15 @@
         <v>83584.23</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27">
         <v>579513026</v>
       </c>
-      <c r="B27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" t="s">
-        <v>18</v>
+      <c r="B27" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C27" t="str">
+        <v>W</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1649,8 +1559,8 @@
       <c r="E27">
         <v>1788</v>
       </c>
-      <c r="F27" t="s">
-        <v>20</v>
+      <c r="F27" t="str">
+        <v>P</v>
       </c>
       <c r="G27">
         <v>0.5</v>
@@ -1661,14 +1571,14 @@
       <c r="I27">
         <v>2.82</v>
       </c>
-      <c r="J27" t="s">
-        <v>17</v>
+      <c r="J27" t="str">
+        <v/>
       </c>
       <c r="K27">
-        <v>-76.992608606815352</v>
+        <v>-76.99260860681535</v>
       </c>
       <c r="L27">
-        <v>37.575975218714852</v>
+        <v>37.57597521871485</v>
       </c>
       <c r="M27">
         <v>261843.66</v>
@@ -1677,15 +1587,15 @@
         <v>130921.83</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28">
         <v>579513027</v>
       </c>
-      <c r="B28" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" t="s">
-        <v>15</v>
+      <c r="B28" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C28" t="str">
+        <v>H</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -1693,8 +1603,8 @@
       <c r="E28">
         <v>1420.1</v>
       </c>
-      <c r="F28" t="s">
-        <v>16</v>
+      <c r="F28" t="str">
+        <v>C</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1705,14 +1615,14 @@
       <c r="I28">
         <v>10.9</v>
       </c>
-      <c r="J28" t="s">
-        <v>17</v>
+      <c r="J28" t="str">
+        <v/>
       </c>
       <c r="K28">
-        <v>-77.007690499999995</v>
+        <v>-77.0076905</v>
       </c>
       <c r="L28">
-        <v>37.578275499999997</v>
+        <v>37.5782755</v>
       </c>
       <c r="M28">
         <v>222042.43</v>
@@ -1721,15 +1631,15 @@
         <v>111021.22</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29">
         <v>579513028</v>
       </c>
-      <c r="B29" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" t="s">
-        <v>18</v>
+      <c r="B29" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C29" t="str">
+        <v>W</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1737,8 +1647,8 @@
       <c r="E29">
         <v>1427</v>
       </c>
-      <c r="F29" t="s">
-        <v>19</v>
+      <c r="F29" t="str">
+        <v>S</v>
       </c>
       <c r="G29">
         <v>0.5</v>
@@ -1749,31 +1659,31 @@
       <c r="I29">
         <v>12.6</v>
       </c>
-      <c r="J29" t="s">
-        <v>17</v>
+      <c r="J29" t="str">
+        <v/>
       </c>
       <c r="K29">
-        <v>-77.012001979999994</v>
+        <v>-77.01200198</v>
       </c>
       <c r="L29">
         <v>37.57717306</v>
       </c>
       <c r="M29">
-        <v>166511.79999999999</v>
+        <v>166511.8</v>
       </c>
       <c r="N29">
-        <v>83255.899999999994</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+        <v>83255.9</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30">
         <v>579513029</v>
       </c>
-      <c r="B30" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" t="s">
-        <v>15</v>
+      <c r="B30" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C30" t="str">
+        <v>H</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1781,8 +1691,8 @@
       <c r="E30">
         <v>1859</v>
       </c>
-      <c r="F30" t="s">
-        <v>20</v>
+      <c r="F30" t="str">
+        <v>P</v>
       </c>
       <c r="G30">
         <v>2.5</v>
@@ -1793,14 +1703,14 @@
       <c r="I30">
         <v>7.56</v>
       </c>
-      <c r="J30" t="s">
-        <v>17</v>
+      <c r="J30" t="str">
+        <v/>
       </c>
       <c r="K30">
-        <v>-77.005437612533584</v>
+        <v>-77.00543761253358</v>
       </c>
       <c r="L30">
-        <v>37.571555606632913</v>
+        <v>37.57155560663291</v>
       </c>
       <c r="M30">
         <v>240843.43</v>
@@ -1809,15 +1719,15 @@
         <v>120421.71</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31">
         <v>579513030</v>
       </c>
-      <c r="B31" t="s">
-        <v>21</v>
-      </c>
-      <c r="C31" t="s">
-        <v>24</v>
+      <c r="B31" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C31" t="str">
+        <v>M</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -1825,8 +1735,8 @@
       <c r="E31">
         <v>1441.8</v>
       </c>
-      <c r="F31" t="s">
-        <v>16</v>
+      <c r="F31" t="str">
+        <v>C</v>
       </c>
       <c r="G31">
         <v>1.5</v>
@@ -1837,14 +1747,14 @@
       <c r="I31">
         <v>10.09</v>
       </c>
-      <c r="J31" t="s">
-        <v>17</v>
+      <c r="J31" t="str">
+        <v/>
       </c>
       <c r="K31">
-        <v>-76.9935969</v>
+        <v>-76.99365735054018</v>
       </c>
       <c r="L31">
-        <v>37.574554550000002</v>
+        <v>37.574576447301745</v>
       </c>
       <c r="M31">
         <v>224582.55</v>
@@ -1853,15 +1763,15 @@
         <v>112291.27</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32">
         <v>579513031</v>
       </c>
-      <c r="B32" t="s">
-        <v>21</v>
-      </c>
-      <c r="C32" t="s">
-        <v>24</v>
+      <c r="B32" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C32" t="str">
+        <v>M</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -1869,8 +1779,8 @@
       <c r="E32">
         <v>3990.4</v>
       </c>
-      <c r="F32" t="s">
-        <v>19</v>
+      <c r="F32" t="str">
+        <v>S</v>
       </c>
       <c r="G32">
         <v>0.5</v>
@@ -1881,14 +1791,14 @@
       <c r="I32">
         <v>12.09</v>
       </c>
-      <c r="J32" t="s">
-        <v>17</v>
+      <c r="J32" t="str">
+        <v/>
       </c>
       <c r="K32">
-        <v>-77.006987300000006</v>
+        <v>-77.0069873</v>
       </c>
       <c r="L32">
-        <v>37.575886699999998</v>
+        <v>37.5758867</v>
       </c>
       <c r="M32">
         <v>255415.96</v>
@@ -1897,15 +1807,15 @@
         <v>127707.98</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33">
         <v>579513032</v>
       </c>
-      <c r="B33" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33" t="s">
-        <v>15</v>
+      <c r="B33" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C33" t="str">
+        <v>H</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1913,8 +1823,8 @@
       <c r="E33">
         <v>2024</v>
       </c>
-      <c r="F33" t="s">
-        <v>20</v>
+      <c r="F33" t="str">
+        <v>P</v>
       </c>
       <c r="G33">
         <v>3</v>
@@ -1925,31 +1835,31 @@
       <c r="I33">
         <v>10.57</v>
       </c>
-      <c r="J33" t="s">
-        <v>17</v>
+      <c r="J33" t="str">
+        <v/>
       </c>
       <c r="K33">
-        <v>-77.004181669999994</v>
+        <v>-77.00418167</v>
       </c>
       <c r="L33">
-        <v>37.574810200000002</v>
+        <v>37.5748102</v>
       </c>
       <c r="M33">
         <v>168509.43</v>
       </c>
       <c r="N33">
-        <v>84254.720000000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+        <v>84254.72</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34">
         <v>579513033</v>
       </c>
-      <c r="B34" t="s">
-        <v>25</v>
-      </c>
-      <c r="C34" t="s">
-        <v>24</v>
+      <c r="B34" t="str">
+        <v>RES3A</v>
+      </c>
+      <c r="C34" t="str">
+        <v>M</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -1957,8 +1867,8 @@
       <c r="E34">
         <v>3170.7</v>
       </c>
-      <c r="F34" t="s">
-        <v>19</v>
+      <c r="F34" t="str">
+        <v>S</v>
       </c>
       <c r="G34">
         <v>4</v>
@@ -1967,16 +1877,16 @@
         <v>1980</v>
       </c>
       <c r="I34">
-        <v>6.3266999999999998</v>
-      </c>
-      <c r="J34" t="s">
-        <v>17</v>
+        <v>6.3267</v>
+      </c>
+      <c r="J34" t="str">
+        <v/>
       </c>
       <c r="K34">
-        <v>-76.995094989999998</v>
+        <v>-76.99509499</v>
       </c>
       <c r="L34">
-        <v>37.574441630000003</v>
+        <v>37.57444163</v>
       </c>
       <c r="M34">
         <v>290641</v>
@@ -1985,15 +1895,15 @@
         <v>145321</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="A35">
         <v>579534897</v>
       </c>
-      <c r="B35" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>15</v>
+      <c r="B35" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C35" t="str">
+        <v>H</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -2001,8 +1911,8 @@
       <c r="E35">
         <v>1271</v>
       </c>
-      <c r="F35" t="s">
-        <v>20</v>
+      <c r="F35" t="str">
+        <v>P</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -2013,14 +1923,14 @@
       <c r="I35">
         <v>12.53</v>
       </c>
-      <c r="J35" t="s">
-        <v>17</v>
+      <c r="J35" t="str">
+        <v/>
       </c>
       <c r="K35">
-        <v>-76.996458959999998</v>
+        <v>-76.99645896</v>
       </c>
       <c r="L35">
-        <v>37.577203529999998</v>
+        <v>37.57720353</v>
       </c>
       <c r="M35">
         <v>169885.84</v>
@@ -2029,15 +1939,15 @@
         <v>84942.92</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="A36">
         <v>579534898</v>
       </c>
-      <c r="B36" t="s">
-        <v>21</v>
-      </c>
-      <c r="C36" t="s">
-        <v>18</v>
+      <c r="B36" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C36" t="str">
+        <v>W</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -2045,8 +1955,8 @@
       <c r="E36">
         <v>1595.2</v>
       </c>
-      <c r="F36" t="s">
-        <v>19</v>
+      <c r="F36" t="str">
+        <v>S</v>
       </c>
       <c r="G36">
         <v>0.5</v>
@@ -2057,31 +1967,31 @@
       <c r="I36">
         <v>6.96</v>
       </c>
-      <c r="J36" t="s">
-        <v>17</v>
+      <c r="J36" t="str">
+        <v/>
       </c>
       <c r="K36">
-        <v>-76.997783889999994</v>
+        <v>-76.99778389</v>
       </c>
       <c r="L36">
-        <v>37.578822709999997</v>
+        <v>37.57882271</v>
       </c>
       <c r="M36">
-        <v>138870.01999999999</v>
+        <v>138870.02</v>
       </c>
       <c r="N36">
-        <v>69435.009999999995</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+        <v>69435.01</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37">
         <v>579534899</v>
       </c>
-      <c r="B37" t="s">
-        <v>21</v>
-      </c>
-      <c r="C37" t="s">
-        <v>18</v>
+      <c r="B37" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C37" t="str">
+        <v>W</v>
       </c>
       <c r="D37">
         <v>2</v>
@@ -2089,8 +1999,8 @@
       <c r="E37">
         <v>2413</v>
       </c>
-      <c r="F37" t="s">
-        <v>19</v>
+      <c r="F37" t="str">
+        <v>S</v>
       </c>
       <c r="G37">
         <v>0.5</v>
@@ -2101,14 +2011,14 @@
       <c r="I37">
         <v>14.62</v>
       </c>
-      <c r="J37" t="s">
-        <v>17</v>
+      <c r="J37" t="str">
+        <v/>
       </c>
       <c r="K37">
-        <v>-76.998755610000003</v>
+        <v>-76.99875561</v>
       </c>
       <c r="L37">
-        <v>37.577446299999998</v>
+        <v>37.5774463</v>
       </c>
       <c r="M37">
         <v>311493.3</v>
@@ -2117,15 +2027,15 @@
         <v>155746.65</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38">
         <v>579534905</v>
       </c>
-      <c r="B38" t="s">
-        <v>23</v>
-      </c>
-      <c r="C38" t="s">
-        <v>18</v>
+      <c r="B38" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C38" t="str">
+        <v>W</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -2133,8 +2043,8 @@
       <c r="E38">
         <v>1375</v>
       </c>
-      <c r="F38" t="s">
-        <v>19</v>
+      <c r="F38" t="str">
+        <v>S</v>
       </c>
       <c r="G38">
         <v>0.5</v>
@@ -2143,13 +2053,13 @@
         <v>1980</v>
       </c>
       <c r="I38">
-        <v>9.7200000000000006</v>
-      </c>
-      <c r="J38" t="s">
-        <v>17</v>
+        <v>9.72</v>
+      </c>
+      <c r="J38" t="str">
+        <v/>
       </c>
       <c r="K38">
-        <v>-77.002607882022872</v>
+        <v>-77.00260788202287</v>
       </c>
       <c r="L38">
         <v>37.58002683078432</v>
@@ -2161,15 +2071,15 @@
         <v>70656.45</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39">
         <v>579534906</v>
       </c>
-      <c r="B39" t="s">
-        <v>21</v>
-      </c>
-      <c r="C39" t="s">
-        <v>24</v>
+      <c r="B39" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C39" t="str">
+        <v>M</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -2177,8 +2087,8 @@
       <c r="E39">
         <v>1956</v>
       </c>
-      <c r="F39" t="s">
-        <v>16</v>
+      <c r="F39" t="str">
+        <v>C</v>
       </c>
       <c r="G39">
         <v>2.5</v>
@@ -2189,40 +2099,40 @@
       <c r="I39">
         <v>10.15</v>
       </c>
-      <c r="J39" t="s">
-        <v>17</v>
+      <c r="J39" t="str">
+        <v/>
       </c>
       <c r="K39">
-        <v>-77.002594470977797</v>
+        <v>-77.0025944709778</v>
       </c>
       <c r="L39">
         <v>37.579399759391364</v>
       </c>
       <c r="M39">
-        <v>147409.95000000001</v>
+        <v>147409.95</v>
       </c>
       <c r="N39">
         <v>73704.98</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40">
         <v>579534907</v>
       </c>
-      <c r="B40" t="s">
-        <v>14</v>
-      </c>
-      <c r="C40" t="s">
-        <v>15</v>
+      <c r="B40" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C40" t="str">
+        <v>H</v>
       </c>
       <c r="D40">
         <v>1</v>
       </c>
       <c r="E40">
-        <v>1165.5999999999999</v>
-      </c>
-      <c r="F40" t="s">
-        <v>20</v>
+        <v>1165.6</v>
+      </c>
+      <c r="F40" t="str">
+        <v>P</v>
       </c>
       <c r="G40">
         <v>2</v>
@@ -2233,14 +2143,14 @@
       <c r="I40">
         <v>9.24</v>
       </c>
-      <c r="J40" t="s">
-        <v>17</v>
+      <c r="J40" t="str">
+        <v/>
       </c>
       <c r="K40">
-        <v>-77.001480959999995</v>
+        <v>-77.00148096</v>
       </c>
       <c r="L40">
-        <v>37.579149149999999</v>
+        <v>37.57914915</v>
       </c>
       <c r="M40">
         <v>190356.2</v>
@@ -2249,15 +2159,15 @@
         <v>95178.1</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41">
         <v>579536184</v>
       </c>
-      <c r="B41" t="s">
-        <v>21</v>
-      </c>
-      <c r="C41" t="s">
-        <v>24</v>
+      <c r="B41" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C41" t="str">
+        <v>M</v>
       </c>
       <c r="D41">
         <v>2</v>
@@ -2265,8 +2175,8 @@
       <c r="E41">
         <v>3858</v>
       </c>
-      <c r="F41" t="s">
-        <v>19</v>
+      <c r="F41" t="str">
+        <v>S</v>
       </c>
       <c r="G41">
         <v>0.5</v>
@@ -2277,11 +2187,11 @@
       <c r="I41">
         <v>6</v>
       </c>
-      <c r="J41" t="s">
-        <v>17</v>
+      <c r="J41" t="str">
+        <v/>
       </c>
       <c r="K41">
-        <v>-76.993297049999995</v>
+        <v>-76.99329705</v>
       </c>
       <c r="L41">
         <v>37.57617407</v>
@@ -2293,15 +2203,15 @@
         <v>200307.7</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42">
         <v>579536842</v>
       </c>
-      <c r="B42" t="s">
-        <v>21</v>
-      </c>
-      <c r="C42" t="s">
-        <v>18</v>
+      <c r="B42" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C42" t="str">
+        <v>W</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -2309,8 +2219,8 @@
       <c r="E42">
         <v>1462</v>
       </c>
-      <c r="F42" t="s">
-        <v>16</v>
+      <c r="F42" t="str">
+        <v>C</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -2321,14 +2231,14 @@
       <c r="I42">
         <v>11.17</v>
       </c>
-      <c r="J42" t="s">
-        <v>17</v>
+      <c r="J42" t="str">
+        <v/>
       </c>
       <c r="K42">
-        <v>-77.008948624134078</v>
+        <v>-77.00894862413408</v>
       </c>
       <c r="L42">
-        <v>37.579935427486348</v>
+        <v>37.57993542748635</v>
       </c>
       <c r="M42">
         <v>87561.3</v>
@@ -2337,15 +2247,15 @@
         <v>43780.65</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43">
         <v>579536843</v>
       </c>
-      <c r="B43" t="s">
-        <v>21</v>
-      </c>
-      <c r="C43" t="s">
-        <v>24</v>
+      <c r="B43" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C43" t="str">
+        <v>M</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -2353,8 +2263,8 @@
       <c r="E43">
         <v>1202</v>
       </c>
-      <c r="F43" t="s">
-        <v>26</v>
+      <c r="F43" t="str">
+        <v>B</v>
       </c>
       <c r="G43">
         <v>2</v>
@@ -2363,16 +2273,16 @@
         <v>1980</v>
       </c>
       <c r="I43">
-        <v>10.074299999999999</v>
-      </c>
-      <c r="J43" t="s">
-        <v>17</v>
+        <v>10.0743</v>
+      </c>
+      <c r="J43" t="str">
+        <v/>
       </c>
       <c r="K43">
-        <v>-77.010799348354354</v>
+        <v>-77.01079934835435</v>
       </c>
       <c r="L43">
-        <v>37.581489268290973</v>
+        <v>37.58148926829097</v>
       </c>
       <c r="M43">
         <v>258203.36</v>
@@ -2381,15 +2291,15 @@
         <v>129101.68</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44">
         <v>579536844</v>
       </c>
-      <c r="B44" t="s">
-        <v>14</v>
-      </c>
-      <c r="C44" t="s">
-        <v>15</v>
+      <c r="B44" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C44" t="str">
+        <v>H</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -2397,8 +2307,8 @@
       <c r="E44">
         <v>2250</v>
       </c>
-      <c r="F44" t="s">
-        <v>20</v>
+      <c r="F44" t="str">
+        <v>P</v>
       </c>
       <c r="G44">
         <v>2</v>
@@ -2409,31 +2319,31 @@
       <c r="I44">
         <v>17.5</v>
       </c>
-      <c r="J44" t="s">
-        <v>17</v>
+      <c r="J44" t="str">
+        <v/>
       </c>
       <c r="K44">
-        <v>-77.009839117527022</v>
+        <v>-77.00983911752702</v>
       </c>
       <c r="L44">
         <v>37.582345886221525</v>
       </c>
       <c r="M44">
-        <v>724184.03</v>
+        <v>224184.03</v>
       </c>
       <c r="N44">
         <v>362092.02</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="A45">
         <v>579537054</v>
       </c>
-      <c r="B45" t="s">
-        <v>21</v>
-      </c>
-      <c r="C45" t="s">
-        <v>18</v>
+      <c r="B45" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C45" t="str">
+        <v>W</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -2441,8 +2351,8 @@
       <c r="E45">
         <v>1765</v>
       </c>
-      <c r="F45" t="s">
-        <v>19</v>
+      <c r="F45" t="str">
+        <v>S</v>
       </c>
       <c r="G45">
         <v>0.5</v>
@@ -2453,14 +2363,14 @@
       <c r="I45">
         <v>11.23</v>
       </c>
-      <c r="J45" t="s">
-        <v>17</v>
+      <c r="J45" t="str">
+        <v/>
       </c>
       <c r="K45">
-        <v>-77.007752999999994</v>
+        <v>-77.007753</v>
       </c>
       <c r="L45">
-        <v>37.580795000000002</v>
+        <v>37.580795</v>
       </c>
       <c r="M45">
         <v>149746.78</v>
@@ -2469,15 +2379,15 @@
         <v>74873.39</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="A46">
         <v>579537067</v>
       </c>
-      <c r="B46" t="s">
-        <v>21</v>
-      </c>
-      <c r="C46" t="s">
-        <v>18</v>
+      <c r="B46" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C46" t="str">
+        <v>W</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -2485,8 +2395,8 @@
       <c r="E46">
         <v>1576.6</v>
       </c>
-      <c r="F46" t="s">
-        <v>19</v>
+      <c r="F46" t="str">
+        <v>S</v>
       </c>
       <c r="G46">
         <v>0.5</v>
@@ -2497,14 +2407,14 @@
       <c r="I46">
         <v>10.06</v>
       </c>
-      <c r="J46" t="s">
-        <v>17</v>
+      <c r="J46" t="str">
+        <v/>
       </c>
       <c r="K46">
-        <v>-77.011919000000006</v>
+        <v>-77.011919</v>
       </c>
       <c r="L46">
-        <v>37.580516000000003</v>
+        <v>37.580516</v>
       </c>
       <c r="M46">
         <v>137875.75</v>
@@ -2513,15 +2423,15 @@
         <v>68937.87</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="A47">
         <v>10000001</v>
       </c>
-      <c r="B47" t="s">
-        <v>21</v>
-      </c>
-      <c r="C47" t="s">
-        <v>24</v>
+      <c r="B47" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C47" t="str">
+        <v>M</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -2529,8 +2439,8 @@
       <c r="E47">
         <v>1019</v>
       </c>
-      <c r="F47" t="s">
-        <v>16</v>
+      <c r="F47" t="str">
+        <v>C</v>
       </c>
       <c r="G47">
         <v>4</v>
@@ -2541,11 +2451,11 @@
       <c r="I47">
         <v>11</v>
       </c>
-      <c r="J47" t="s">
-        <v>17</v>
+      <c r="J47" t="str">
+        <v/>
       </c>
       <c r="K47">
-        <v>-76.999695003032699</v>
+        <v>-76.9996950030327</v>
       </c>
       <c r="L47">
         <v>37.573396612081154</v>
@@ -2557,15 +2467,15 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="A48">
         <v>10000002</v>
       </c>
-      <c r="B48" t="s">
-        <v>14</v>
-      </c>
-      <c r="C48" t="s">
-        <v>15</v>
+      <c r="B48" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C48" t="str">
+        <v>H</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -2573,8 +2483,8 @@
       <c r="E48">
         <v>1362</v>
       </c>
-      <c r="F48" t="s">
-        <v>20</v>
+      <c r="F48" t="str">
+        <v>P</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -2583,16 +2493,16 @@
         <v>1980</v>
       </c>
       <c r="I48">
-        <v>9.4700000000000006</v>
-      </c>
-      <c r="J48" t="s">
-        <v>17</v>
+        <v>9.47</v>
+      </c>
+      <c r="J48" t="str">
+        <v/>
       </c>
       <c r="K48">
-        <v>-77.003503739833846</v>
+        <v>-77.00350373983385</v>
       </c>
       <c r="L48">
-        <v>37.578728043159273</v>
+        <v>37.57872804315927</v>
       </c>
       <c r="M48">
         <v>207278</v>
@@ -2601,15 +2511,15 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="A49">
         <v>10000003</v>
       </c>
-      <c r="B49" t="s">
-        <v>14</v>
-      </c>
-      <c r="C49" t="s">
-        <v>15</v>
+      <c r="B49" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C49" t="str">
+        <v>H</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -2617,8 +2527,8 @@
       <c r="E49">
         <v>1366</v>
       </c>
-      <c r="F49" t="s">
-        <v>20</v>
+      <c r="F49" t="str">
+        <v>P</v>
       </c>
       <c r="G49">
         <v>3</v>
@@ -2629,14 +2539,14 @@
       <c r="I49">
         <v>16</v>
       </c>
-      <c r="J49" t="s">
-        <v>17</v>
+      <c r="J49" t="str">
+        <v/>
       </c>
       <c r="K49">
-        <v>-77.005335688591018</v>
+        <v>-77.00533568859102</v>
       </c>
       <c r="L49">
-        <v>37.580509353311491</v>
+        <v>37.58050935331149</v>
       </c>
       <c r="M49">
         <v>207278</v>
@@ -2645,15 +2555,15 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="A50">
         <v>10000004</v>
       </c>
-      <c r="B50" t="s">
-        <v>23</v>
-      </c>
-      <c r="C50" t="s">
-        <v>18</v>
+      <c r="B50" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C50" t="str">
+        <v>W</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -2661,8 +2571,8 @@
       <c r="E50">
         <v>3051</v>
       </c>
-      <c r="F50" t="s">
-        <v>19</v>
+      <c r="F50" t="str">
+        <v>S</v>
       </c>
       <c r="G50">
         <v>0.5</v>
@@ -2673,11 +2583,11 @@
       <c r="I50">
         <v>11.67</v>
       </c>
-      <c r="J50" t="s">
-        <v>17</v>
+      <c r="J50" t="str">
+        <v/>
       </c>
       <c r="K50">
-        <v>-77.008499099999995</v>
+        <v>-77.0084991</v>
       </c>
       <c r="L50">
         <v>37.5807492</v>
@@ -2689,15 +2599,15 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="A51">
         <v>10000005</v>
       </c>
-      <c r="B51" t="s">
-        <v>21</v>
-      </c>
-      <c r="C51" t="s">
-        <v>18</v>
+      <c r="B51" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C51" t="str">
+        <v>W</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -2705,8 +2615,8 @@
       <c r="E51">
         <v>859</v>
       </c>
-      <c r="F51" t="s">
-        <v>19</v>
+      <c r="F51" t="str">
+        <v>S</v>
       </c>
       <c r="G51">
         <v>0.5</v>
@@ -2717,14 +2627,14 @@
       <c r="I51">
         <v>17.28</v>
       </c>
-      <c r="J51" t="s">
-        <v>17</v>
+      <c r="J51" t="str">
+        <v/>
       </c>
       <c r="K51">
-        <v>-77.009181976318374</v>
+        <v>-77.00918197631837</v>
       </c>
       <c r="L51">
-        <v>37.582382021252577</v>
+        <v>37.58238202125258</v>
       </c>
       <c r="M51">
         <v>178578</v>
@@ -2733,15 +2643,15 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="A52">
         <v>10000006</v>
       </c>
-      <c r="B52" t="s">
-        <v>14</v>
-      </c>
-      <c r="C52" t="s">
-        <v>15</v>
+      <c r="B52" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C52" t="str">
+        <v>H</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2749,8 +2659,8 @@
       <c r="E52">
         <v>952</v>
       </c>
-      <c r="F52" t="s">
-        <v>20</v>
+      <c r="F52" t="str">
+        <v>P</v>
       </c>
       <c r="G52">
         <v>3</v>
@@ -2761,14 +2671,14 @@
       <c r="I52">
         <v>12.05</v>
       </c>
-      <c r="J52" t="s">
-        <v>17</v>
+      <c r="J52" t="str">
+        <v/>
       </c>
       <c r="K52">
-        <v>-77.012489140033736</v>
+        <v>-77.01248914003374</v>
       </c>
       <c r="L52">
-        <v>37.578932109490879</v>
+        <v>37.57893210949088</v>
       </c>
       <c r="M52">
         <v>207278</v>
@@ -2777,15 +2687,15 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="A53">
         <v>10000007</v>
       </c>
-      <c r="B53" t="s">
-        <v>14</v>
-      </c>
-      <c r="C53" t="s">
-        <v>18</v>
+      <c r="B53" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C53" t="str">
+        <v>W</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2793,8 +2703,8 @@
       <c r="E53">
         <v>1369</v>
       </c>
-      <c r="F53" t="s">
-        <v>20</v>
+      <c r="F53" t="str">
+        <v>P</v>
       </c>
       <c r="G53">
         <v>2</v>
@@ -2805,14 +2715,14 @@
       <c r="I53">
         <v>12.13</v>
       </c>
-      <c r="J53" t="s">
-        <v>17</v>
+      <c r="J53" t="str">
+        <v/>
       </c>
       <c r="K53">
-        <v>-77.013352811336532</v>
+        <v>-77.01335281133653</v>
       </c>
       <c r="L53">
-        <v>37.578009555165558</v>
+        <v>37.57800955516556</v>
       </c>
       <c r="M53">
         <v>178578</v>
@@ -2821,15 +2731,15 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="A54">
         <v>10000008</v>
       </c>
-      <c r="B54" t="s">
-        <v>14</v>
-      </c>
-      <c r="C54" t="s">
-        <v>15</v>
+      <c r="B54" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C54" t="str">
+        <v>H</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2837,8 +2747,8 @@
       <c r="E54">
         <v>2752</v>
       </c>
-      <c r="F54" t="s">
-        <v>20</v>
+      <c r="F54" t="str">
+        <v>P</v>
       </c>
       <c r="G54">
         <v>2.5</v>
@@ -2849,14 +2759,14 @@
       <c r="I54">
         <v>13</v>
       </c>
-      <c r="J54" t="s">
-        <v>17</v>
+      <c r="J54" t="str">
+        <v/>
       </c>
       <c r="K54">
-        <v>-77.000909100000001</v>
+        <v>-77.0009091</v>
       </c>
       <c r="L54">
-        <v>35.574165299999997</v>
+        <v>35.5741653</v>
       </c>
       <c r="M54">
         <v>207278</v>
@@ -2865,15 +2775,15 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="A55">
         <v>10000009</v>
       </c>
-      <c r="B55" t="s">
-        <v>14</v>
-      </c>
-      <c r="C55" t="s">
-        <v>15</v>
+      <c r="B55" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C55" t="str">
+        <v>H</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2881,8 +2791,8 @@
       <c r="E55">
         <v>1058</v>
       </c>
-      <c r="F55" t="s">
-        <v>20</v>
+      <c r="F55" t="str">
+        <v>P</v>
       </c>
       <c r="G55">
         <v>0.5</v>
@@ -2893,14 +2803,14 @@
       <c r="I55">
         <v>9</v>
       </c>
-      <c r="J55" t="s">
-        <v>17</v>
+      <c r="J55" t="str">
+        <v/>
       </c>
       <c r="K55">
-        <v>-76.999274299999996</v>
+        <v>-76.9992743</v>
       </c>
       <c r="L55">
-        <v>37.569889600000003</v>
+        <v>37.5698896</v>
       </c>
       <c r="M55">
         <v>207278</v>
@@ -2909,15 +2819,15 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="A56">
         <v>10000010</v>
       </c>
-      <c r="B56" t="s">
-        <v>14</v>
-      </c>
-      <c r="C56" t="s">
-        <v>15</v>
+      <c r="B56" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C56" t="str">
+        <v>H</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2925,8 +2835,8 @@
       <c r="E56">
         <v>1339</v>
       </c>
-      <c r="F56" t="s">
-        <v>20</v>
+      <c r="F56" t="str">
+        <v>P</v>
       </c>
       <c r="G56">
         <v>0.5</v>
@@ -2937,14 +2847,14 @@
       <c r="I56">
         <v>9</v>
       </c>
-      <c r="J56" t="s">
-        <v>17</v>
+      <c r="J56" t="str">
+        <v/>
       </c>
       <c r="K56">
-        <v>-76.999095800000006</v>
+        <v>-76.9990958</v>
       </c>
       <c r="L56">
-        <v>37.569559699999999</v>
+        <v>37.5695597</v>
       </c>
       <c r="M56">
         <v>207278</v>
@@ -2953,15 +2863,15 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="A57">
         <v>10000011</v>
       </c>
-      <c r="B57" t="s">
-        <v>21</v>
-      </c>
-      <c r="C57" t="s">
-        <v>18</v>
+      <c r="B57" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C57" t="str">
+        <v>W</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -2969,8 +2879,8 @@
       <c r="E57">
         <v>1594</v>
       </c>
-      <c r="F57" t="s">
-        <v>19</v>
+      <c r="F57" t="str">
+        <v>S</v>
       </c>
       <c r="G57">
         <v>0.5</v>
@@ -2981,14 +2891,14 @@
       <c r="I57">
         <v>7.98</v>
       </c>
-      <c r="J57" t="s">
-        <v>17</v>
+      <c r="J57" t="str">
+        <v/>
       </c>
       <c r="K57">
-        <v>-76.991307899999995</v>
+        <v>-76.9913079</v>
       </c>
       <c r="L57">
-        <v>37.574853400000002</v>
+        <v>37.5748534</v>
       </c>
       <c r="M57">
         <v>270574</v>
@@ -2997,15 +2907,15 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="A58">
         <v>10000012</v>
       </c>
-      <c r="B58" t="s">
-        <v>21</v>
-      </c>
-      <c r="C58" t="s">
-        <v>18</v>
+      <c r="B58" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C58" t="str">
+        <v>W</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -3013,8 +2923,8 @@
       <c r="E58">
         <v>1567</v>
       </c>
-      <c r="F58" t="s">
-        <v>16</v>
+      <c r="F58" t="str">
+        <v>C</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -3025,14 +2935,14 @@
       <c r="I58">
         <v>12.22</v>
       </c>
-      <c r="J58" t="s">
-        <v>17</v>
+      <c r="J58" t="str">
+        <v/>
       </c>
       <c r="K58">
-        <v>-77.004171799999995</v>
+        <v>-77.0041718</v>
       </c>
       <c r="L58">
-        <v>37.575179300000002</v>
+        <v>37.5751793</v>
       </c>
       <c r="M58">
         <v>270574</v>
@@ -3041,15 +2951,15 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="A59">
         <v>10000013</v>
       </c>
-      <c r="B59" t="s">
-        <v>23</v>
-      </c>
-      <c r="C59" t="s">
-        <v>18</v>
+      <c r="B59" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C59" t="str">
+        <v>W</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -3057,8 +2967,8 @@
       <c r="E59">
         <v>903</v>
       </c>
-      <c r="F59" t="s">
-        <v>20</v>
+      <c r="F59" t="str">
+        <v>P</v>
       </c>
       <c r="G59">
         <v>2</v>
@@ -3069,11 +2979,11 @@
       <c r="I59">
         <v>12</v>
       </c>
-      <c r="J59" t="s">
-        <v>17</v>
+      <c r="J59" t="str">
+        <v/>
       </c>
       <c r="K59">
-        <v>-77.001787126064315</v>
+        <v>-77.00178712606431</v>
       </c>
       <c r="L59">
         <v>37.575673358414306</v>
@@ -3085,15 +2995,15 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60">
       <c r="A60">
         <v>10000014</v>
       </c>
-      <c r="B60" t="s">
-        <v>21</v>
-      </c>
-      <c r="C60" t="s">
-        <v>18</v>
+      <c r="B60" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C60" t="str">
+        <v>W</v>
       </c>
       <c r="D60">
         <v>2</v>
@@ -3101,8 +3011,8 @@
       <c r="E60">
         <v>1129</v>
       </c>
-      <c r="F60" t="s">
-        <v>19</v>
+      <c r="F60" t="str">
+        <v>S</v>
       </c>
       <c r="G60">
         <v>0.5</v>
@@ -3113,14 +3023,14 @@
       <c r="I60">
         <v>12.38</v>
       </c>
-      <c r="J60" t="s">
-        <v>17</v>
+      <c r="J60" t="str">
+        <v/>
       </c>
       <c r="K60">
-        <v>-77.004660900000005</v>
+        <v>-77.0046609</v>
       </c>
       <c r="L60">
-        <v>37.578172899999998</v>
+        <v>37.5781729</v>
       </c>
       <c r="M60">
         <v>270574</v>
@@ -3129,15 +3039,15 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61">
       <c r="A61">
         <v>10000015</v>
       </c>
-      <c r="B61" t="s">
-        <v>14</v>
-      </c>
-      <c r="C61" t="s">
-        <v>15</v>
+      <c r="B61" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C61" t="str">
+        <v>H</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -3145,8 +3055,8 @@
       <c r="E61">
         <v>1015</v>
       </c>
-      <c r="F61" t="s">
-        <v>20</v>
+      <c r="F61" t="str">
+        <v>P</v>
       </c>
       <c r="G61">
         <v>3</v>
@@ -3157,14 +3067,14 @@
       <c r="I61">
         <v>9.26</v>
       </c>
-      <c r="J61" t="s">
-        <v>17</v>
+      <c r="J61" t="str">
+        <v/>
       </c>
       <c r="K61">
-        <v>-77.004142799999997</v>
+        <v>-77.0041428</v>
       </c>
       <c r="L61">
-        <v>37.578917099999998</v>
+        <v>37.5789171</v>
       </c>
       <c r="M61">
         <v>207278</v>
@@ -3173,15 +3083,15 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62">
       <c r="A62">
         <v>10001</v>
       </c>
-      <c r="B62" t="s">
-        <v>27</v>
-      </c>
-      <c r="C62" t="s">
-        <v>18</v>
+      <c r="B62" t="str">
+        <v>COM8</v>
+      </c>
+      <c r="C62" t="str">
+        <v>W</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -3189,23 +3099,23 @@
       <c r="E62">
         <v>8541</v>
       </c>
-      <c r="F62" t="s">
-        <v>19</v>
+      <c r="F62" t="str">
+        <v>S</v>
       </c>
       <c r="G62">
         <v>0.5</v>
       </c>
-      <c r="H62" t="s">
-        <v>17</v>
+      <c r="H62" t="str">
+        <v/>
       </c>
       <c r="I62">
         <v>10.01</v>
       </c>
-      <c r="J62" t="s">
-        <v>17</v>
+      <c r="J62" t="str">
+        <v/>
       </c>
       <c r="K62">
-        <v>-77.000888586044326</v>
+        <v>-77.00088858604433</v>
       </c>
       <c r="L62">
         <v>37.57556919506888</v>
@@ -3217,15 +3127,15 @@
         <v>171172</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63">
       <c r="A63">
         <v>10002</v>
       </c>
-      <c r="B63" t="s">
-        <v>27</v>
-      </c>
-      <c r="C63" t="s">
-        <v>18</v>
+      <c r="B63" t="str">
+        <v>COM8</v>
+      </c>
+      <c r="C63" t="str">
+        <v>W</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -3233,26 +3143,26 @@
       <c r="E63">
         <v>4665</v>
       </c>
-      <c r="F63" t="s">
-        <v>19</v>
+      <c r="F63" t="str">
+        <v>S</v>
       </c>
       <c r="G63">
         <v>0.5</v>
       </c>
-      <c r="H63" t="s">
-        <v>17</v>
+      <c r="H63" t="str">
+        <v/>
       </c>
       <c r="I63">
         <v>12.48</v>
       </c>
-      <c r="J63" t="s">
-        <v>17</v>
+      <c r="J63" t="str">
+        <v/>
       </c>
       <c r="K63">
-        <v>-77.002066075801864</v>
+        <v>-77.00206607580186</v>
       </c>
       <c r="L63">
-        <v>37.575609584954812</v>
+        <v>37.57560958495481</v>
       </c>
       <c r="M63">
         <v>262820</v>
@@ -3261,15 +3171,15 @@
         <v>131410</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64">
       <c r="A64">
         <v>10003</v>
       </c>
-      <c r="B64" t="s">
-        <v>23</v>
-      </c>
-      <c r="C64" t="s">
-        <v>18</v>
+      <c r="B64" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C64" t="str">
+        <v>W</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -3277,23 +3187,23 @@
       <c r="E64">
         <v>559</v>
       </c>
-      <c r="F64" t="s">
-        <v>20</v>
+      <c r="F64" t="str">
+        <v>P</v>
       </c>
       <c r="G64">
         <v>0.5</v>
       </c>
-      <c r="H64" t="s">
-        <v>17</v>
+      <c r="H64" t="str">
+        <v/>
       </c>
       <c r="I64">
         <v>4.17</v>
       </c>
-      <c r="J64" t="s">
-        <v>17</v>
+      <c r="J64" t="str">
+        <v/>
       </c>
       <c r="K64">
-        <v>-76.992273330688491</v>
+        <v>-76.99227333068849</v>
       </c>
       <c r="L64">
         <v>37.575728628701675</v>
@@ -3305,15 +3215,15 @@
         <v>89583</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65">
       <c r="A65">
         <v>10004</v>
       </c>
-      <c r="B65" t="s">
-        <v>23</v>
-      </c>
-      <c r="C65" t="s">
-        <v>18</v>
+      <c r="B65" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C65" t="str">
+        <v>W</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -3321,23 +3231,23 @@
       <c r="E65">
         <v>1473</v>
       </c>
-      <c r="F65" t="s">
-        <v>19</v>
+      <c r="F65" t="str">
+        <v>S</v>
       </c>
       <c r="G65">
         <v>0.5</v>
       </c>
-      <c r="H65" t="s">
-        <v>17</v>
+      <c r="H65" t="str">
+        <v/>
       </c>
       <c r="I65">
         <v>4.49</v>
       </c>
-      <c r="J65" t="s">
-        <v>17</v>
+      <c r="J65" t="str">
+        <v/>
       </c>
       <c r="K65">
-        <v>-76.999686956405654</v>
+        <v>-76.99968695640565</v>
       </c>
       <c r="L65">
         <v>37.57147269654066</v>
@@ -3349,15 +3259,15 @@
         <v>98945</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66">
       <c r="A66">
         <v>10005</v>
       </c>
-      <c r="B66" t="s">
-        <v>23</v>
-      </c>
-      <c r="C66" t="s">
-        <v>18</v>
+      <c r="B66" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C66" t="str">
+        <v>W</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -3365,26 +3275,26 @@
       <c r="E66">
         <v>2105</v>
       </c>
-      <c r="F66" t="s">
-        <v>19</v>
+      <c r="F66" t="str">
+        <v>S</v>
       </c>
       <c r="G66">
         <v>0.5</v>
       </c>
-      <c r="H66" t="s">
-        <v>17</v>
+      <c r="H66" t="str">
+        <v/>
       </c>
       <c r="I66">
         <v>7.54</v>
       </c>
-      <c r="J66" t="s">
-        <v>17</v>
+      <c r="J66" t="str">
+        <v/>
       </c>
       <c r="K66">
-        <v>-76.999268531799331</v>
+        <v>-76.99926853179933</v>
       </c>
       <c r="L66">
-        <v>37.573528414420608</v>
+        <v>37.57352841442061</v>
       </c>
       <c r="M66">
         <v>210837</v>
@@ -3393,15 +3303,15 @@
         <v>105419</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67">
       <c r="A67">
         <v>10007</v>
       </c>
-      <c r="B67" t="s">
-        <v>23</v>
-      </c>
-      <c r="C67" t="s">
-        <v>18</v>
+      <c r="B67" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C67" t="str">
+        <v>W</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -3409,26 +3319,26 @@
       <c r="E67">
         <v>930</v>
       </c>
-      <c r="F67" t="s">
-        <v>19</v>
+      <c r="F67" t="str">
+        <v>S</v>
       </c>
       <c r="G67">
         <v>0.5</v>
       </c>
-      <c r="H67" t="s">
-        <v>17</v>
+      <c r="H67" t="str">
+        <v/>
       </c>
       <c r="I67">
         <v>7.18</v>
       </c>
-      <c r="J67" t="s">
-        <v>17</v>
+      <c r="J67" t="str">
+        <v/>
       </c>
       <c r="K67">
         <v>-76.99765115976335</v>
       </c>
       <c r="L67">
-        <v>37.574187422618898</v>
+        <v>37.5741874226189</v>
       </c>
       <c r="M67">
         <v>186766</v>
@@ -3437,15 +3347,15 @@
         <v>93383</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68">
       <c r="A68">
         <v>10008</v>
       </c>
-      <c r="B68" t="s">
-        <v>21</v>
-      </c>
-      <c r="C68" t="s">
-        <v>18</v>
+      <c r="B68" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C68" t="str">
+        <v>W</v>
       </c>
       <c r="D68">
         <v>2</v>
@@ -3453,26 +3363,26 @@
       <c r="E68">
         <v>763</v>
       </c>
-      <c r="F68" t="s">
-        <v>16</v>
+      <c r="F68" t="str">
+        <v>C</v>
       </c>
       <c r="G68">
         <v>1</v>
       </c>
-      <c r="H68" t="s">
-        <v>17</v>
+      <c r="H68" t="str">
+        <v/>
       </c>
       <c r="I68">
         <v>7</v>
       </c>
-      <c r="J68" t="s">
-        <v>17</v>
+      <c r="J68" t="str">
+        <v/>
       </c>
       <c r="K68">
-        <v>-76.997519731521621</v>
+        <v>-76.99751973152162</v>
       </c>
       <c r="L68">
-        <v>37.574372369033007</v>
+        <v>37.57437236903301</v>
       </c>
       <c r="M68">
         <v>198976</v>
@@ -3481,15 +3391,15 @@
         <v>99488</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69">
       <c r="A69">
         <v>10009</v>
       </c>
-      <c r="B69" t="s">
-        <v>23</v>
-      </c>
-      <c r="C69" t="s">
-        <v>18</v>
+      <c r="B69" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C69" t="str">
+        <v>W</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -3497,26 +3407,26 @@
       <c r="E69">
         <v>2153</v>
       </c>
-      <c r="F69" t="s">
-        <v>19</v>
+      <c r="F69" t="str">
+        <v>S</v>
       </c>
       <c r="G69">
         <v>0.5</v>
       </c>
-      <c r="H69" t="s">
-        <v>17</v>
+      <c r="H69" t="str">
+        <v/>
       </c>
       <c r="I69">
         <v>6.02</v>
       </c>
-      <c r="J69" t="s">
-        <v>17</v>
+      <c r="J69" t="str">
+        <v/>
       </c>
       <c r="K69">
-        <v>-76.997648477554321</v>
+        <v>-76.99764847755432</v>
       </c>
       <c r="L69">
-        <v>37.573953581667688</v>
+        <v>37.57395358166769</v>
       </c>
       <c r="M69">
         <v>211820</v>
@@ -3525,15 +3435,15 @@
         <v>105910</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70">
       <c r="A70">
         <v>10010</v>
       </c>
-      <c r="B70" t="s">
-        <v>23</v>
-      </c>
-      <c r="C70" t="s">
-        <v>18</v>
+      <c r="B70" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C70" t="str">
+        <v>W</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -3541,26 +3451,26 @@
       <c r="E70">
         <v>939</v>
       </c>
-      <c r="F70" t="s">
-        <v>19</v>
+      <c r="F70" t="str">
+        <v>S</v>
       </c>
       <c r="G70">
         <v>0.5</v>
       </c>
-      <c r="H70" t="s">
-        <v>17</v>
+      <c r="H70" t="str">
+        <v/>
       </c>
       <c r="I70">
         <v>6.03</v>
       </c>
-      <c r="J70" t="s">
-        <v>17</v>
+      <c r="J70" t="str">
+        <v/>
       </c>
       <c r="K70">
-        <v>-76.994963586330428</v>
+        <v>-76.99496358633043</v>
       </c>
       <c r="L70">
-        <v>37.574274581331053</v>
+        <v>37.57427458133105</v>
       </c>
       <c r="M70">
         <v>186951</v>
@@ -3569,15 +3479,15 @@
         <v>93476</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71">
       <c r="A71">
         <v>10011</v>
       </c>
-      <c r="B71" t="s">
-        <v>23</v>
-      </c>
-      <c r="C71" t="s">
-        <v>18</v>
+      <c r="B71" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C71" t="str">
+        <v>W</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -3585,26 +3495,26 @@
       <c r="E71">
         <v>992</v>
       </c>
-      <c r="F71" t="s">
-        <v>19</v>
+      <c r="F71" t="str">
+        <v>S</v>
       </c>
       <c r="G71">
         <v>0.5</v>
       </c>
-      <c r="H71" t="s">
-        <v>17</v>
+      <c r="H71" t="str">
+        <v/>
       </c>
       <c r="I71">
         <v>4.33</v>
       </c>
-      <c r="J71" t="s">
-        <v>17</v>
+      <c r="J71" t="str">
+        <v/>
       </c>
       <c r="K71">
-        <v>-76.992839276790619</v>
+        <v>-76.99283927679062</v>
       </c>
       <c r="L71">
-        <v>37.574183170971793</v>
+        <v>37.57418317097179</v>
       </c>
       <c r="M71">
         <v>188036</v>
@@ -3613,15 +3523,15 @@
         <v>94018</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72">
       <c r="A72">
         <v>10012</v>
       </c>
-      <c r="B72" t="s">
-        <v>23</v>
-      </c>
-      <c r="C72" t="s">
-        <v>18</v>
+      <c r="B72" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C72" t="str">
+        <v>W</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -3629,23 +3539,23 @@
       <c r="E72">
         <v>789</v>
       </c>
-      <c r="F72" t="s">
-        <v>19</v>
+      <c r="F72" t="str">
+        <v>S</v>
       </c>
       <c r="G72">
         <v>0.5</v>
       </c>
-      <c r="H72" t="s">
-        <v>17</v>
+      <c r="H72" t="str">
+        <v/>
       </c>
       <c r="I72">
         <v>5.9</v>
       </c>
-      <c r="J72" t="s">
-        <v>17</v>
+      <c r="J72" t="str">
+        <v/>
       </c>
       <c r="K72">
-        <v>-76.993032395839705</v>
+        <v>-76.9930323958397</v>
       </c>
       <c r="L72">
         <v>37.574317097739005</v>
@@ -3657,15 +3567,15 @@
         <v>91939</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73">
       <c r="A73">
         <v>10013</v>
       </c>
-      <c r="B73" t="s">
-        <v>23</v>
-      </c>
-      <c r="C73" t="s">
-        <v>18</v>
+      <c r="B73" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C73" t="str">
+        <v>W</v>
       </c>
       <c r="D73">
         <v>2</v>
@@ -3673,23 +3583,23 @@
       <c r="E73">
         <v>1692</v>
       </c>
-      <c r="F73" t="s">
-        <v>19</v>
+      <c r="F73" t="str">
+        <v>S</v>
       </c>
       <c r="G73">
         <v>0.5</v>
       </c>
-      <c r="H73" t="s">
-        <v>17</v>
+      <c r="H73" t="str">
+        <v/>
       </c>
       <c r="I73">
         <v>7.8</v>
       </c>
-      <c r="J73" t="s">
-        <v>17</v>
+      <c r="J73" t="str">
+        <v/>
       </c>
       <c r="K73">
-        <v>-76.994150876998901</v>
+        <v>-76.9941508769989</v>
       </c>
       <c r="L73">
         <v>37.575654226382184</v>
@@ -3701,15 +3611,15 @@
         <v>118519</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74">
       <c r="A74">
         <v>10014</v>
       </c>
-      <c r="B74" t="s">
-        <v>23</v>
-      </c>
-      <c r="C74" t="s">
-        <v>18</v>
+      <c r="B74" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C74" t="str">
+        <v>W</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -3717,26 +3627,26 @@
       <c r="E74">
         <v>675</v>
       </c>
-      <c r="F74" t="s">
-        <v>20</v>
+      <c r="F74" t="str">
+        <v>P</v>
       </c>
       <c r="G74">
         <v>0.5</v>
       </c>
-      <c r="H74" t="s">
-        <v>17</v>
+      <c r="H74" t="str">
+        <v/>
       </c>
       <c r="I74">
         <v>3</v>
       </c>
-      <c r="J74" t="s">
-        <v>17</v>
+      <c r="J74" t="str">
+        <v/>
       </c>
       <c r="K74">
-        <v>-76.992858052253737</v>
+        <v>-76.99285805225374</v>
       </c>
       <c r="L74">
-        <v>37.576462019016013</v>
+        <v>37.57646201901601</v>
       </c>
       <c r="M74">
         <v>181542</v>
@@ -3745,15 +3655,15 @@
         <v>90771</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75">
       <c r="A75">
         <v>10015</v>
       </c>
-      <c r="B75" t="s">
-        <v>23</v>
-      </c>
-      <c r="C75" t="s">
-        <v>18</v>
+      <c r="B75" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C75" t="str">
+        <v>W</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3761,23 +3671,23 @@
       <c r="E75">
         <v>1141</v>
       </c>
-      <c r="F75" t="s">
-        <v>19</v>
+      <c r="F75" t="str">
+        <v>S</v>
       </c>
       <c r="G75">
         <v>0.5</v>
       </c>
-      <c r="H75" t="s">
-        <v>17</v>
+      <c r="H75" t="str">
+        <v/>
       </c>
       <c r="I75">
         <v>5.37</v>
       </c>
-      <c r="J75" t="s">
-        <v>17</v>
+      <c r="J75" t="str">
+        <v/>
       </c>
       <c r="K75">
-        <v>-76.992718577384963</v>
+        <v>-76.99271857738496</v>
       </c>
       <c r="L75">
         <v>37.57565635216379</v>
@@ -3789,15 +3699,15 @@
         <v>95545</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76">
       <c r="A76">
         <v>10016</v>
       </c>
-      <c r="B76" t="s">
-        <v>23</v>
-      </c>
-      <c r="C76" t="s">
-        <v>18</v>
+      <c r="B76" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C76" t="str">
+        <v>W</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -3805,23 +3715,23 @@
       <c r="E76">
         <v>724</v>
       </c>
-      <c r="F76" t="s">
-        <v>20</v>
+      <c r="F76" t="str">
+        <v>P</v>
       </c>
       <c r="G76">
         <v>0.5</v>
       </c>
-      <c r="H76" t="s">
-        <v>17</v>
+      <c r="H76" t="str">
+        <v/>
       </c>
       <c r="I76">
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="J76" t="s">
-        <v>17</v>
+        <v>2.03</v>
+      </c>
+      <c r="J76" t="str">
+        <v/>
       </c>
       <c r="K76">
-        <v>-76.992694437503829</v>
+        <v>-76.99269443750383</v>
       </c>
       <c r="L76">
         <v>37.57607300418362</v>
@@ -3833,15 +3743,15 @@
         <v>91273</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77">
       <c r="A77">
         <v>10017</v>
       </c>
-      <c r="B77" t="s">
-        <v>23</v>
-      </c>
-      <c r="C77" t="s">
-        <v>18</v>
+      <c r="B77" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C77" t="str">
+        <v>W</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3849,26 +3759,26 @@
       <c r="E77">
         <v>795</v>
       </c>
-      <c r="F77" t="s">
-        <v>20</v>
+      <c r="F77" t="str">
+        <v>P</v>
       </c>
       <c r="G77">
         <v>0.5</v>
       </c>
-      <c r="H77" t="s">
-        <v>17</v>
+      <c r="H77" t="str">
+        <v/>
       </c>
       <c r="I77">
         <v>4.46</v>
       </c>
-      <c r="J77" t="s">
-        <v>17</v>
+      <c r="J77" t="str">
+        <v/>
       </c>
       <c r="K77">
-        <v>-76.992149949073806</v>
+        <v>-76.9921499490738</v>
       </c>
       <c r="L77">
-        <v>37.575662729508181</v>
+        <v>37.57566272950818</v>
       </c>
       <c r="M77">
         <v>184001</v>
@@ -3877,15 +3787,15 @@
         <v>92001</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78">
       <c r="A78">
         <v>10018</v>
       </c>
-      <c r="B78" t="s">
-        <v>23</v>
-      </c>
-      <c r="C78" t="s">
-        <v>18</v>
+      <c r="B78" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C78" t="str">
+        <v>W</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -3893,26 +3803,26 @@
       <c r="E78">
         <v>604</v>
       </c>
-      <c r="F78" t="s">
-        <v>20</v>
+      <c r="F78" t="str">
+        <v>P</v>
       </c>
       <c r="G78">
         <v>0.5</v>
       </c>
-      <c r="H78" t="s">
-        <v>17</v>
+      <c r="H78" t="str">
+        <v/>
       </c>
       <c r="I78">
         <v>4.46</v>
       </c>
-      <c r="J78" t="s">
-        <v>17</v>
+      <c r="J78" t="str">
+        <v/>
       </c>
       <c r="K78">
         <v>-76.99204266071321</v>
       </c>
       <c r="L78">
-        <v>37.575611710737668</v>
+        <v>37.57561171073767</v>
       </c>
       <c r="M78">
         <v>192461</v>
@@ -3921,15 +3831,15 @@
         <v>96231</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79">
       <c r="A79">
         <v>10019</v>
       </c>
-      <c r="B79" t="s">
-        <v>23</v>
-      </c>
-      <c r="C79" t="s">
-        <v>18</v>
+      <c r="B79" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C79" t="str">
+        <v>W</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3937,23 +3847,23 @@
       <c r="E79">
         <v>444</v>
       </c>
-      <c r="F79" t="s">
-        <v>20</v>
+      <c r="F79" t="str">
+        <v>P</v>
       </c>
       <c r="G79">
         <v>0.5</v>
       </c>
-      <c r="H79" t="s">
-        <v>17</v>
+      <c r="H79" t="str">
+        <v/>
       </c>
       <c r="I79">
         <v>4</v>
       </c>
-      <c r="J79" t="s">
-        <v>17</v>
+      <c r="J79" t="str">
+        <v/>
       </c>
       <c r="K79">
-        <v>-76.991924643516555</v>
+        <v>-76.99192464351655</v>
       </c>
       <c r="L79">
         <v>37.57556919506888</v>
@@ -3965,15 +3875,15 @@
         <v>88405</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80">
       <c r="A80">
         <v>10020</v>
       </c>
-      <c r="B80" t="s">
-        <v>23</v>
-      </c>
-      <c r="C80" t="s">
-        <v>18</v>
+      <c r="B80" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C80" t="str">
+        <v>W</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -3981,23 +3891,23 @@
       <c r="E80">
         <v>183</v>
       </c>
-      <c r="F80" t="s">
-        <v>20</v>
+      <c r="F80" t="str">
+        <v>P</v>
       </c>
       <c r="G80">
         <v>1.5</v>
       </c>
-      <c r="H80" t="s">
-        <v>17</v>
+      <c r="H80" t="str">
+        <v/>
       </c>
       <c r="I80">
         <v>2.59</v>
       </c>
-      <c r="J80" t="s">
-        <v>17</v>
+      <c r="J80" t="str">
+        <v/>
       </c>
       <c r="K80">
-        <v>-76.991734206676497</v>
+        <v>-76.9917342066765</v>
       </c>
       <c r="L80">
         <v>37.575473534725326</v>
@@ -4009,15 +3919,15 @@
         <v>85732</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81">
       <c r="A81">
         <v>10021</v>
       </c>
-      <c r="B81" t="s">
-        <v>23</v>
-      </c>
-      <c r="C81" t="s">
-        <v>15</v>
+      <c r="B81" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C81" t="str">
+        <v>H</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -4025,26 +3935,26 @@
       <c r="E81">
         <v>298</v>
       </c>
-      <c r="F81" t="s">
-        <v>19</v>
+      <c r="F81" t="str">
+        <v>S</v>
       </c>
       <c r="G81">
         <v>0.5</v>
       </c>
-      <c r="H81" t="s">
-        <v>17</v>
+      <c r="H81" t="str">
+        <v/>
       </c>
       <c r="I81">
         <v>7.53</v>
       </c>
-      <c r="J81" t="s">
-        <v>17</v>
+      <c r="J81" t="str">
+        <v/>
       </c>
       <c r="K81">
-        <v>-76.991232633590712</v>
+        <v>-76.99123263359071</v>
       </c>
       <c r="L81">
-        <v>37.574695492700229</v>
+        <v>37.57469549270023</v>
       </c>
       <c r="M81">
         <v>173819</v>
@@ -4053,15 +3963,15 @@
         <v>86910</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82">
       <c r="A82">
         <v>10022</v>
       </c>
-      <c r="B82" t="s">
-        <v>23</v>
-      </c>
-      <c r="C82" t="s">
-        <v>15</v>
+      <c r="B82" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C82" t="str">
+        <v>H</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -4069,26 +3979,26 @@
       <c r="E82">
         <v>717</v>
       </c>
-      <c r="F82" t="s">
-        <v>19</v>
+      <c r="F82" t="str">
+        <v>S</v>
       </c>
       <c r="G82">
         <v>0.5</v>
       </c>
-      <c r="H82" t="s">
-        <v>17</v>
+      <c r="H82" t="str">
+        <v/>
       </c>
       <c r="I82">
         <v>5.71</v>
       </c>
-      <c r="J82" t="s">
-        <v>17</v>
+      <c r="J82" t="str">
+        <v/>
       </c>
       <c r="K82">
-        <v>-76.991305053234115</v>
+        <v>-76.99130505323411</v>
       </c>
       <c r="L82">
-        <v>37.574491414757738</v>
+        <v>37.57449141475774</v>
       </c>
       <c r="M82">
         <v>182403</v>
@@ -4097,15 +4007,15 @@
         <v>91202</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83">
       <c r="A83">
         <v>10023</v>
       </c>
-      <c r="B83" t="s">
-        <v>23</v>
-      </c>
-      <c r="C83" t="s">
-        <v>18</v>
+      <c r="B83" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C83" t="str">
+        <v>W</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -4113,26 +4023,26 @@
       <c r="E83">
         <v>389</v>
       </c>
-      <c r="F83" t="s">
-        <v>19</v>
+      <c r="F83" t="str">
+        <v>S</v>
       </c>
       <c r="G83">
         <v>0.5</v>
       </c>
-      <c r="H83" t="s">
-        <v>17</v>
+      <c r="H83" t="str">
+        <v/>
       </c>
       <c r="I83">
         <v>6.85</v>
       </c>
-      <c r="J83" t="s">
-        <v>17</v>
+      <c r="J83" t="str">
+        <v/>
       </c>
       <c r="K83">
-        <v>-76.990881264209762</v>
+        <v>-76.99088126420976</v>
       </c>
       <c r="L83">
-        <v>37.574691241082128</v>
+        <v>37.57469124108213</v>
       </c>
       <c r="M83">
         <v>175684</v>
@@ -4141,15 +4051,15 @@
         <v>87842</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84">
       <c r="A84">
         <v>10024</v>
       </c>
-      <c r="B84" t="s">
-        <v>21</v>
-      </c>
-      <c r="C84" t="s">
-        <v>18</v>
+      <c r="B84" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C84" t="str">
+        <v>W</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -4157,23 +4067,23 @@
       <c r="E84">
         <v>1681</v>
       </c>
-      <c r="F84" t="s">
-        <v>16</v>
+      <c r="F84" t="str">
+        <v>C</v>
       </c>
       <c r="G84">
         <v>0.5</v>
       </c>
-      <c r="H84" t="s">
-        <v>17</v>
+      <c r="H84" t="str">
+        <v/>
       </c>
       <c r="I84">
         <v>6.7</v>
       </c>
-      <c r="J84" t="s">
-        <v>17</v>
+      <c r="J84" t="str">
+        <v/>
       </c>
       <c r="K84">
-        <v>-76.990763247013106</v>
+        <v>-76.9907632470131</v>
       </c>
       <c r="L84">
         <v>37.57479115404324</v>
@@ -4185,15 +4095,15 @@
         <v>101076</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85">
       <c r="A85">
         <v>10025</v>
       </c>
-      <c r="B85" t="s">
-        <v>21</v>
-      </c>
-      <c r="C85" t="s">
-        <v>18</v>
+      <c r="B85" t="str">
+        <v>RES1</v>
+      </c>
+      <c r="C85" t="str">
+        <v>W</v>
       </c>
       <c r="D85">
         <v>2</v>
@@ -4201,26 +4111,26 @@
       <c r="E85">
         <v>1590</v>
       </c>
-      <c r="F85" t="s">
-        <v>16</v>
+      <c r="F85" t="str">
+        <v>C</v>
       </c>
       <c r="G85">
         <v>1</v>
       </c>
-      <c r="H85" t="s">
-        <v>17</v>
+      <c r="H85" t="str">
+        <v/>
       </c>
       <c r="I85">
         <v>13.94</v>
       </c>
-      <c r="J85" t="s">
-        <v>17</v>
+      <c r="J85" t="str">
+        <v/>
       </c>
       <c r="K85">
-        <v>-76.996181309223189</v>
+        <v>-76.99618130922319</v>
       </c>
       <c r="L85">
-        <v>37.576899923991498</v>
+        <v>37.5768999239915</v>
       </c>
       <c r="M85">
         <v>232859</v>
@@ -4229,15 +4139,15 @@
         <v>116430</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86">
       <c r="A86">
         <v>10026</v>
       </c>
-      <c r="B86" t="s">
-        <v>23</v>
-      </c>
-      <c r="C86" t="s">
-        <v>18</v>
+      <c r="B86" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C86" t="str">
+        <v>W</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -4245,26 +4155,26 @@
       <c r="E86">
         <v>880</v>
       </c>
-      <c r="F86" t="s">
-        <v>19</v>
+      <c r="F86" t="str">
+        <v>S</v>
       </c>
       <c r="G86">
         <v>0.5</v>
       </c>
-      <c r="H86" t="s">
-        <v>17</v>
+      <c r="H86" t="str">
+        <v/>
       </c>
       <c r="I86">
         <v>12.44</v>
       </c>
-      <c r="J86" t="s">
-        <v>17</v>
+      <c r="J86" t="str">
+        <v/>
       </c>
       <c r="K86">
-        <v>-76.996253728866577</v>
+        <v>-76.99625372886658</v>
       </c>
       <c r="L86">
-        <v>37.577189024894111</v>
+        <v>37.57718902489411</v>
       </c>
       <c r="M86">
         <v>185742</v>
@@ -4273,15 +4183,15 @@
         <v>92871</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87">
       <c r="A87">
         <v>10027</v>
       </c>
-      <c r="B87" t="s">
-        <v>23</v>
-      </c>
-      <c r="C87" t="s">
-        <v>18</v>
+      <c r="B87" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C87" t="str">
+        <v>W</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -4289,26 +4199,26 @@
       <c r="E87">
         <v>679</v>
       </c>
-      <c r="F87" t="s">
-        <v>19</v>
+      <c r="F87" t="str">
+        <v>S</v>
       </c>
       <c r="G87">
         <v>0.5</v>
       </c>
-      <c r="H87" t="s">
-        <v>17</v>
+      <c r="H87" t="str">
+        <v/>
       </c>
       <c r="I87">
         <v>12.54</v>
       </c>
-      <c r="J87" t="s">
-        <v>17</v>
+      <c r="J87" t="str">
+        <v/>
       </c>
       <c r="K87">
-        <v>-76.996162533760085</v>
+        <v>-76.99616253376009</v>
       </c>
       <c r="L87">
-        <v>37.577254922736863</v>
+        <v>37.57725492273686</v>
       </c>
       <c r="M87">
         <v>181624</v>
@@ -4317,15 +4227,15 @@
         <v>90812</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88">
       <c r="A88">
         <v>10028</v>
       </c>
-      <c r="B88" t="s">
-        <v>23</v>
-      </c>
-      <c r="C88" t="s">
-        <v>18</v>
+      <c r="B88" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C88" t="str">
+        <v>W</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -4333,23 +4243,23 @@
       <c r="E88">
         <v>457</v>
       </c>
-      <c r="F88" t="s">
-        <v>19</v>
+      <c r="F88" t="str">
+        <v>S</v>
       </c>
       <c r="G88">
         <v>0.5</v>
       </c>
-      <c r="H88" t="s">
-        <v>17</v>
+      <c r="H88" t="str">
+        <v/>
       </c>
       <c r="I88">
         <v>12.24</v>
       </c>
-      <c r="J88" t="s">
-        <v>17</v>
+      <c r="J88" t="str">
+        <v/>
       </c>
       <c r="K88">
-        <v>-76.996618509292617</v>
+        <v>-76.99661850929262</v>
       </c>
       <c r="L88">
         <v>37.577346329325465</v>
@@ -4361,15 +4271,15 @@
         <v>88539</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89">
       <c r="A89">
         <v>10029</v>
       </c>
-      <c r="B89" t="s">
-        <v>23</v>
-      </c>
-      <c r="C89" t="s">
-        <v>18</v>
+      <c r="B89" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C89" t="str">
+        <v>W</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -4377,23 +4287,23 @@
       <c r="E89">
         <v>354</v>
       </c>
-      <c r="F89" t="s">
-        <v>19</v>
+      <c r="F89" t="str">
+        <v>S</v>
       </c>
       <c r="G89">
         <v>0.5</v>
       </c>
-      <c r="H89" t="s">
-        <v>17</v>
+      <c r="H89" t="str">
+        <v/>
       </c>
       <c r="I89">
         <v>12.5</v>
       </c>
-      <c r="J89" t="s">
-        <v>17</v>
+      <c r="J89" t="str">
+        <v/>
       </c>
       <c r="K89">
-        <v>-76.996733844280257</v>
+        <v>-76.99673384428026</v>
       </c>
       <c r="L89">
         <v>37.577371838120854</v>
@@ -4405,15 +4315,15 @@
         <v>87484</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90">
       <c r="A90">
         <v>10030</v>
       </c>
-      <c r="B90" t="s">
-        <v>23</v>
-      </c>
-      <c r="C90" t="s">
-        <v>18</v>
+      <c r="B90" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C90" t="str">
+        <v>W</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -4421,20 +4331,20 @@
       <c r="E90">
         <v>814</v>
       </c>
-      <c r="F90" t="s">
-        <v>19</v>
+      <c r="F90" t="str">
+        <v>S</v>
       </c>
       <c r="G90">
         <v>0.5</v>
       </c>
-      <c r="H90" t="s">
-        <v>17</v>
+      <c r="H90" t="str">
+        <v/>
       </c>
       <c r="I90">
         <v>15.02</v>
       </c>
-      <c r="J90" t="s">
-        <v>17</v>
+      <c r="J90" t="str">
+        <v/>
       </c>
       <c r="K90">
         <v>-76.99879646301271</v>
@@ -4449,15 +4359,15 @@
         <v>92195</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91">
       <c r="A91">
         <v>10031</v>
       </c>
-      <c r="B91" t="s">
-        <v>23</v>
-      </c>
-      <c r="C91" t="s">
-        <v>18</v>
+      <c r="B91" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C91" t="str">
+        <v>W</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -4465,26 +4375,26 @@
       <c r="E91">
         <v>1233</v>
       </c>
-      <c r="F91" t="s">
-        <v>19</v>
+      <c r="F91" t="str">
+        <v>S</v>
       </c>
       <c r="G91">
         <v>0.5</v>
       </c>
-      <c r="H91" t="s">
-        <v>17</v>
+      <c r="H91" t="str">
+        <v/>
       </c>
       <c r="I91">
         <v>15.13</v>
       </c>
-      <c r="J91" t="s">
-        <v>17</v>
+      <c r="J91" t="str">
+        <v/>
       </c>
       <c r="K91">
         <v>-77.00027704238893</v>
       </c>
       <c r="L91">
-        <v>37.577635428494879</v>
+        <v>37.57763542849488</v>
       </c>
       <c r="M91">
         <v>192973</v>
@@ -4493,15 +4403,15 @@
         <v>96487</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92">
       <c r="A92">
         <v>10032</v>
       </c>
-      <c r="B92" t="s">
-        <v>23</v>
-      </c>
-      <c r="C92" t="s">
-        <v>18</v>
+      <c r="B92" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C92" t="str">
+        <v>W</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -4509,26 +4419,26 @@
       <c r="E92">
         <v>1069</v>
       </c>
-      <c r="F92" t="s">
-        <v>19</v>
+      <c r="F92" t="str">
+        <v>S</v>
       </c>
       <c r="G92">
         <v>0.5</v>
       </c>
-      <c r="H92" t="s">
-        <v>17</v>
+      <c r="H92" t="str">
+        <v/>
       </c>
       <c r="I92">
         <v>14.25</v>
       </c>
-      <c r="J92" t="s">
-        <v>17</v>
+      <c r="J92" t="str">
+        <v/>
       </c>
       <c r="K92">
-        <v>-77.000389695167556</v>
+        <v>-77.00038969516756</v>
       </c>
       <c r="L92">
-        <v>37.577405849834463</v>
+        <v>37.57740584983446</v>
       </c>
       <c r="M92">
         <v>189614</v>
@@ -4537,15 +4447,15 @@
         <v>94807</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93">
       <c r="A93">
         <v>10033</v>
       </c>
-      <c r="B93" t="s">
-        <v>23</v>
-      </c>
-      <c r="C93" t="s">
-        <v>15</v>
+      <c r="B93" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C93" t="str">
+        <v>H</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -4553,26 +4463,26 @@
       <c r="E93">
         <v>2043</v>
       </c>
-      <c r="F93" t="s">
-        <v>19</v>
+      <c r="F93" t="str">
+        <v>S</v>
       </c>
       <c r="G93">
         <v>0.5</v>
       </c>
-      <c r="H93" t="s">
-        <v>17</v>
+      <c r="H93" t="str">
+        <v/>
       </c>
       <c r="I93">
         <v>9.81</v>
       </c>
-      <c r="J93" t="s">
-        <v>17</v>
+      <c r="J93" t="str">
+        <v/>
       </c>
       <c r="K93">
-        <v>-77.000998556613936</v>
+        <v>-77.00099855661394</v>
       </c>
       <c r="L93">
-        <v>37.579612326556934</v>
+        <v>37.57961232655693</v>
       </c>
       <c r="M93">
         <v>209567</v>
@@ -4581,15 +4491,15 @@
         <v>104784</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94">
       <c r="A94">
         <v>10034</v>
       </c>
-      <c r="B94" t="s">
-        <v>23</v>
-      </c>
-      <c r="C94" t="s">
-        <v>15</v>
+      <c r="B94" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C94" t="str">
+        <v>H</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -4597,23 +4507,23 @@
       <c r="E94">
         <v>490</v>
       </c>
-      <c r="F94" t="s">
-        <v>19</v>
+      <c r="F94" t="str">
+        <v>S</v>
       </c>
       <c r="G94">
         <v>0.5</v>
       </c>
-      <c r="H94" t="s">
-        <v>17</v>
+      <c r="H94" t="str">
+        <v/>
       </c>
       <c r="I94">
         <v>8.65</v>
       </c>
-      <c r="J94" t="s">
-        <v>17</v>
+      <c r="J94" t="str">
+        <v/>
       </c>
       <c r="K94">
-        <v>-77.001344561576857</v>
+        <v>-77.00134456157686</v>
       </c>
       <c r="L94">
         <v>37.57922120250327</v>
@@ -4625,15 +4535,15 @@
         <v>88877</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95">
       <c r="A95">
         <v>10035</v>
       </c>
-      <c r="B95" t="s">
-        <v>23</v>
-      </c>
-      <c r="C95" t="s">
-        <v>15</v>
+      <c r="B95" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C95" t="str">
+        <v>H</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -4641,26 +4551,26 @@
       <c r="E95">
         <v>215</v>
       </c>
-      <c r="F95" t="s">
-        <v>19</v>
+      <c r="F95" t="str">
+        <v>S</v>
       </c>
       <c r="G95">
         <v>0.5</v>
       </c>
-      <c r="H95" t="s">
-        <v>17</v>
+      <c r="H95" t="str">
+        <v/>
       </c>
       <c r="I95">
         <v>9.68</v>
       </c>
-      <c r="J95" t="s">
-        <v>17</v>
+      <c r="J95" t="str">
+        <v/>
       </c>
       <c r="K95">
-        <v>-77.002672255039229</v>
+        <v>-77.00267225503923</v>
       </c>
       <c r="L95">
-        <v>37.579529425434558</v>
+        <v>37.57952942543456</v>
       </c>
       <c r="M95">
         <v>172119</v>
@@ -4669,15 +4579,15 @@
         <v>86060</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96">
       <c r="A96">
         <v>10036</v>
       </c>
-      <c r="B96" t="s">
-        <v>23</v>
-      </c>
-      <c r="C96" t="s">
-        <v>15</v>
+      <c r="B96" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C96" t="str">
+        <v>H</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -4685,23 +4595,23 @@
       <c r="E96">
         <v>208</v>
       </c>
-      <c r="F96" t="s">
-        <v>19</v>
+      <c r="F96" t="str">
+        <v>S</v>
       </c>
       <c r="G96">
         <v>0.5</v>
       </c>
-      <c r="H96" t="s">
-        <v>17</v>
+      <c r="H96" t="str">
+        <v/>
       </c>
       <c r="I96">
         <v>10.1</v>
       </c>
-      <c r="J96" t="s">
-        <v>17</v>
+      <c r="J96" t="str">
+        <v/>
       </c>
       <c r="K96">
-        <v>-77.002868056297316</v>
+        <v>-77.00286805629732</v>
       </c>
       <c r="L96">
         <v>37.57945715258586</v>
@@ -4713,15 +4623,15 @@
         <v>85988</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97">
       <c r="A97">
         <v>10037</v>
       </c>
-      <c r="B97" t="s">
-        <v>28</v>
-      </c>
-      <c r="C97" t="s">
-        <v>15</v>
+      <c r="B97" t="str">
+        <v>RES3F</v>
+      </c>
+      <c r="C97" t="str">
+        <v>H</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -4729,26 +4639,26 @@
       <c r="E97">
         <v>1365</v>
       </c>
-      <c r="F97" t="s">
-        <v>19</v>
+      <c r="F97" t="str">
+        <v>S</v>
       </c>
       <c r="G97">
         <v>0.5</v>
       </c>
-      <c r="H97" t="s">
-        <v>17</v>
+      <c r="H97" t="str">
+        <v/>
       </c>
       <c r="I97">
         <v>10.91</v>
       </c>
-      <c r="J97" t="s">
-        <v>17</v>
+      <c r="J97" t="str">
+        <v/>
       </c>
       <c r="K97">
-        <v>-77.008551657199874</v>
+        <v>-77.00855165719987</v>
       </c>
       <c r="L97">
-        <v>37.576999833989191</v>
+        <v>37.57699983398919</v>
       </c>
       <c r="M97">
         <v>195677</v>
@@ -4757,15 +4667,15 @@
         <v>97839</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98">
       <c r="A98">
         <v>10038</v>
       </c>
-      <c r="B98" t="s">
-        <v>23</v>
-      </c>
-      <c r="C98" t="s">
-        <v>15</v>
+      <c r="B98" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C98" t="str">
+        <v>H</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -4773,23 +4683,23 @@
       <c r="E98">
         <v>995</v>
       </c>
-      <c r="F98" t="s">
-        <v>19</v>
+      <c r="F98" t="str">
+        <v>S</v>
       </c>
       <c r="G98">
         <v>0.5</v>
       </c>
-      <c r="H98" t="s">
-        <v>17</v>
+      <c r="H98" t="str">
+        <v/>
       </c>
       <c r="I98">
         <v>12.39</v>
       </c>
-      <c r="J98" t="s">
-        <v>17</v>
+      <c r="J98" t="str">
+        <v/>
       </c>
       <c r="K98">
-        <v>-77.006564140319838</v>
+        <v>-77.00656414031984</v>
       </c>
       <c r="L98">
         <v>37.574346859210095</v>
@@ -4801,15 +4711,15 @@
         <v>94049</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99">
       <c r="A99">
         <v>10039</v>
       </c>
-      <c r="B99" t="s">
-        <v>23</v>
-      </c>
-      <c r="C99" t="s">
-        <v>15</v>
+      <c r="B99" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C99" t="str">
+        <v>H</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -4817,26 +4727,26 @@
       <c r="E99">
         <v>739</v>
       </c>
-      <c r="F99" t="s">
-        <v>19</v>
+      <c r="F99" t="str">
+        <v>S</v>
       </c>
       <c r="G99">
         <v>0.5</v>
       </c>
-      <c r="H99" t="s">
-        <v>17</v>
+      <c r="H99" t="str">
+        <v/>
       </c>
       <c r="I99">
-        <v>9.9600000000000009</v>
-      </c>
-      <c r="J99" t="s">
-        <v>17</v>
+        <v>9.96</v>
+      </c>
+      <c r="J99" t="str">
+        <v/>
       </c>
       <c r="K99">
-        <v>-77.006832361221328</v>
+        <v>-77.00683236122133</v>
       </c>
       <c r="L99">
-        <v>37.573609196384339</v>
+        <v>37.57360919638434</v>
       </c>
       <c r="M99">
         <v>182853</v>
@@ -4845,15 +4755,15 @@
         <v>91427</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100">
       <c r="A100">
         <v>10040</v>
       </c>
-      <c r="B100" t="s">
-        <v>23</v>
-      </c>
-      <c r="C100" t="s">
-        <v>18</v>
+      <c r="B100" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C100" t="str">
+        <v>W</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -4861,23 +4771,23 @@
       <c r="E100">
         <v>1280</v>
       </c>
-      <c r="F100" t="s">
-        <v>19</v>
+      <c r="F100" t="str">
+        <v>S</v>
       </c>
       <c r="G100">
         <v>0.5</v>
       </c>
-      <c r="H100" t="s">
-        <v>17</v>
+      <c r="H100" t="str">
+        <v/>
       </c>
       <c r="I100">
-        <v>8.9600000000000009</v>
-      </c>
-      <c r="J100" t="s">
-        <v>17</v>
+        <v>8.96</v>
+      </c>
+      <c r="J100" t="str">
+        <v/>
       </c>
       <c r="K100">
-        <v>-77.006210088729873</v>
+        <v>-77.00621008872987</v>
       </c>
       <c r="L100">
         <v>37.57288853313819</v>
@@ -4889,15 +4799,15 @@
         <v>96968</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101">
       <c r="A101">
         <v>10041</v>
       </c>
-      <c r="B101" t="s">
-        <v>23</v>
-      </c>
-      <c r="C101" t="s">
-        <v>18</v>
+      <c r="B101" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C101" t="str">
+        <v>W</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -4905,26 +4815,26 @@
       <c r="E101">
         <v>388</v>
       </c>
-      <c r="F101" t="s">
-        <v>19</v>
+      <c r="F101" t="str">
+        <v>S</v>
       </c>
       <c r="G101">
         <v>0.5</v>
       </c>
-      <c r="H101" t="s">
-        <v>17</v>
+      <c r="H101" t="str">
+        <v/>
       </c>
       <c r="I101">
         <v>8.09</v>
       </c>
-      <c r="J101" t="s">
-        <v>17</v>
+      <c r="J101" t="str">
+        <v/>
       </c>
       <c r="K101">
-        <v>-77.004922628402724</v>
+        <v>-77.00492262840272</v>
       </c>
       <c r="L101">
-        <v>37.572350688471957</v>
+        <v>37.57235068847196</v>
       </c>
       <c r="M101">
         <v>175663</v>
@@ -4933,15 +4843,15 @@
         <v>87832</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102">
       <c r="A102">
         <v>10042</v>
       </c>
-      <c r="B102" t="s">
-        <v>23</v>
-      </c>
-      <c r="C102" t="s">
-        <v>18</v>
+      <c r="B102" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C102" t="str">
+        <v>W</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -4949,26 +4859,26 @@
       <c r="E102">
         <v>1529</v>
       </c>
-      <c r="F102" t="s">
-        <v>19</v>
+      <c r="F102" t="str">
+        <v>S</v>
       </c>
       <c r="G102">
         <v>0.5</v>
       </c>
-      <c r="H102" t="s">
-        <v>17</v>
+      <c r="H102" t="str">
+        <v/>
       </c>
       <c r="I102">
         <v>5.92</v>
       </c>
-      <c r="J102" t="s">
-        <v>17</v>
+      <c r="J102" t="str">
+        <v/>
       </c>
       <c r="K102">
-        <v>-77.005341053009047</v>
+        <v>-77.00534105300905</v>
       </c>
       <c r="L102">
-        <v>37.571336638753387</v>
+        <v>37.57133663875339</v>
       </c>
       <c r="M102">
         <v>199037</v>
@@ -4977,15 +4887,15 @@
         <v>99519</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103">
       <c r="A103">
         <v>10043</v>
       </c>
-      <c r="B103" t="s">
-        <v>23</v>
-      </c>
-      <c r="C103" t="s">
-        <v>18</v>
+      <c r="B103" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C103" t="str">
+        <v>W</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -4993,26 +4903,26 @@
       <c r="E103">
         <v>582</v>
       </c>
-      <c r="F103" t="s">
-        <v>19</v>
+      <c r="F103" t="str">
+        <v>S</v>
       </c>
       <c r="G103">
         <v>0.5</v>
       </c>
-      <c r="H103" t="s">
-        <v>17</v>
+      <c r="H103" t="str">
+        <v/>
       </c>
       <c r="I103">
-        <v>10.029999999999999</v>
-      </c>
-      <c r="J103" t="s">
-        <v>17</v>
+        <v>10.03</v>
+      </c>
+      <c r="J103" t="str">
+        <v/>
       </c>
       <c r="K103">
-        <v>-77.003940939903273</v>
+        <v>-77.00394093990327</v>
       </c>
       <c r="L103">
-        <v>37.574676360416888</v>
+        <v>37.57467636041689</v>
       </c>
       <c r="M103">
         <v>179637</v>
@@ -5021,15 +4931,15 @@
         <v>89819</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104">
       <c r="A104">
         <v>10044</v>
       </c>
-      <c r="B104" t="s">
-        <v>23</v>
-      </c>
-      <c r="C104" t="s">
-        <v>18</v>
+      <c r="B104" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C104" t="str">
+        <v>W</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -5037,23 +4947,23 @@
       <c r="E104">
         <v>573</v>
       </c>
-      <c r="F104" t="s">
-        <v>19</v>
+      <c r="F104" t="str">
+        <v>S</v>
       </c>
       <c r="G104">
         <v>0.5</v>
       </c>
-      <c r="H104" t="s">
-        <v>17</v>
+      <c r="H104" t="str">
+        <v/>
       </c>
       <c r="I104">
         <v>11.28</v>
       </c>
-      <c r="J104" t="s">
-        <v>17</v>
+      <c r="J104" t="str">
+        <v/>
       </c>
       <c r="K104">
-        <v>-77.003962397575393</v>
+        <v>-77.00396239757539</v>
       </c>
       <c r="L104">
         <v>37.574997356964715</v>
@@ -5065,15 +4975,15 @@
         <v>89727</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105">
       <c r="A105">
         <v>10045</v>
       </c>
-      <c r="B105" t="s">
-        <v>23</v>
-      </c>
-      <c r="C105" t="s">
-        <v>18</v>
+      <c r="B105" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C105" t="str">
+        <v>W</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -5081,26 +4991,26 @@
       <c r="E105">
         <v>358</v>
       </c>
-      <c r="F105" t="s">
-        <v>19</v>
+      <c r="F105" t="str">
+        <v>S</v>
       </c>
       <c r="G105">
         <v>0.5</v>
       </c>
-      <c r="H105" t="s">
-        <v>17</v>
+      <c r="H105" t="str">
+        <v/>
       </c>
       <c r="I105">
         <v>12.36</v>
       </c>
-      <c r="J105" t="s">
-        <v>17</v>
+      <c r="J105" t="str">
+        <v/>
       </c>
       <c r="K105">
-        <v>-77.002733945846572</v>
+        <v>-77.00273394584657</v>
       </c>
       <c r="L105">
-        <v>37.575820037163879</v>
+        <v>37.57582003716388</v>
       </c>
       <c r="M105">
         <v>175048</v>
@@ -5109,15 +5019,15 @@
         <v>87524</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106">
       <c r="A106">
         <v>10046</v>
       </c>
-      <c r="B106" t="s">
-        <v>23</v>
-      </c>
-      <c r="C106" t="s">
-        <v>18</v>
+      <c r="B106" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C106" t="str">
+        <v>W</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -5125,26 +5035,26 @@
       <c r="E106">
         <v>984</v>
       </c>
-      <c r="F106" t="s">
-        <v>19</v>
+      <c r="F106" t="str">
+        <v>S</v>
       </c>
       <c r="G106">
         <v>0.5</v>
       </c>
-      <c r="H106" t="s">
-        <v>17</v>
+      <c r="H106" t="str">
+        <v/>
       </c>
       <c r="I106">
         <v>10.35</v>
       </c>
-      <c r="J106" t="s">
-        <v>17</v>
+      <c r="J106" t="str">
+        <v/>
       </c>
       <c r="K106">
-        <v>-77.002076804637923</v>
+        <v>-77.00207680463792</v>
       </c>
       <c r="L106">
-        <v>37.574531805228233</v>
+        <v>37.57453180522823</v>
       </c>
       <c r="M106">
         <v>187872</v>
@@ -5153,15 +5063,15 @@
         <v>93936</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107">
       <c r="A107">
         <v>10047</v>
       </c>
-      <c r="B107" t="s">
-        <v>14</v>
-      </c>
-      <c r="C107" t="s">
-        <v>15</v>
+      <c r="B107" t="str">
+        <v>RES2</v>
+      </c>
+      <c r="C107" t="str">
+        <v>H</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -5169,26 +5079,26 @@
       <c r="E107">
         <v>2185</v>
       </c>
-      <c r="F107" t="s">
-        <v>20</v>
+      <c r="F107" t="str">
+        <v>P</v>
       </c>
       <c r="G107">
         <v>3</v>
       </c>
-      <c r="H107" t="s">
-        <v>17</v>
+      <c r="H107" t="str">
+        <v/>
       </c>
       <c r="I107">
         <v>7.29</v>
       </c>
-      <c r="J107" t="s">
-        <v>17</v>
+      <c r="J107" t="str">
+        <v/>
       </c>
       <c r="K107">
         <v>-77.0009019970894</v>
       </c>
       <c r="L107">
-        <v>37.574153409435262</v>
+        <v>37.57415340943526</v>
       </c>
       <c r="M107">
         <v>212475</v>
@@ -5197,15 +5107,15 @@
         <v>106238</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108">
       <c r="A108">
         <v>10048</v>
       </c>
-      <c r="B108" t="s">
-        <v>23</v>
-      </c>
-      <c r="C108" t="s">
-        <v>18</v>
+      <c r="B108" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C108" t="str">
+        <v>W</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -5213,26 +5123,26 @@
       <c r="E108">
         <v>532</v>
       </c>
-      <c r="F108" t="s">
-        <v>20</v>
+      <c r="F108" t="str">
+        <v>P</v>
       </c>
       <c r="G108">
         <v>1</v>
       </c>
-      <c r="H108" t="s">
-        <v>17</v>
+      <c r="H108" t="str">
+        <v/>
       </c>
       <c r="I108">
         <v>6.49</v>
       </c>
-      <c r="J108" t="s">
-        <v>17</v>
+      <c r="J108" t="str">
+        <v/>
       </c>
       <c r="K108">
-        <v>-77.000821530818953</v>
+        <v>-77.00082153081895</v>
       </c>
       <c r="L108">
-        <v>37.573815402578632</v>
+        <v>37.57381540257863</v>
       </c>
       <c r="M108">
         <v>178613</v>
@@ -5241,15 +5151,15 @@
         <v>89307</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109">
       <c r="A109">
         <v>10049</v>
       </c>
-      <c r="B109" t="s">
-        <v>23</v>
-      </c>
-      <c r="C109" t="s">
-        <v>18</v>
+      <c r="B109" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C109" t="str">
+        <v>W</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -5257,26 +5167,26 @@
       <c r="E109">
         <v>1687</v>
       </c>
-      <c r="F109" t="s">
-        <v>16</v>
+      <c r="F109" t="str">
+        <v>C</v>
       </c>
       <c r="G109">
         <v>0.5</v>
       </c>
-      <c r="H109" t="s">
-        <v>17</v>
+      <c r="H109" t="str">
+        <v/>
       </c>
       <c r="I109">
         <v>10.39</v>
       </c>
-      <c r="J109" t="s">
-        <v>17</v>
+      <c r="J109" t="str">
+        <v/>
       </c>
       <c r="K109">
-        <v>-77.008634805679335</v>
+        <v>-77.00863480567934</v>
       </c>
       <c r="L109">
-        <v>37.580864334848123</v>
+        <v>37.58086433484812</v>
       </c>
       <c r="M109">
         <v>202274</v>
@@ -5285,15 +5195,15 @@
         <v>101137</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110">
       <c r="A110">
         <v>10050</v>
       </c>
-      <c r="B110" t="s">
-        <v>23</v>
-      </c>
-      <c r="C110" t="s">
-        <v>15</v>
+      <c r="B110" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C110" t="str">
+        <v>H</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -5301,26 +5211,26 @@
       <c r="E110">
         <v>1272</v>
       </c>
-      <c r="F110" t="s">
-        <v>19</v>
+      <c r="F110" t="str">
+        <v>S</v>
       </c>
       <c r="G110">
         <v>0.5</v>
       </c>
-      <c r="H110" t="s">
-        <v>17</v>
+      <c r="H110" t="str">
+        <v/>
       </c>
       <c r="I110">
         <v>10.52</v>
       </c>
-      <c r="J110" t="s">
-        <v>17</v>
+      <c r="J110" t="str">
+        <v/>
       </c>
       <c r="K110">
-        <v>-77.009133696556106</v>
+        <v>-77.0091336965561</v>
       </c>
       <c r="L110">
-        <v>37.579754746218377</v>
+        <v>37.57975474621838</v>
       </c>
       <c r="M110">
         <v>193772</v>
@@ -5329,15 +5239,15 @@
         <v>96886</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111">
       <c r="A111">
         <v>10051</v>
       </c>
-      <c r="B111" t="s">
-        <v>23</v>
-      </c>
-      <c r="C111" t="s">
-        <v>18</v>
+      <c r="B111" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C111" t="str">
+        <v>W</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -5345,26 +5255,26 @@
       <c r="E111">
         <v>689</v>
       </c>
-      <c r="F111" t="s">
-        <v>19</v>
+      <c r="F111" t="str">
+        <v>S</v>
       </c>
       <c r="G111">
         <v>0.5</v>
       </c>
-      <c r="H111" t="s">
-        <v>17</v>
+      <c r="H111" t="str">
+        <v/>
       </c>
       <c r="I111">
         <v>13</v>
       </c>
-      <c r="J111" t="s">
-        <v>17</v>
+      <c r="J111" t="str">
+        <v/>
       </c>
       <c r="K111">
-        <v>-77.012167274951949</v>
+        <v>-77.01216727495195</v>
       </c>
       <c r="L111">
-        <v>37.577242168320232</v>
+        <v>37.57724216832023</v>
       </c>
       <c r="M111">
         <v>181829</v>
@@ -5373,15 +5283,15 @@
         <v>90915</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112">
       <c r="A112">
         <v>10052</v>
       </c>
-      <c r="B112" t="s">
-        <v>23</v>
-      </c>
-      <c r="C112" t="s">
-        <v>18</v>
+      <c r="B112" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C112" t="str">
+        <v>W</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -5389,26 +5299,26 @@
       <c r="E112">
         <v>642</v>
       </c>
-      <c r="F112" t="s">
-        <v>19</v>
+      <c r="F112" t="str">
+        <v>S</v>
       </c>
       <c r="G112">
         <v>0.5</v>
       </c>
-      <c r="H112" t="s">
-        <v>17</v>
+      <c r="H112" t="str">
+        <v/>
       </c>
       <c r="I112">
         <v>11.37</v>
       </c>
-      <c r="J112" t="s">
-        <v>17</v>
+      <c r="J112" t="str">
+        <v/>
       </c>
       <c r="K112">
-        <v>-77.011330425739303</v>
+        <v>-77.0113304257393</v>
       </c>
       <c r="L112">
-        <v>37.576925432939831</v>
+        <v>37.57692543293983</v>
       </c>
       <c r="M112">
         <v>180866</v>
@@ -5417,15 +5327,15 @@
         <v>90433</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="113">
       <c r="A113">
         <v>579537068</v>
       </c>
-      <c r="B113" t="s">
-        <v>23</v>
-      </c>
-      <c r="C113" t="s">
-        <v>18</v>
+      <c r="B113" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C113" t="str">
+        <v>W</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -5433,23 +5343,23 @@
       <c r="E113">
         <v>642</v>
       </c>
-      <c r="F113" t="s">
-        <v>19</v>
+      <c r="F113" t="str">
+        <v>S</v>
       </c>
       <c r="G113">
         <v>0.5</v>
       </c>
-      <c r="H113" t="s">
-        <v>17</v>
+      <c r="H113" t="str">
+        <v/>
       </c>
       <c r="I113">
         <v>10.87</v>
       </c>
-      <c r="J113" t="s">
-        <v>17</v>
+      <c r="J113" t="str">
+        <v/>
       </c>
       <c r="K113">
-        <v>-77.011164128780379</v>
+        <v>-77.01116412878038</v>
       </c>
       <c r="L113">
         <v>37.57661507347494</v>
@@ -5461,15 +5371,15 @@
         <v>90433</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="114">
       <c r="A114">
         <v>579537069</v>
       </c>
-      <c r="B114" t="s">
-        <v>23</v>
-      </c>
-      <c r="C114" t="s">
-        <v>18</v>
+      <c r="B114" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C114" t="str">
+        <v>W</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -5477,20 +5387,20 @@
       <c r="E114">
         <v>642</v>
       </c>
-      <c r="F114" t="s">
-        <v>19</v>
+      <c r="F114" t="str">
+        <v>S</v>
       </c>
       <c r="G114">
         <v>0.5</v>
       </c>
-      <c r="H114" t="s">
-        <v>17</v>
+      <c r="H114" t="str">
+        <v/>
       </c>
       <c r="I114">
         <v>12.48</v>
       </c>
-      <c r="J114" t="s">
-        <v>17</v>
+      <c r="J114" t="str">
+        <v/>
       </c>
       <c r="K114">
         <v>-77.01164156198503</v>
@@ -5505,15 +5415,15 @@
         <v>90433</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="115">
       <c r="A115">
         <v>10006</v>
       </c>
-      <c r="B115" t="s">
-        <v>23</v>
-      </c>
-      <c r="C115" t="s">
-        <v>18</v>
+      <c r="B115" t="str">
+        <v>RES4</v>
+      </c>
+      <c r="C115" t="str">
+        <v>W</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -5521,26 +5431,26 @@
       <c r="E115">
         <v>1157</v>
       </c>
-      <c r="F115" t="s">
-        <v>19</v>
+      <c r="F115" t="str">
+        <v>S</v>
       </c>
       <c r="G115">
         <v>0.5</v>
       </c>
-      <c r="H115" t="s">
-        <v>17</v>
+      <c r="H115" t="str">
+        <v/>
       </c>
       <c r="I115">
         <v>5.21</v>
       </c>
-      <c r="J115" t="s">
-        <v>17</v>
+      <c r="J115" t="str">
+        <v/>
       </c>
       <c r="K115">
-        <v>-76.997310519218459</v>
+        <v>-76.99731051921846</v>
       </c>
       <c r="L115">
-        <v>37.574017356545383</v>
+        <v>37.57401735654538</v>
       </c>
       <c r="M115">
         <v>191416</v>
@@ -5550,9 +5460,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:N16 A18:N40 A17:F17 H17:N17 A42:N115 A41:H41 J41:N41" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N115"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/DDD___Pamunkey___NSI.xlsx
+++ b/DDD___Pamunkey___NSI.xlsx
@@ -2332,7 +2332,7 @@
         <v>224184.03</v>
       </c>
       <c r="N44">
-        <v>362092.02</v>
+        <v>112092</v>
       </c>
     </row>
     <row r="45">
